--- a/playlists.xlsx
+++ b/playlists.xlsx
@@ -9,8 +9,8 @@
     <sheet name="playlists" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1415</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="2007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="2013">
   <si>
     <t xml:space="preserve">Playlist Name</t>
   </si>
@@ -5356,6 +5356,9 @@
     <t>Anri</t>
   </si>
   <si>
+    <t xml:space="preserve">This is Zabadak</t>
+  </si>
+  <si>
     <t xml:space="preserve">ガラスのPALM TREE</t>
   </si>
   <si>
@@ -5953,6 +5956,12 @@
     <t>DeBarge</t>
   </si>
   <si>
+    <t xml:space="preserve">Haven't You Heard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrice Rushen</t>
+  </si>
+  <si>
     <t xml:space="preserve">All Night Long</t>
   </si>
   <si>
@@ -5962,6 +5971,9 @@
     <t xml:space="preserve">Mint Condition</t>
   </si>
   <si>
+    <t xml:space="preserve">Forget Me Nots</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mr. Telephone Man</t>
   </si>
   <si>
@@ -6041,6 +6053,12 @@
   </si>
   <si>
     <t>Puzzle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stay With Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remind Me</t>
   </si>
 </sst>
 </file>
@@ -6116,7 +6134,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6155,6 +6173,9 @@
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -10623,7 +10644,7 @@
       <c r="D305"/>
       <c r="G305"/>
     </row>
-    <row r="306" s="0" customFormat="1" ht="12.75">
+    <row r="306" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A306" s="6" t="s">
         <v>469</v>
       </c>
@@ -10673,7 +10694,7 @@
       <c r="AO306"/>
       <c r="AP306"/>
     </row>
-    <row r="307" s="0" customFormat="1" ht="12.75">
+    <row r="307" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A307" s="6" t="s">
         <v>469</v>
       </c>
@@ -10686,7 +10707,7 @@
       <c r="D307"/>
       <c r="G307"/>
     </row>
-    <row r="308" s="0" customFormat="1" ht="12.75">
+    <row r="308" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A308" s="6" t="s">
         <v>469</v>
       </c>
@@ -10736,7 +10757,7 @@
       <c r="AO308"/>
       <c r="AP308"/>
     </row>
-    <row r="309" s="0" customFormat="1" ht="12.75">
+    <row r="309" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A309" s="6" t="s">
         <v>469</v>
       </c>
@@ -10749,7 +10770,7 @@
       <c r="D309"/>
       <c r="G309"/>
     </row>
-    <row r="310" s="0" customFormat="1" ht="12.75">
+    <row r="310" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A310" s="6" t="s">
         <v>469</v>
       </c>
@@ -10799,7 +10820,7 @@
       <c r="AO310"/>
       <c r="AP310"/>
     </row>
-    <row r="311" s="0" customFormat="1" ht="12.75">
+    <row r="311" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A311" s="6" t="s">
         <v>469</v>
       </c>
@@ -10812,7 +10833,7 @@
       <c r="D311"/>
       <c r="G311"/>
     </row>
-    <row r="312" s="0" customFormat="1" ht="12.75">
+    <row r="312" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A312" s="6" t="s">
         <v>469</v>
       </c>
@@ -10862,7 +10883,7 @@
       <c r="AO312"/>
       <c r="AP312"/>
     </row>
-    <row r="313" s="0" customFormat="1" ht="12.75">
+    <row r="313" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A313" s="6" t="s">
         <v>469</v>
       </c>
@@ -10875,7 +10896,7 @@
       <c r="D313"/>
       <c r="G313"/>
     </row>
-    <row r="314" s="0" customFormat="1" ht="12.75">
+    <row r="314" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A314" s="6" t="s">
         <v>469</v>
       </c>
@@ -10925,7 +10946,7 @@
       <c r="AO314"/>
       <c r="AP314"/>
     </row>
-    <row r="315" s="0" customFormat="1" ht="12.75">
+    <row r="315" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A315" s="6" t="s">
         <v>469</v>
       </c>
@@ -10938,7 +10959,7 @@
       <c r="D315"/>
       <c r="G315"/>
     </row>
-    <row r="316" s="0" customFormat="1" ht="12.75">
+    <row r="316" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A316" s="6" t="s">
         <v>469</v>
       </c>
@@ -10988,7 +11009,7 @@
       <c r="AO316"/>
       <c r="AP316"/>
     </row>
-    <row r="317" s="0" customFormat="1" ht="12.75">
+    <row r="317" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A317" s="6" t="s">
         <v>469</v>
       </c>
@@ -11001,7 +11022,7 @@
       <c r="D317"/>
       <c r="G317"/>
     </row>
-    <row r="318" s="0" customFormat="1" ht="12.75">
+    <row r="318" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A318" s="6" t="s">
         <v>469</v>
       </c>
@@ -11051,7 +11072,7 @@
       <c r="AO318"/>
       <c r="AP318"/>
     </row>
-    <row r="319" s="0" customFormat="1" ht="12.75">
+    <row r="319" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A319" s="6" t="s">
         <v>469</v>
       </c>
@@ -11064,7 +11085,7 @@
       <c r="D319"/>
       <c r="G319"/>
     </row>
-    <row r="320" s="0" customFormat="1" ht="12.75">
+    <row r="320" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A320" s="6" t="s">
         <v>469</v>
       </c>
@@ -11114,7 +11135,7 @@
       <c r="AO320"/>
       <c r="AP320"/>
     </row>
-    <row r="321" s="0" customFormat="1" ht="12.75">
+    <row r="321" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A321" s="6" t="s">
         <v>469</v>
       </c>
@@ -11127,7 +11148,7 @@
       <c r="D321"/>
       <c r="G321"/>
     </row>
-    <row r="322" s="0" customFormat="1" ht="12.75">
+    <row r="322" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A322" s="6" t="s">
         <v>469</v>
       </c>
@@ -11177,7 +11198,7 @@
       <c r="AO322"/>
       <c r="AP322"/>
     </row>
-    <row r="323" s="0" customFormat="1" ht="12.75">
+    <row r="323" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A323" s="6" t="s">
         <v>469</v>
       </c>
@@ -11190,7 +11211,7 @@
       <c r="D323"/>
       <c r="G323"/>
     </row>
-    <row r="324" s="0" customFormat="1" ht="12.75">
+    <row r="324" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A324" s="6" t="s">
         <v>469</v>
       </c>
@@ -11240,7 +11261,7 @@
       <c r="AO324"/>
       <c r="AP324"/>
     </row>
-    <row r="325" s="0" customFormat="1" ht="12.75">
+    <row r="325" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A325" s="6" t="s">
         <v>469</v>
       </c>
@@ -11253,7 +11274,7 @@
       <c r="D325"/>
       <c r="G325"/>
     </row>
-    <row r="326" s="0" customFormat="1" ht="12.75">
+    <row r="326" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A326" s="6" t="s">
         <v>469</v>
       </c>
@@ -11303,7 +11324,7 @@
       <c r="AO326"/>
       <c r="AP326"/>
     </row>
-    <row r="327" s="0" customFormat="1" ht="12.75">
+    <row r="327" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A327" s="6" t="s">
         <v>469</v>
       </c>
@@ -11353,7 +11374,7 @@
       <c r="AO327"/>
       <c r="AP327"/>
     </row>
-    <row r="328" s="0" customFormat="1" ht="12.75">
+    <row r="328" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A328" s="6" t="s">
         <v>469</v>
       </c>
@@ -11365,7 +11386,7 @@
       </c>
       <c r="D328"/>
     </row>
-    <row r="329" s="0" customFormat="1" ht="12.75">
+    <row r="329" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A329" s="6" t="s">
         <v>469</v>
       </c>
@@ -11415,7 +11436,7 @@
       <c r="AO329"/>
       <c r="AP329"/>
     </row>
-    <row r="330" s="0" customFormat="1" ht="12.75">
+    <row r="330" s="0" customFormat="1" ht="12.75" hidden="1">
       <c r="A330" s="6" t="s">
         <v>469</v>
       </c>
@@ -20398,7 +20419,7 @@
       <c r="D1022"/>
       <c r="G1022"/>
     </row>
-    <row r="1023" ht="12.75">
+    <row r="1023" ht="12.75" hidden="1">
       <c r="A1023" s="6" t="s">
         <v>469</v>
       </c>
@@ -20410,7 +20431,7 @@
       </c>
       <c r="D1023" s="1"/>
     </row>
-    <row r="1024" ht="12.75">
+    <row r="1024" ht="12.75" hidden="1">
       <c r="A1024" s="6" t="s">
         <v>469</v>
       </c>
@@ -20423,7 +20444,7 @@
       <c r="D1024"/>
       <c r="G1024"/>
     </row>
-    <row r="1025" ht="12.75">
+    <row r="1025" ht="12.75" hidden="1">
       <c r="A1025" s="6" t="s">
         <v>469</v>
       </c>
@@ -20435,7 +20456,7 @@
       </c>
       <c r="D1025" s="1"/>
     </row>
-    <row r="1026" ht="12.75">
+    <row r="1026" ht="12.75" hidden="1">
       <c r="A1026" s="6" t="s">
         <v>469</v>
       </c>
@@ -20448,7 +20469,7 @@
       <c r="D1026"/>
       <c r="G1026"/>
     </row>
-    <row r="1027" ht="12.75">
+    <row r="1027" ht="12.75" hidden="1">
       <c r="A1027" s="6" t="s">
         <v>469</v>
       </c>
@@ -20460,7 +20481,7 @@
       </c>
       <c r="D1027" s="1"/>
     </row>
-    <row r="1028" ht="12.75">
+    <row r="1028" ht="12.75" hidden="1">
       <c r="A1028" s="6" t="s">
         <v>469</v>
       </c>
@@ -20473,7 +20494,7 @@
       <c r="D1028"/>
       <c r="G1028"/>
     </row>
-    <row r="1029" ht="12.75">
+    <row r="1029" ht="12.75" hidden="1">
       <c r="A1029" s="6" t="s">
         <v>469</v>
       </c>
@@ -20485,7 +20506,7 @@
       </c>
       <c r="D1029" s="1"/>
     </row>
-    <row r="1030" ht="12.75">
+    <row r="1030" ht="12.75" hidden="1">
       <c r="A1030" s="6" t="s">
         <v>469</v>
       </c>
@@ -20498,7 +20519,7 @@
       <c r="D1030"/>
       <c r="G1030"/>
     </row>
-    <row r="1031" ht="12.75">
+    <row r="1031" ht="12.75" hidden="1">
       <c r="A1031" s="6" t="s">
         <v>469</v>
       </c>
@@ -20510,7 +20531,7 @@
       </c>
       <c r="D1031" s="1"/>
     </row>
-    <row r="1032" ht="12.75">
+    <row r="1032" ht="12.75" hidden="1">
       <c r="A1032" s="6" t="s">
         <v>469</v>
       </c>
@@ -20523,7 +20544,7 @@
       <c r="D1032"/>
       <c r="G1032"/>
     </row>
-    <row r="1033" ht="12.75">
+    <row r="1033" ht="12.75" hidden="1">
       <c r="A1033" s="6" t="s">
         <v>469</v>
       </c>
@@ -20535,7 +20556,7 @@
       </c>
       <c r="D1033" s="1"/>
     </row>
-    <row r="1034" ht="12.75">
+    <row r="1034" ht="12.75" hidden="1">
       <c r="A1034" s="6" t="s">
         <v>469</v>
       </c>
@@ -20548,7 +20569,7 @@
       <c r="D1034"/>
       <c r="G1034"/>
     </row>
-    <row r="1035" ht="12.75">
+    <row r="1035" ht="12.75" hidden="1">
       <c r="A1035" s="6" t="s">
         <v>469</v>
       </c>
@@ -20560,7 +20581,7 @@
       </c>
       <c r="D1035" s="1"/>
     </row>
-    <row r="1036" ht="12.75">
+    <row r="1036" ht="12.75" hidden="1">
       <c r="A1036" s="6" t="s">
         <v>469</v>
       </c>
@@ -20573,7 +20594,7 @@
       <c r="D1036"/>
       <c r="G1036"/>
     </row>
-    <row r="1037" ht="12.75">
+    <row r="1037" ht="12.75" hidden="1">
       <c r="A1037" s="6" t="s">
         <v>469</v>
       </c>
@@ -22719,7 +22740,7 @@
       <c r="D1208"/>
       <c r="G1208"/>
     </row>
-    <row r="1209" ht="12.75" hidden="1">
+    <row r="1209" ht="12.75">
       <c r="A1209" s="6" t="s">
         <v>1733</v>
       </c>
@@ -22731,7 +22752,7 @@
       </c>
       <c r="D1209" s="1"/>
     </row>
-    <row r="1210" ht="12.75" hidden="1">
+    <row r="1210" ht="12.75">
       <c r="A1210" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22744,7 +22765,7 @@
       <c r="D1210" s="1"/>
       <c r="G1210" s="1"/>
     </row>
-    <row r="1211" ht="12.75" hidden="1">
+    <row r="1211" ht="12.75">
       <c r="A1211" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22756,7 +22777,7 @@
       </c>
       <c r="D1211" s="1"/>
     </row>
-    <row r="1212" ht="12.75" hidden="1">
+    <row r="1212" ht="12.75">
       <c r="A1212" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22769,7 +22790,7 @@
       <c r="D1212"/>
       <c r="G1212"/>
     </row>
-    <row r="1213" ht="12.75" hidden="1">
+    <row r="1213" ht="12.75">
       <c r="A1213" s="6" t="s">
         <v>1733</v>
       </c>
@@ -22781,7 +22802,7 @@
       </c>
       <c r="D1213" s="1"/>
     </row>
-    <row r="1214" ht="12.75" hidden="1">
+    <row r="1214" ht="12.75">
       <c r="A1214" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22794,7 +22815,7 @@
       <c r="D1214"/>
       <c r="G1214"/>
     </row>
-    <row r="1215" ht="12.75" hidden="1">
+    <row r="1215" ht="12.75">
       <c r="A1215" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22806,7 +22827,7 @@
       </c>
       <c r="D1215" s="1"/>
     </row>
-    <row r="1216" ht="12.75" hidden="1">
+    <row r="1216" ht="12.75">
       <c r="A1216" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22819,7 +22840,7 @@
       <c r="D1216"/>
       <c r="G1216"/>
     </row>
-    <row r="1217" ht="12.75" hidden="1">
+    <row r="1217" ht="12.75">
       <c r="A1217" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22831,7 +22852,7 @@
       </c>
       <c r="D1217" s="1"/>
     </row>
-    <row r="1218" ht="12.75" hidden="1">
+    <row r="1218" ht="12.75">
       <c r="A1218" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22844,7 +22865,7 @@
       <c r="D1218"/>
       <c r="G1218"/>
     </row>
-    <row r="1219" ht="12.75" hidden="1">
+    <row r="1219" ht="12.75">
       <c r="A1219" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22856,7 +22877,7 @@
       </c>
       <c r="D1219" s="1"/>
     </row>
-    <row r="1220" ht="12.75" hidden="1">
+    <row r="1220" ht="12.75">
       <c r="A1220" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22869,7 +22890,7 @@
       <c r="D1220"/>
       <c r="G1220"/>
     </row>
-    <row r="1221" ht="12.75" hidden="1">
+    <row r="1221" ht="12.75">
       <c r="A1221" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22881,7 +22902,7 @@
       </c>
       <c r="D1221" s="1"/>
     </row>
-    <row r="1222" ht="12.75" hidden="1">
+    <row r="1222" ht="12.75">
       <c r="A1222" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22894,7 +22915,7 @@
       <c r="D1222"/>
       <c r="G1222"/>
     </row>
-    <row r="1223" ht="12.75" hidden="1">
+    <row r="1223" ht="12.75">
       <c r="A1223" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22906,7 +22927,7 @@
       </c>
       <c r="D1223" s="1"/>
     </row>
-    <row r="1224" ht="12.75" hidden="1">
+    <row r="1224" ht="12.75">
       <c r="A1224" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22919,7 +22940,7 @@
       <c r="D1224"/>
       <c r="G1224"/>
     </row>
-    <row r="1225" ht="12.75" hidden="1">
+    <row r="1225" ht="12.75">
       <c r="A1225" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22931,7 +22952,7 @@
       </c>
       <c r="D1225" s="1"/>
     </row>
-    <row r="1226" ht="12.75" hidden="1">
+    <row r="1226" ht="12.75">
       <c r="A1226" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22944,7 +22965,7 @@
       <c r="D1226"/>
       <c r="G1226"/>
     </row>
-    <row r="1227" ht="12.75" hidden="1">
+    <row r="1227" ht="12.75">
       <c r="A1227" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22956,7 +22977,7 @@
       </c>
       <c r="D1227" s="1"/>
     </row>
-    <row r="1228" ht="12.75" hidden="1">
+    <row r="1228" ht="12.75">
       <c r="A1228" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22969,7 +22990,7 @@
       <c r="D1228"/>
       <c r="G1228"/>
     </row>
-    <row r="1229" ht="12.75" hidden="1">
+    <row r="1229" ht="12.75">
       <c r="A1229" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22981,7 +23002,7 @@
       </c>
       <c r="D1229" s="1"/>
     </row>
-    <row r="1230" ht="12.75" hidden="1">
+    <row r="1230" ht="12.75">
       <c r="A1230" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22994,7 +23015,7 @@
       <c r="D1230"/>
       <c r="G1230"/>
     </row>
-    <row r="1231" ht="12.75" hidden="1">
+    <row r="1231" ht="12.75">
       <c r="A1231" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23006,7 +23027,7 @@
       </c>
       <c r="D1231" s="1"/>
     </row>
-    <row r="1232" ht="12.75" hidden="1">
+    <row r="1232" ht="12.75">
       <c r="A1232" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23019,9 +23040,9 @@
       <c r="D1232"/>
       <c r="G1232"/>
     </row>
-    <row r="1233" ht="12.75" hidden="1">
+    <row r="1233" ht="12.75">
       <c r="A1233" s="11" t="s">
-        <v>1733</v>
+        <v>1778</v>
       </c>
       <c r="B1233" t="s">
         <v>1596</v>
@@ -23031,12 +23052,12 @@
       </c>
       <c r="D1233" s="1"/>
     </row>
-    <row r="1234" ht="12.75" hidden="1">
+    <row r="1234" ht="12.75">
       <c r="A1234" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1234" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C1234" t="s">
         <v>1745</v>
@@ -23044,44 +23065,44 @@
       <c r="D1234"/>
       <c r="G1234"/>
     </row>
-    <row r="1235" ht="12.75" hidden="1">
+    <row r="1235" ht="12.75">
       <c r="A1235" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1235" s="1" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C1235" t="s">
         <v>1743</v>
       </c>
       <c r="D1235" s="1"/>
     </row>
-    <row r="1236" ht="12.75" hidden="1">
+    <row r="1236" ht="12.75">
       <c r="A1236" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1236" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="C1236" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="D1236"/>
       <c r="G1236"/>
     </row>
-    <row r="1237" ht="12.75" hidden="1">
+    <row r="1237" ht="12.75">
       <c r="A1237" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1237" s="8" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C1237" s="8" t="s">
         <v>1764</v>
       </c>
       <c r="D1237" s="1"/>
     </row>
-    <row r="1238" ht="12.75" hidden="1">
+    <row r="1238" ht="12.75">
       <c r="A1238" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23094,24 +23115,24 @@
       <c r="D1238"/>
       <c r="G1238"/>
     </row>
-    <row r="1239" ht="12.75" hidden="1">
+    <row r="1239" ht="12.75">
       <c r="A1239" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1239" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C1239" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D1239" s="1"/>
     </row>
-    <row r="1240" ht="12.75" hidden="1">
+    <row r="1240" ht="12.75">
       <c r="A1240" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1240" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C1240" t="s">
         <v>1765</v>
@@ -23119,44 +23140,44 @@
       <c r="D1240"/>
       <c r="G1240"/>
     </row>
-    <row r="1241" ht="12.75" hidden="1">
+    <row r="1241" ht="12.75">
       <c r="A1241" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1241" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C1241" t="s">
         <v>1747</v>
       </c>
       <c r="D1241" s="1"/>
     </row>
-    <row r="1242" ht="12.75" hidden="1">
+    <row r="1242" ht="12.75">
       <c r="A1242" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1242" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C1242" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D1242"/>
       <c r="G1242"/>
     </row>
-    <row r="1243" ht="12.75" hidden="1">
+    <row r="1243" ht="12.75">
       <c r="A1243" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1243" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C1243" s="1" t="s">
         <v>1777</v>
       </c>
       <c r="D1243" s="1"/>
     </row>
-    <row r="1244" ht="12.75" hidden="1">
+    <row r="1244" ht="12.75">
       <c r="A1244" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23168,12 +23189,12 @@
       </c>
       <c r="D1244" s="1"/>
     </row>
-    <row r="1245" ht="12.75" hidden="1">
+    <row r="1245" ht="12.75">
       <c r="A1245" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1245" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C1245" t="s">
         <v>278</v>
@@ -23181,24 +23202,24 @@
       <c r="D1245"/>
       <c r="G1245"/>
     </row>
-    <row r="1246" ht="12.75" hidden="1">
+    <row r="1246" ht="12.75">
       <c r="A1246" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1246" s="8" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="C1246" s="8" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1246" s="1"/>
     </row>
-    <row r="1247" ht="12.75" hidden="1">
+    <row r="1247" ht="12.75">
       <c r="A1247" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1247" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="C1247" s="13" t="s">
         <v>1737</v>
@@ -23206,49 +23227,49 @@
       <c r="D1247"/>
       <c r="G1247"/>
     </row>
-    <row r="1248" ht="12.75" hidden="1">
+    <row r="1248" ht="12.75">
       <c r="A1248" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1248" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C1248" t="s">
         <v>1745</v>
       </c>
       <c r="D1248" s="1"/>
     </row>
-    <row r="1249" ht="12.75" hidden="1">
+    <row r="1249" ht="12.75">
       <c r="A1249" s="7" t="s">
         <v>1733</v>
       </c>
       <c r="B1249" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="C1249" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="D1249"/>
       <c r="G1249"/>
     </row>
-    <row r="1250" ht="12.75" hidden="1">
+    <row r="1250" ht="12.75">
       <c r="A1250" s="7" t="s">
         <v>1733</v>
       </c>
       <c r="B1250" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C1250" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="D1250" s="1"/>
     </row>
-    <row r="1251" ht="12.75" hidden="1">
+    <row r="1251" ht="12.75">
       <c r="A1251" s="7" t="s">
         <v>1733</v>
       </c>
       <c r="B1251" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="C1251" t="s">
         <v>1745</v>
@@ -23256,19 +23277,19 @@
       <c r="D1251"/>
       <c r="G1251"/>
     </row>
-    <row r="1252" ht="12.75" hidden="1">
+    <row r="1252" ht="12.75">
       <c r="A1252" s="7" t="s">
         <v>1733</v>
       </c>
       <c r="B1252" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C1252" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D1252" s="1"/>
     </row>
-    <row r="1253" ht="12.75" hidden="1">
+    <row r="1253" ht="12.75">
       <c r="A1253" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23281,24 +23302,24 @@
       <c r="D1253"/>
       <c r="G1253"/>
     </row>
-    <row r="1254" ht="12.75" hidden="1">
+    <row r="1254" ht="12.75">
       <c r="A1254" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1254" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C1254" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D1254" s="1"/>
     </row>
-    <row r="1255" ht="12.75" hidden="1">
+    <row r="1255" ht="12.75">
       <c r="A1255" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1255" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C1255" t="s">
         <v>1747</v>
@@ -23306,27 +23327,27 @@
       <c r="D1255"/>
       <c r="G1255"/>
     </row>
-    <row r="1256" ht="12.75" hidden="1">
+    <row r="1256" ht="12.75">
       <c r="A1256" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1256" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="C1256" t="s">
         <v>1745</v>
       </c>
       <c r="D1256" s="1"/>
     </row>
-    <row r="1257" ht="12.75" hidden="1">
+    <row r="1257" ht="12.75">
       <c r="A1257" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1257" s="1" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C1257" s="1" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D1257"/>
       <c r="G1257"/>
@@ -23336,7 +23357,7 @@
         <v>1586</v>
       </c>
       <c r="B1258" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C1258" t="s">
         <v>1531</v>
@@ -23345,13 +23366,13 @@
     </row>
     <row r="1259" ht="12.75" hidden="1">
       <c r="A1259" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1259" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C1259" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D1259"/>
       <c r="G1259"/>
@@ -23364,7 +23385,7 @@
     </row>
     <row r="1261" ht="12.75" hidden="1">
       <c r="A1261" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1261" s="9" t="s">
         <v>1599</v>
@@ -23377,22 +23398,22 @@
     </row>
     <row r="1262" ht="12.75" hidden="1">
       <c r="A1262" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1262" s="1" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="C1262" s="1" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="D1262" s="1"/>
     </row>
     <row r="1263" ht="12.75" hidden="1">
       <c r="A1263" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1263" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="C1263" t="s">
         <v>423</v>
@@ -23401,10 +23422,10 @@
     </row>
     <row r="1264" ht="12.75" hidden="1">
       <c r="A1264" s="7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1264" s="1" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="C1264" s="1" t="s">
         <v>1145</v>
@@ -23414,7 +23435,7 @@
     </row>
     <row r="1265" ht="12.75" hidden="1">
       <c r="A1265" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1265" s="9" t="s">
         <v>1600</v>
@@ -23427,19 +23448,19 @@
     </row>
     <row r="1266" ht="12.75" hidden="1">
       <c r="A1266" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1266" s="1" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="C1266" s="1" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="D1266" s="1"/>
     </row>
     <row r="1267" ht="12.75" hidden="1">
       <c r="A1267" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1267" t="s">
         <v>428</v>
@@ -23451,10 +23472,10 @@
     </row>
     <row r="1268" ht="12.75" hidden="1">
       <c r="A1268" s="7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1268" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="C1268" t="s">
         <v>956</v>
@@ -23464,7 +23485,7 @@
     </row>
     <row r="1269" ht="12.75" hidden="1">
       <c r="A1269" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1269" s="9" t="s">
         <v>1605</v>
@@ -23476,10 +23497,10 @@
     </row>
     <row r="1270" ht="12.75" hidden="1">
       <c r="A1270" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1270" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="C1270" t="s">
         <v>1145</v>
@@ -23489,10 +23510,10 @@
     </row>
     <row r="1271" ht="12.75" hidden="1">
       <c r="A1271" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1271" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C1271" s="9" t="s">
         <v>423</v>
@@ -23501,22 +23522,22 @@
     </row>
     <row r="1272" ht="12.75" hidden="1">
       <c r="A1272" s="7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1272" s="1" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C1272" s="1" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="D1272" s="1"/>
     </row>
     <row r="1273" ht="12.75" hidden="1">
       <c r="A1273" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1273" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="C1273" s="9" t="s">
         <v>423</v>
@@ -23529,7 +23550,7 @@
         <v>1598</v>
       </c>
       <c r="B1274" s="1" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="C1274" s="9" t="s">
         <v>423</v>
@@ -23539,13 +23560,13 @@
     </row>
     <row r="1275" ht="12.75" hidden="1">
       <c r="A1275" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1275" s="8" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="C1275" s="8" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D1275" s="1"/>
     </row>
@@ -23554,7 +23575,7 @@
         <v>1665</v>
       </c>
       <c r="B1276" s="1" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="C1276" s="1" t="s">
         <v>1667</v>
@@ -23564,10 +23585,10 @@
     </row>
     <row r="1277" ht="12.75" hidden="1">
       <c r="A1277" s="6" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1277" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="C1277" t="s">
         <v>1542</v>
@@ -23576,33 +23597,33 @@
     </row>
     <row r="1278" ht="12.75" hidden="1">
       <c r="A1278" s="6" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1278" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="C1278" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D1278"/>
       <c r="G1278"/>
     </row>
     <row r="1279" ht="12.75" hidden="1">
       <c r="A1279" s="6" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1279" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="C1279"/>
       <c r="D1279" s="1"/>
     </row>
     <row r="1280" ht="12.75" hidden="1">
       <c r="A1280" s="6" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1280" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="C1280" t="s">
         <v>432</v>
@@ -23615,7 +23636,7 @@
         <v>1665</v>
       </c>
       <c r="B1281" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C1281" s="1" t="s">
         <v>1667</v>
@@ -23624,23 +23645,23 @@
     </row>
     <row r="1282" ht="12.75" hidden="1">
       <c r="A1282" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1282" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="C1282" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="D1282"/>
       <c r="G1282"/>
     </row>
     <row r="1283" ht="12.75" hidden="1">
       <c r="A1283" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1283" s="8" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="C1283" t="s">
         <v>432</v>
@@ -23649,10 +23670,10 @@
     </row>
     <row r="1284" ht="12.75" hidden="1">
       <c r="A1284" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1284" s="8" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="C1284" t="s">
         <v>1112</v>
@@ -23662,10 +23683,10 @@
     </row>
     <row r="1285" ht="12.75" hidden="1">
       <c r="A1285" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1285" s="8" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C1285" t="s">
         <v>497</v>
@@ -23674,23 +23695,23 @@
     </row>
     <row r="1286" ht="12.75" hidden="1">
       <c r="A1286" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1286" s="8" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="C1286" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="D1286"/>
       <c r="G1286"/>
     </row>
     <row r="1287" ht="12.75" hidden="1">
       <c r="A1287" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1287" s="8" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="C1287" t="s">
         <v>1123</v>
@@ -23699,10 +23720,10 @@
     </row>
     <row r="1288" ht="12.75" hidden="1">
       <c r="A1288" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1288" s="8" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="C1288" t="s">
         <v>126</v>
@@ -23712,47 +23733,47 @@
     </row>
     <row r="1289" ht="12.75" hidden="1">
       <c r="A1289" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1289" s="8" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="C1289" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="D1289" s="1"/>
     </row>
     <row r="1290" ht="12.75" hidden="1">
       <c r="A1290" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1290" s="8" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="C1290" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="D1290"/>
       <c r="G1290"/>
     </row>
     <row r="1291" ht="12.75" hidden="1">
       <c r="A1291" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1291" s="8" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C1291" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="D1291" s="1"/>
     </row>
     <row r="1292" ht="12.75" hidden="1">
       <c r="A1292" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1292" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="C1292"/>
       <c r="D1292"/>
@@ -23760,22 +23781,22 @@
     </row>
     <row r="1293" ht="12.75" hidden="1">
       <c r="A1293" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1293" s="8" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="C1293" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="D1293" s="1"/>
     </row>
     <row r="1294" ht="12.75" hidden="1">
       <c r="A1294" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1294" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C1294" t="s">
         <v>423</v>
@@ -23783,27 +23804,27 @@
       <c r="D1294"/>
       <c r="G1294"/>
     </row>
-    <row r="1295" ht="12.75" hidden="1">
+    <row r="1295" ht="12.75">
       <c r="A1295" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1295" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C1295" t="s">
         <v>1764</v>
       </c>
       <c r="D1295" s="1"/>
     </row>
-    <row r="1296" ht="12.75" hidden="1">
+    <row r="1296" ht="12.75">
       <c r="A1296" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1296" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C1296" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="D1296"/>
       <c r="G1296"/>
@@ -23813,264 +23834,264 @@
         <v>1342</v>
       </c>
       <c r="B1297" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C1297" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="D1297" s="1"/>
     </row>
-    <row r="1298" ht="12.75" hidden="1">
+    <row r="1298" ht="12.75">
       <c r="A1298" s="11" t="s">
         <v>1733</v>
       </c>
       <c r="B1298" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="C1298" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="D1298"/>
       <c r="G1298"/>
     </row>
     <row r="1299" ht="12.75" hidden="1">
       <c r="A1299" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1299" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="C1299" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1299" s="8"/>
       <c r="G1299" s="8"/>
     </row>
     <row r="1300" ht="12.75" hidden="1">
       <c r="A1300" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1300" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C1300" t="s">
         <v>1865</v>
-      </c>
-      <c r="C1300" t="s">
-        <v>1864</v>
       </c>
       <c r="D1300" s="1"/>
     </row>
     <row r="1301" ht="12.75" hidden="1">
       <c r="A1301" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1301" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="C1301" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1301"/>
       <c r="G1301"/>
     </row>
     <row r="1302" ht="12.75" hidden="1">
       <c r="A1302" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1302" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C1302" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1302" s="1"/>
     </row>
     <row r="1303" ht="12.75" hidden="1">
       <c r="A1303" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1303" s="1" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="C1303" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1303"/>
       <c r="G1303"/>
     </row>
     <row r="1304" ht="12.75" hidden="1">
       <c r="A1304" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1304" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="C1304" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1304" s="1"/>
     </row>
     <row r="1305" ht="12.75" hidden="1">
       <c r="A1305" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1305" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="C1305" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1305"/>
       <c r="G1305"/>
     </row>
     <row r="1306" ht="12.75" hidden="1">
       <c r="A1306" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1306" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C1306" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1306"/>
       <c r="G1306"/>
     </row>
     <row r="1307" ht="12.75" hidden="1">
       <c r="A1307" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1307" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="C1307" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1307" s="1"/>
     </row>
     <row r="1308" ht="12.75" hidden="1">
       <c r="A1308" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1308" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C1308" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1308"/>
       <c r="G1308"/>
     </row>
     <row r="1309" ht="12.75" hidden="1">
       <c r="A1309" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1309" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="C1309" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1309" s="1"/>
     </row>
     <row r="1310" ht="12.75" hidden="1">
       <c r="A1310" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1310" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C1310" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1310"/>
       <c r="G1310"/>
     </row>
     <row r="1311" ht="12.75" hidden="1">
       <c r="A1311" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1311" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="C1311" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1311" s="1"/>
     </row>
     <row r="1312" ht="12.75" hidden="1">
       <c r="A1312" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1312" s="8" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="C1312" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1312"/>
       <c r="G1312"/>
     </row>
     <row r="1313" ht="12.75" hidden="1">
       <c r="A1313" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1313" s="8" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="C1313" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1313" s="1"/>
     </row>
     <row r="1314" ht="12.75" hidden="1">
       <c r="A1314" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1314" s="8" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="C1314" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1314"/>
       <c r="G1314"/>
     </row>
     <row r="1315" ht="12.75" hidden="1">
       <c r="A1315" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1315" s="8"/>
       <c r="C1315" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1315" s="1"/>
     </row>
     <row r="1316" ht="12.75" hidden="1">
       <c r="A1316" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1316" s="8"/>
       <c r="C1316" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1316"/>
       <c r="G1316"/>
     </row>
     <row r="1317" ht="12.75" hidden="1">
       <c r="A1317" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1317" s="8"/>
       <c r="C1317" s="9" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D1317" s="1"/>
     </row>
     <row r="1318" ht="12.75" hidden="1">
       <c r="A1318" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1318" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="C1318" t="s">
         <v>1226</v>
@@ -24080,10 +24101,10 @@
     </row>
     <row r="1319" ht="12.75" hidden="1">
       <c r="A1319" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1319" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="C1319" t="s">
         <v>1226</v>
@@ -24093,10 +24114,10 @@
     </row>
     <row r="1320" ht="12.75" hidden="1">
       <c r="A1320" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1320" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C1320" s="9" t="s">
         <v>1226</v>
@@ -24105,10 +24126,10 @@
     </row>
     <row r="1321" ht="12.75" hidden="1">
       <c r="A1321" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1321" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C1321" s="9" t="s">
         <v>1226</v>
@@ -24118,10 +24139,10 @@
     </row>
     <row r="1322" ht="12.75" hidden="1">
       <c r="A1322" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1322" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="C1322" s="9" t="s">
         <v>1226</v>
@@ -24130,10 +24151,10 @@
     </row>
     <row r="1323" ht="12.75" hidden="1">
       <c r="A1323" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1323" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="C1323" s="9" t="s">
         <v>1226</v>
@@ -24143,10 +24164,10 @@
     </row>
     <row r="1324" ht="12.75" hidden="1">
       <c r="A1324" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1324" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="C1324" s="9" t="s">
         <v>1226</v>
@@ -24155,10 +24176,10 @@
     </row>
     <row r="1325" ht="12.75" hidden="1">
       <c r="A1325" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1325" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="C1325" s="9" t="s">
         <v>1226</v>
@@ -24168,10 +24189,10 @@
     </row>
     <row r="1326" ht="12.75" hidden="1">
       <c r="A1326" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1326" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="C1326" s="9" t="s">
         <v>1226</v>
@@ -24181,10 +24202,10 @@
     </row>
     <row r="1327" ht="12.75" hidden="1">
       <c r="A1327" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1327" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="C1327" s="9" t="s">
         <v>1226</v>
@@ -24193,23 +24214,23 @@
     </row>
     <row r="1328" ht="12.75" hidden="1">
       <c r="A1328" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1328" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="C1328" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D1328"/>
       <c r="G1328"/>
     </row>
     <row r="1329" ht="12.75" hidden="1">
       <c r="A1329" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1329" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="C1329" t="s">
         <v>1226</v>
@@ -24219,23 +24240,23 @@
     </row>
     <row r="1330" ht="12.75" hidden="1">
       <c r="A1330" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1330" s="8" t="s">
         <v>521</v>
       </c>
       <c r="C1330" s="8" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="D1330" s="1"/>
       <c r="G1330" s="1"/>
     </row>
     <row r="1331" ht="12.75" hidden="1">
       <c r="A1331" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1331" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="C1331" s="9" t="s">
         <v>1226</v>
@@ -24245,10 +24266,10 @@
     </row>
     <row r="1332" ht="12.75" hidden="1">
       <c r="A1332" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1332" s="8" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C1332" s="9" t="s">
         <v>514</v>
@@ -24258,10 +24279,10 @@
     </row>
     <row r="1333" ht="12.75" hidden="1">
       <c r="A1333" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1333" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C1333" s="9" t="s">
         <v>1226</v>
@@ -24270,22 +24291,22 @@
     </row>
     <row r="1334" ht="12.75" hidden="1">
       <c r="A1334" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1334" s="8" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="C1334" s="9" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D1334" s="1"/>
     </row>
     <row r="1335" ht="12.75" hidden="1">
       <c r="A1335" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1335" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C1335" s="9" t="s">
         <v>1226</v>
@@ -24295,23 +24316,23 @@
     </row>
     <row r="1336" ht="12.75" hidden="1">
       <c r="A1336" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1336" s="8" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="C1336" s="9" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="D1336" s="8"/>
       <c r="G1336" s="8"/>
     </row>
     <row r="1337" ht="12.75" hidden="1">
       <c r="A1337" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1337" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="C1337" s="9" t="s">
         <v>1226</v>
@@ -24320,22 +24341,22 @@
     </row>
     <row r="1338" ht="12.75" hidden="1">
       <c r="A1338" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1338" s="8" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="C1338" s="9" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="D1338" s="1"/>
     </row>
     <row r="1339" ht="12.75" hidden="1">
       <c r="A1339" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1339" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="C1339" s="9" t="s">
         <v>1226</v>
@@ -24345,23 +24366,23 @@
     </row>
     <row r="1340" ht="12.75" hidden="1">
       <c r="A1340" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1340" s="8" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="C1340" s="9" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="D1340" s="8"/>
       <c r="G1340" s="8"/>
     </row>
     <row r="1341" ht="12.75" hidden="1">
       <c r="A1341" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1341" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="C1341" s="9" t="s">
         <v>1226</v>
@@ -24370,22 +24391,22 @@
     </row>
     <row r="1342" ht="12.75" hidden="1">
       <c r="A1342" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1342" s="8" t="s">
         <v>1141</v>
       </c>
       <c r="C1342" s="9" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="D1342" s="1"/>
     </row>
     <row r="1343" ht="12.75" hidden="1">
       <c r="A1343" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1343" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="C1343" s="9" t="s">
         <v>1226</v>
@@ -24395,23 +24416,23 @@
     </row>
     <row r="1344" ht="12.75" hidden="1">
       <c r="A1344" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1344" s="8" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C1344" s="9" t="s">
         <v>1904</v>
-      </c>
-      <c r="C1344" s="9" t="s">
-        <v>1903</v>
       </c>
       <c r="D1344" s="8"/>
       <c r="G1344" s="8"/>
     </row>
     <row r="1345" ht="12.75" hidden="1">
       <c r="A1345" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1345" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="C1345" s="9" t="s">
         <v>1226</v>
@@ -24420,7 +24441,7 @@
     </row>
     <row r="1346" ht="12.75" hidden="1">
       <c r="A1346" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1346"/>
       <c r="C1346" s="9"/>
@@ -24428,10 +24449,10 @@
     </row>
     <row r="1347" ht="12.75" hidden="1">
       <c r="A1347" s="6" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B1347" t="s">
         <v>1891</v>
-      </c>
-      <c r="B1347" t="s">
-        <v>1890</v>
       </c>
       <c r="C1347" s="9" t="s">
         <v>1226</v>
@@ -24441,10 +24462,10 @@
     </row>
     <row r="1348" ht="12.75" hidden="1">
       <c r="A1348" s="7" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1348" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="C1348" t="s">
         <v>1531</v>
@@ -24453,111 +24474,111 @@
     </row>
     <row r="1349" ht="12.75" hidden="1">
       <c r="A1349" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1349" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="C1349" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1349"/>
       <c r="G1349"/>
     </row>
     <row r="1350" ht="12.75" hidden="1">
       <c r="A1350" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1350" s="8" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="C1350" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1350" s="1"/>
     </row>
     <row r="1351" ht="12.75" hidden="1">
       <c r="A1351" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1351" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C1351" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1351"/>
       <c r="G1351"/>
     </row>
     <row r="1352" ht="12.75" hidden="1">
       <c r="A1352" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1352" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="C1352" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1352" s="1"/>
     </row>
     <row r="1353" ht="12.75" hidden="1">
       <c r="A1353" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1353" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C1353" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1353"/>
       <c r="G1353"/>
     </row>
     <row r="1354" ht="12.75" hidden="1">
       <c r="A1354" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1354" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="C1354" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D1354"/>
       <c r="G1354"/>
     </row>
     <row r="1355" ht="12.75" hidden="1">
       <c r="A1355" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1355" s="8" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="C1355" s="8" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="D1355" s="1"/>
     </row>
     <row r="1356" ht="12.75" hidden="1">
       <c r="A1356" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1356" s="8" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C1356" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="D1356"/>
       <c r="G1356"/>
     </row>
     <row r="1357" ht="12.75" hidden="1">
       <c r="A1357" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1357" s="8" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="C1357" t="s">
         <v>1753</v>
@@ -24566,235 +24587,235 @@
     </row>
     <row r="1358" ht="12.75" hidden="1">
       <c r="A1358" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1358" s="8" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="C1358" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="D1358"/>
       <c r="G1358"/>
     </row>
     <row r="1359" ht="12.75" hidden="1">
       <c r="A1359" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1359" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C1359" t="s">
         <v>1920</v>
-      </c>
-      <c r="C1359" t="s">
-        <v>1919</v>
       </c>
       <c r="D1359" s="1"/>
     </row>
     <row r="1360" ht="12.75" hidden="1">
       <c r="A1360" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1360" s="8" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="C1360" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="D1360"/>
       <c r="G1360"/>
     </row>
     <row r="1361" ht="12.75" hidden="1">
       <c r="A1361" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1361" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C1361" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="D1361" s="1"/>
     </row>
     <row r="1362" ht="12.75" hidden="1">
       <c r="A1362" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1362" s="8" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="C1362" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="D1362"/>
       <c r="G1362"/>
     </row>
     <row r="1363" ht="12.75" hidden="1">
       <c r="A1363" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1363" s="8" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="C1363" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="D1363" s="1"/>
     </row>
     <row r="1364" ht="12.75" hidden="1">
       <c r="A1364" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1364" s="8" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="C1364" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="D1364"/>
       <c r="G1364"/>
     </row>
     <row r="1365" ht="12.75" hidden="1">
       <c r="A1365" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1365" s="8" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C1365" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="D1365" s="1"/>
     </row>
     <row r="1366" ht="12.75" hidden="1">
       <c r="A1366" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1366" s="8" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C1366" s="8" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="D1366"/>
       <c r="G1366"/>
     </row>
     <row r="1367" ht="12.75" hidden="1">
       <c r="A1367" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1367" s="8" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C1367" s="8" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="D1367" s="1"/>
     </row>
     <row r="1368" ht="12.75" hidden="1">
       <c r="A1368" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1368" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C1368" s="8" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="D1368"/>
       <c r="G1368"/>
     </row>
     <row r="1369" ht="12.75" hidden="1">
       <c r="A1369" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1369" s="8" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="C1369" s="8" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="D1369" s="1"/>
     </row>
     <row r="1370" ht="12.75" hidden="1">
       <c r="A1370" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1370" s="8" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C1370" s="8" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D1370"/>
       <c r="G1370"/>
     </row>
     <row r="1371" ht="12.75" hidden="1">
       <c r="A1371" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1371" s="8" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="C1371" s="8" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="D1371" s="1"/>
     </row>
     <row r="1372" ht="12.75" hidden="1">
       <c r="A1372" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1372" s="8" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C1372" s="8" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D1372"/>
       <c r="G1372"/>
     </row>
     <row r="1373" ht="12.75" hidden="1">
       <c r="A1373" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1373" s="8" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="C1373" s="8" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D1373" s="1"/>
     </row>
     <row r="1374" ht="12.75" hidden="1">
       <c r="A1374" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1374" s="8" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="C1374" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="D1374"/>
       <c r="G1374"/>
     </row>
     <row r="1375" ht="12.75" hidden="1">
       <c r="A1375" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1375" s="8" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="C1375" s="8" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="D1375" s="1"/>
     </row>
     <row r="1376" ht="12.75" hidden="1">
       <c r="A1376" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1376" s="8" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C1376" t="s">
         <v>1777</v>
@@ -24804,195 +24825,195 @@
     </row>
     <row r="1377" ht="12.75" hidden="1">
       <c r="A1377" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1377" s="8" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="C1377" s="8" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D1377" s="1"/>
     </row>
     <row r="1378" ht="12.75" hidden="1">
       <c r="A1378" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1378" s="8" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="C1378" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="D1378"/>
       <c r="G1378"/>
     </row>
     <row r="1379" ht="12.75" hidden="1">
       <c r="A1379" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1379" s="8" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="C1379" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D1379" s="1"/>
     </row>
     <row r="1380" ht="12.75" hidden="1">
       <c r="A1380" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1380" s="8" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="C1380" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D1380"/>
       <c r="G1380"/>
     </row>
     <row r="1381" ht="12.75" hidden="1">
       <c r="A1381" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1381" s="8" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="C1381" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="D1381" s="1"/>
     </row>
     <row r="1382" ht="12.75" hidden="1">
       <c r="A1382" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1382" s="8" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="C1382" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="D1382"/>
       <c r="G1382"/>
     </row>
     <row r="1383" ht="12.75" hidden="1">
       <c r="A1383" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1383" s="8" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="C1383" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D1383" s="1"/>
     </row>
     <row r="1384" ht="12.75" hidden="1">
       <c r="A1384" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1384" s="8" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="C1384" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D1384"/>
       <c r="G1384"/>
     </row>
     <row r="1385" ht="12.75" hidden="1">
       <c r="A1385" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1385" s="8" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C1385" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D1385" s="1"/>
     </row>
     <row r="1386" ht="12.75" hidden="1">
       <c r="A1386" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1386" s="8" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="C1386" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D1386"/>
       <c r="G1386"/>
     </row>
     <row r="1387" ht="12.75" hidden="1">
       <c r="A1387" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1387" s="8" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="C1387" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D1387" s="1"/>
     </row>
     <row r="1388" ht="12.75" hidden="1">
       <c r="A1388" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1388" s="8" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="C1388" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="D1388"/>
       <c r="G1388"/>
     </row>
     <row r="1389" ht="12.75" hidden="1">
       <c r="A1389" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1389" s="8" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="C1389" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D1389" s="1"/>
     </row>
     <row r="1390" ht="12.75" hidden="1">
       <c r="A1390" s="11" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1390" s="8" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="C1390" s="8" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="D1390"/>
       <c r="G1390"/>
     </row>
     <row r="1391" ht="12.75" hidden="1">
       <c r="A1391" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1391" s="8" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="C1391" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="D1391"/>
       <c r="G1391"/>
     </row>
     <row r="1392" ht="12.75" hidden="1">
       <c r="A1392" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1392" s="8" t="s">
         <v>1438</v>
@@ -25004,62 +25025,61 @@
     </row>
     <row r="1393" ht="12.75" hidden="1">
       <c r="A1393" s="6" t="s">
-        <v>1974</v>
-      </c>
-      <c r="B1393" s="8" t="s">
-        <v>1977</v>
-      </c>
-      <c r="C1393" s="8" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1393" s="14" t="s">
         <v>1978</v>
       </c>
-      <c r="D1393"/>
-      <c r="G1393"/>
+      <c r="C1393" s="15" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D1393" s="16"/>
     </row>
     <row r="1394" ht="12.75" hidden="1">
       <c r="A1394" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1394" s="8" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C1394" t="s">
-        <v>1979</v>
-      </c>
-      <c r="D1394" s="1"/>
+        <v>1980</v>
+      </c>
+      <c r="C1394" s="8" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D1394"/>
+      <c r="G1394"/>
     </row>
     <row r="1395" ht="12.75" hidden="1">
       <c r="A1395" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1395" s="8" t="s">
-        <v>1980</v>
+        <v>1440</v>
       </c>
       <c r="C1395" t="s">
-        <v>1981</v>
-      </c>
-      <c r="D1395"/>
-      <c r="G1395"/>
+        <v>1982</v>
+      </c>
+      <c r="D1395" s="1"/>
     </row>
     <row r="1396" ht="12.75" hidden="1">
       <c r="A1396" s="6" t="s">
-        <v>1974</v>
-      </c>
-      <c r="B1396" s="8" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C1396" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1396" s="14" t="s">
         <v>1983</v>
       </c>
-      <c r="D1396" s="1"/>
+      <c r="C1396" s="15" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D1396" s="16"/>
     </row>
     <row r="1397" ht="12.75" hidden="1">
       <c r="A1397" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1397" s="8" t="s">
         <v>1984</v>
       </c>
-      <c r="C1397" s="8" t="s">
+      <c r="C1397" t="s">
         <v>1985</v>
       </c>
       <c r="D1397"/>
@@ -25067,202 +25087,226 @@
     </row>
     <row r="1398" ht="12.75" hidden="1">
       <c r="A1398" s="6" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B1398" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1398" s="8" t="s">
         <v>1986</v>
       </c>
       <c r="C1398" t="s">
-        <v>1791</v>
+        <v>1987</v>
       </c>
       <c r="D1398" s="1"/>
     </row>
     <row r="1399" ht="12.75" hidden="1">
       <c r="A1399" s="6" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B1399" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C1399" t="s">
-        <v>1791</v>
+        <v>1975</v>
+      </c>
+      <c r="B1399" s="8" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C1399" s="8" t="s">
+        <v>1989</v>
       </c>
       <c r="D1399"/>
       <c r="G1399"/>
     </row>
     <row r="1400" ht="12.75" hidden="1">
       <c r="A1400" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1400" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="C1400" t="s">
-        <v>1791</v>
-      </c>
-      <c r="D1400"/>
-      <c r="G1400"/>
+        <v>1792</v>
+      </c>
+      <c r="D1400" s="1"/>
     </row>
     <row r="1401" ht="12.75" hidden="1">
       <c r="A1401" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1401" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="C1401" t="s">
-        <v>1791</v>
-      </c>
-      <c r="D1401" s="1"/>
+        <v>1792</v>
+      </c>
+      <c r="D1401"/>
+      <c r="G1401"/>
     </row>
     <row r="1402" ht="12.75" hidden="1">
       <c r="A1402" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1402" t="s">
-        <v>1990</v>
-      </c>
-      <c r="C1402" s="9" t="s">
-        <v>1791</v>
+        <v>1992</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>1792</v>
       </c>
       <c r="D1402"/>
       <c r="G1402"/>
     </row>
     <row r="1403" ht="12.75" hidden="1">
-      <c r="A1403" s="7" t="s">
-        <v>1598</v>
-      </c>
-      <c r="B1403" s="9" t="s">
-        <v>1819</v>
-      </c>
-      <c r="C1403" s="9" t="s">
-        <v>423</v>
+      <c r="A1403" s="6" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>1792</v>
       </c>
       <c r="D1403" s="1"/>
     </row>
     <row r="1404" ht="12.75" hidden="1">
-      <c r="A1404" s="7" t="s">
-        <v>1420</v>
+      <c r="A1404" s="6" t="s">
+        <v>1907</v>
       </c>
       <c r="B1404" t="s">
-        <v>1991</v>
-      </c>
-      <c r="C1404" t="s">
-        <v>1992</v>
+        <v>1994</v>
+      </c>
+      <c r="C1404" s="9" t="s">
+        <v>1792</v>
       </c>
       <c r="D1404"/>
       <c r="G1404"/>
     </row>
     <row r="1405" ht="12.75" hidden="1">
       <c r="A1405" s="7" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B1405" s="9" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1405" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1405" s="1"/>
+    </row>
+    <row r="1406" ht="12.75" hidden="1">
+      <c r="A1406" s="7" t="s">
         <v>1420</v>
       </c>
-      <c r="B1405" t="s">
-        <v>1993</v>
-      </c>
-      <c r="C1405" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D1405" s="1"/>
-    </row>
-    <row r="1406" ht="12.75" hidden="1">
-      <c r="A1406" s="6" t="s">
+      <c r="B1406" t="s">
         <v>1995</v>
       </c>
-      <c r="B1406" t="s">
+      <c r="C1406" t="s">
         <v>1996</v>
-      </c>
-      <c r="C1406" t="s">
-        <v>1997</v>
       </c>
       <c r="D1406"/>
       <c r="G1406"/>
     </row>
     <row r="1407" ht="12.75" hidden="1">
-      <c r="A1407" s="6" t="s">
-        <v>1995</v>
+      <c r="A1407" s="7" t="s">
+        <v>1420</v>
       </c>
       <c r="B1407" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C1407" t="s">
         <v>1998</v>
-      </c>
-      <c r="C1407" t="s">
-        <v>1999</v>
       </c>
       <c r="D1407" s="1"/>
     </row>
     <row r="1408" ht="12.75" hidden="1">
       <c r="A1408" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1408" t="s">
         <v>2000</v>
       </c>
-      <c r="B1408" t="s">
+      <c r="C1408" t="s">
         <v>2001</v>
       </c>
-      <c r="C1408" s="8" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D1408" s="1"/>
-      <c r="G1408" s="1"/>
+      <c r="D1408"/>
+      <c r="G1408"/>
     </row>
     <row r="1409" ht="12.75" hidden="1">
       <c r="A1409" s="6" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B1409" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C1409" t="s">
         <v>2003</v>
       </c>
-      <c r="C1409" t="s">
-        <v>2004</v>
-      </c>
-      <c r="D1409"/>
-      <c r="G1409"/>
+      <c r="D1409" s="1"/>
     </row>
     <row r="1410" ht="12.75" hidden="1">
       <c r="A1410" s="6" t="s">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="B1410" t="s">
         <v>2005</v>
       </c>
-      <c r="C1410" t="s">
+      <c r="C1410" s="8" t="s">
         <v>2006</v>
       </c>
       <c r="D1410" s="1"/>
       <c r="G1410" s="1"/>
     </row>
     <row r="1411" ht="12.75" hidden="1">
-      <c r="A1411" s="6"/>
+      <c r="A1411" s="6" t="s">
+        <v>2004</v>
+      </c>
       <c r="B1411" t="s">
-        <v>1471</v>
+        <v>2007</v>
       </c>
       <c r="C1411" t="s">
-        <v>1472</v>
+        <v>2008</v>
       </c>
       <c r="D1411"/>
       <c r="G1411"/>
     </row>
-    <row r="1412" ht="12.75">
-      <c r="A1412" s="6"/>
-      <c r="B1412"/>
-      <c r="C1412"/>
+    <row r="1412" ht="12.75" hidden="1">
+      <c r="A1412" s="6" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>2010</v>
+      </c>
       <c r="D1412" s="1"/>
-    </row>
-    <row r="1413" ht="12.75">
+      <c r="G1412" s="1"/>
+    </row>
+    <row r="1413" ht="12.75" hidden="1">
       <c r="A1413" s="6"/>
-      <c r="B1413"/>
-      <c r="C1413"/>
+      <c r="B1413" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>1472</v>
+      </c>
       <c r="D1413"/>
       <c r="G1413"/>
     </row>
-    <row r="1414" ht="12.75">
-      <c r="A1414" s="6"/>
-      <c r="B1414"/>
-      <c r="C1414"/>
+    <row r="1414" ht="12.75" hidden="1">
+      <c r="A1414" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C1414" s="9" t="s">
+        <v>1977</v>
+      </c>
       <c r="D1414" s="1"/>
     </row>
-    <row r="1415" ht="12.75">
-      <c r="A1415" s="6"/>
-      <c r="B1415"/>
-      <c r="C1415"/>
+    <row r="1415" ht="12.75" hidden="1">
+      <c r="A1415" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>1979</v>
+      </c>
       <c r="D1415"/>
       <c r="G1415"/>
     </row>
@@ -25905,11 +25949,16 @@
     </row>
     <row r="1514" ht="12.75">
       <c r="A1514" s="6"/>
+      <c r="B1514"/>
+      <c r="C1514"/>
       <c r="D1514" s="1"/>
     </row>
     <row r="1515" ht="12.75">
       <c r="A1515" s="6"/>
-      <c r="D1515" s="1"/>
+      <c r="B1515"/>
+      <c r="C1515"/>
+      <c r="D1515"/>
+      <c r="G1515"/>
     </row>
     <row r="1516" ht="12.75">
       <c r="A1516" s="6"/>
@@ -25997,9 +26046,11 @@
     </row>
     <row r="1537" ht="12.75">
       <c r="A1537" s="6"/>
+      <c r="D1537" s="1"/>
     </row>
     <row r="1538" ht="12.75">
       <c r="A1538" s="6"/>
+      <c r="D1538" s="1"/>
     </row>
     <row r="1539" ht="12.75">
       <c r="A1539" s="6"/>
@@ -26007,18 +26058,11 @@
     <row r="1540" ht="12.75">
       <c r="A1540" s="6"/>
     </row>
-    <row r="1811" ht="12.75">
-      <c r="A1811" s="6"/>
-      <c r="B1811"/>
-      <c r="C1811"/>
-      <c r="D1811" s="1"/>
-    </row>
-    <row r="1812" ht="12.75">
-      <c r="A1812" s="6"/>
-      <c r="B1812"/>
-      <c r="C1812"/>
-      <c r="D1812"/>
-      <c r="G1812"/>
+    <row r="1541" ht="12.75">
+      <c r="A1541" s="6"/>
+    </row>
+    <row r="1542" ht="12.75">
+      <c r="A1542" s="6"/>
     </row>
     <row r="1813" ht="12.75">
       <c r="A1813" s="6"/>
@@ -26072,18 +26116,23 @@
       <c r="D1820"/>
       <c r="G1820"/>
     </row>
-    <row r="1834" ht="12.75">
-      <c r="D1834" s="1"/>
-    </row>
-    <row r="1835" ht="12.75">
-      <c r="D1835" s="1"/>
+    <row r="1821" ht="12.75">
+      <c r="A1821" s="6"/>
+      <c r="B1821"/>
+      <c r="C1821"/>
+      <c r="D1821" s="1"/>
+    </row>
+    <row r="1822" ht="12.75">
+      <c r="A1822" s="6"/>
+      <c r="B1822"/>
+      <c r="C1822"/>
+      <c r="D1822"/>
+      <c r="G1822"/>
     </row>
     <row r="1836" ht="12.75">
-      <c r="A1836" s="6"/>
       <c r="D1836" s="1"/>
     </row>
     <row r="1837" ht="12.75">
-      <c r="A1837" s="6"/>
       <c r="D1837" s="1"/>
     </row>
     <row r="1838" ht="12.75">
@@ -26100,26 +26149,28 @@
     </row>
     <row r="1841" ht="12.75">
       <c r="A1841" s="6"/>
-      <c r="B1841"/>
-      <c r="C1841"/>
       <c r="D1841" s="1"/>
     </row>
     <row r="1842" ht="12.75">
       <c r="A1842" s="6"/>
-      <c r="B1842"/>
-      <c r="C1842"/>
-      <c r="D1842"/>
-      <c r="G1842"/>
+      <c r="D1842" s="1"/>
     </row>
     <row r="1843" ht="12.75">
       <c r="A1843" s="6"/>
+      <c r="B1843"/>
+      <c r="C1843"/>
       <c r="D1843" s="1"/>
     </row>
     <row r="1844" ht="12.75">
       <c r="A1844" s="6"/>
+      <c r="B1844"/>
+      <c r="C1844"/>
+      <c r="D1844"/>
+      <c r="G1844"/>
     </row>
     <row r="1845" ht="12.75">
       <c r="A1845" s="6"/>
+      <c r="D1845" s="1"/>
     </row>
     <row r="1846" ht="12.75">
       <c r="A1846" s="6"/>
@@ -26162,31 +26213,24 @@
     </row>
     <row r="1859" ht="12.75">
       <c r="A1859" s="6"/>
-      <c r="B1859"/>
-      <c r="C1859"/>
-      <c r="D1859" s="1"/>
     </row>
     <row r="1860" ht="12.75">
       <c r="A1860" s="6"/>
     </row>
     <row r="1861" ht="12.75">
       <c r="A1861" s="6"/>
+      <c r="B1861"/>
+      <c r="C1861"/>
+      <c r="D1861" s="1"/>
     </row>
     <row r="1862" ht="12.75">
       <c r="A1862" s="6"/>
     </row>
     <row r="1863" ht="12.75">
       <c r="A1863" s="6"/>
-      <c r="B1863"/>
-      <c r="C1863"/>
-      <c r="D1863" s="1"/>
     </row>
     <row r="1864" ht="12.75">
       <c r="A1864" s="6"/>
-      <c r="B1864"/>
-      <c r="C1864"/>
-      <c r="D1864"/>
-      <c r="G1864"/>
     </row>
     <row r="1865" ht="12.75">
       <c r="A1865" s="6"/>
@@ -26216,9 +26260,16 @@
     </row>
     <row r="1869" ht="12.75">
       <c r="A1869" s="6"/>
+      <c r="B1869"/>
+      <c r="C1869"/>
+      <c r="D1869" s="1"/>
     </row>
     <row r="1870" ht="12.75">
       <c r="A1870" s="6"/>
+      <c r="B1870"/>
+      <c r="C1870"/>
+      <c r="D1870"/>
+      <c r="G1870"/>
     </row>
     <row r="1871" ht="12.75">
       <c r="A1871" s="6"/>
@@ -26234,16 +26285,9 @@
     </row>
     <row r="1875" ht="12.75">
       <c r="A1875" s="6"/>
-      <c r="B1875"/>
-      <c r="C1875"/>
-      <c r="D1875" s="1"/>
     </row>
     <row r="1876" ht="12.75">
       <c r="A1876" s="6"/>
-      <c r="B1876"/>
-      <c r="C1876"/>
-      <c r="D1876"/>
-      <c r="G1876"/>
     </row>
     <row r="1877" ht="12.75">
       <c r="A1877" s="6"/>
@@ -26368,11 +26412,18 @@
       <c r="C1895"/>
       <c r="D1895" s="1"/>
     </row>
-    <row r="1898" ht="12.75">
-      <c r="D1898" s="1"/>
-    </row>
-    <row r="1899" ht="12.75">
-      <c r="D1899" s="1"/>
+    <row r="1896" ht="12.75">
+      <c r="A1896" s="6"/>
+      <c r="B1896"/>
+      <c r="C1896"/>
+      <c r="D1896"/>
+      <c r="G1896"/>
+    </row>
+    <row r="1897" ht="12.75">
+      <c r="A1897" s="6"/>
+      <c r="B1897"/>
+      <c r="C1897"/>
+      <c r="D1897" s="1"/>
     </row>
     <row r="1900" ht="12.75">
       <c r="D1900" s="1"/>
@@ -26431,11 +26482,11 @@
     <row r="1918" ht="12.75">
       <c r="D1918" s="1"/>
     </row>
-    <row r="1942" ht="12.75">
-      <c r="A1942" s="6"/>
-    </row>
-    <row r="1943" ht="12.75">
-      <c r="A1943" s="6"/>
+    <row r="1919" ht="12.75">
+      <c r="D1919" s="1"/>
+    </row>
+    <row r="1920" ht="12.75">
+      <c r="D1920" s="1"/>
     </row>
     <row r="1944" ht="12.75">
       <c r="A1944" s="6"/>
@@ -26557,18 +26608,11 @@
     <row r="1983" ht="12.75">
       <c r="A1983" s="6"/>
     </row>
-    <row r="2076" ht="12.75">
-      <c r="A2076" s="6"/>
-      <c r="B2076"/>
-      <c r="C2076"/>
-      <c r="D2076"/>
-      <c r="G2076"/>
-    </row>
-    <row r="2077" ht="12.75">
-      <c r="A2077" s="6"/>
-      <c r="B2077"/>
-      <c r="C2077"/>
-      <c r="D2077" s="1"/>
+    <row r="1984" ht="12.75">
+      <c r="A1984" s="6"/>
+    </row>
+    <row r="1985" ht="12.75">
+      <c r="A1985" s="6"/>
     </row>
     <row r="2078" ht="12.75">
       <c r="A2078" s="6"/>
@@ -26616,11 +26660,18 @@
       <c r="D2084"/>
       <c r="G2084"/>
     </row>
-    <row r="2099" ht="12.75">
-      <c r="D2099" s="1"/>
-    </row>
-    <row r="2100" ht="12.75">
-      <c r="D2100" s="1"/>
+    <row r="2085" ht="12.75">
+      <c r="A2085" s="6"/>
+      <c r="B2085"/>
+      <c r="C2085"/>
+      <c r="D2085" s="1"/>
+    </row>
+    <row r="2086" ht="12.75">
+      <c r="A2086" s="6"/>
+      <c r="B2086"/>
+      <c r="C2086"/>
+      <c r="D2086"/>
+      <c r="G2086"/>
     </row>
     <row r="2101" ht="12.75">
       <c r="D2101" s="1"/>
@@ -26641,14 +26692,14 @@
       <c r="D2106" s="1"/>
     </row>
     <row r="2107" ht="12.75">
-      <c r="A2107" s="6"/>
       <c r="D2107" s="1"/>
     </row>
     <row r="2108" ht="12.75">
-      <c r="A2108" s="6"/>
+      <c r="D2108" s="1"/>
     </row>
     <row r="2109" ht="12.75">
       <c r="A2109" s="6"/>
+      <c r="D2109" s="1"/>
     </row>
     <row r="2110" ht="12.75">
       <c r="A2110" s="6"/>
@@ -26689,11 +26740,11 @@
     <row r="2122" ht="12.75">
       <c r="A2122" s="6"/>
     </row>
-    <row r="2393" ht="12.75">
-      <c r="A2393" s="6"/>
-    </row>
-    <row r="2394" ht="12.75">
-      <c r="A2394" s="6"/>
+    <row r="2123" ht="12.75">
+      <c r="A2123" s="6"/>
+    </row>
+    <row r="2124" ht="12.75">
+      <c r="A2124" s="6"/>
     </row>
     <row r="2395" ht="12.75">
       <c r="A2395" s="6"/>
@@ -26707,11 +26758,11 @@
     <row r="2398" ht="12.75">
       <c r="A2398" s="6"/>
     </row>
-    <row r="2451" ht="12.75">
-      <c r="A2451" s="6"/>
-    </row>
-    <row r="2452" ht="12.75">
-      <c r="A2452" s="6"/>
+    <row r="2399" ht="12.75">
+      <c r="A2399" s="6"/>
+    </row>
+    <row r="2400" ht="12.75">
+      <c r="A2400" s="6"/>
     </row>
     <row r="2453" ht="12.75">
       <c r="A2453" s="6"/>
@@ -26737,11 +26788,11 @@
     <row r="2460" ht="12.75">
       <c r="A2460" s="6"/>
     </row>
-    <row r="2588" ht="12.75">
-      <c r="A2588" s="6"/>
-    </row>
-    <row r="2589" ht="12.75">
-      <c r="A2589" s="6"/>
+    <row r="2461" ht="12.75">
+      <c r="A2461" s="6"/>
+    </row>
+    <row r="2462" ht="12.75">
+      <c r="A2462" s="6"/>
     </row>
     <row r="2590" ht="12.75">
       <c r="A2590" s="6"/>
@@ -26830,29 +26881,25 @@
     <row r="2618" ht="12.75">
       <c r="A2618" s="6"/>
     </row>
+    <row r="2619" ht="12.75">
+      <c r="A2619" s="6"/>
+    </row>
     <row r="2620" ht="12.75">
       <c r="A2620" s="6"/>
     </row>
-    <row r="2621" ht="12.75">
-      <c r="A2621" s="6"/>
-      <c r="B2621"/>
-      <c r="C2621"/>
-    </row>
     <row r="2622" ht="12.75">
       <c r="A2622" s="6"/>
     </row>
     <row r="2623" ht="12.75">
       <c r="A2623" s="6"/>
+      <c r="B2623"/>
+      <c r="C2623"/>
     </row>
     <row r="2624" ht="12.75">
       <c r="A2624" s="6"/>
-      <c r="B2624"/>
-      <c r="C2624"/>
     </row>
     <row r="2625" ht="12.75">
       <c r="A2625" s="6"/>
-      <c r="B2625"/>
-      <c r="C2625"/>
     </row>
     <row r="2626" ht="12.75">
       <c r="A2626" s="6"/>
@@ -26902,10 +26949,12 @@
     <row r="2635" ht="12.75">
       <c r="A2635" s="6"/>
       <c r="B2635"/>
+      <c r="C2635"/>
     </row>
     <row r="2636" ht="12.75">
       <c r="A2636" s="6"/>
       <c r="B2636"/>
+      <c r="C2636"/>
     </row>
     <row r="2637" ht="12.75">
       <c r="A2637" s="6"/>
@@ -26914,23 +26963,31 @@
     <row r="2638" ht="12.75">
       <c r="A2638" s="6"/>
       <c r="B2638"/>
-      <c r="C2638"/>
     </row>
     <row r="2639" ht="12.75">
-      <c r="A2639" s="2"/>
-      <c r="C2639" s="14"/>
+      <c r="A2639" s="6"/>
+      <c r="B2639"/>
     </row>
     <row r="2640" ht="12.75">
       <c r="A2640" s="6"/>
+      <c r="B2640"/>
+      <c r="C2640"/>
     </row>
     <row r="2641" ht="12.75">
-      <c r="A2641" s="7"/>
+      <c r="A2641" s="2"/>
+      <c r="C2641" s="17"/>
+    </row>
+    <row r="2642" ht="12.75">
+      <c r="A2642" s="6"/>
+    </row>
+    <row r="2643" ht="12.75">
+      <c r="A2643" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1411">
+  <autoFilter ref="A1:C1415">
     <filterColumn colId="0">
       <filters>
-        <filter val="(Genre) Brazilian CityPop"/>
+        <filter val="(Genre) CityPop"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/playlists.xlsx
+++ b/playlists.xlsx
@@ -9,8 +9,8 @@
     <sheet name="playlists" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1413</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1415</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1443</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="2039">
   <si>
     <t xml:space="preserve">Playlist Name</t>
   </si>
@@ -6059,6 +6059,84 @@
   </si>
   <si>
     <t xml:space="preserve">Remind Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until we Rich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(This is ...) Morrissey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Frank</t>
+  </si>
+  <si>
+    <t>Morrissey</t>
+  </si>
+  <si>
+    <t>Suedhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I dont Mind if you forget me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piccadilly Palare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interesting Drug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November Spawned a Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Never Marry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Such a Little Thing Makes Such a Big Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouija Board, Ouija Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hairdresser on Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyday is Like Sunday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifeguard on Duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please Help the Cause Gainst the Loneliness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sing Your Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mute Witness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asian Rut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pashernate Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">East West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driving your girlfriend home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is a place in hell for me and my friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The End of the Family Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glamorous Glue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certain People i Know</t>
   </si>
 </sst>
 </file>
@@ -6134,7 +6212,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6173,9 +6251,10 @@
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -22740,7 +22819,7 @@
       <c r="D1208"/>
       <c r="G1208"/>
     </row>
-    <row r="1209" ht="12.75">
+    <row r="1209" ht="12.75" hidden="1">
       <c r="A1209" s="6" t="s">
         <v>1733</v>
       </c>
@@ -22752,7 +22831,7 @@
       </c>
       <c r="D1209" s="1"/>
     </row>
-    <row r="1210" ht="12.75">
+    <row r="1210" ht="12.75" hidden="1">
       <c r="A1210" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22765,7 +22844,7 @@
       <c r="D1210" s="1"/>
       <c r="G1210" s="1"/>
     </row>
-    <row r="1211" ht="12.75">
+    <row r="1211" ht="12.75" hidden="1">
       <c r="A1211" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22777,7 +22856,7 @@
       </c>
       <c r="D1211" s="1"/>
     </row>
-    <row r="1212" ht="12.75">
+    <row r="1212" ht="12.75" hidden="1">
       <c r="A1212" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22790,7 +22869,7 @@
       <c r="D1212"/>
       <c r="G1212"/>
     </row>
-    <row r="1213" ht="12.75">
+    <row r="1213" ht="12.75" hidden="1">
       <c r="A1213" s="6" t="s">
         <v>1733</v>
       </c>
@@ -22802,7 +22881,7 @@
       </c>
       <c r="D1213" s="1"/>
     </row>
-    <row r="1214" ht="12.75">
+    <row r="1214" ht="12.75" hidden="1">
       <c r="A1214" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22815,7 +22894,7 @@
       <c r="D1214"/>
       <c r="G1214"/>
     </row>
-    <row r="1215" ht="12.75">
+    <row r="1215" ht="12.75" hidden="1">
       <c r="A1215" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22827,7 +22906,7 @@
       </c>
       <c r="D1215" s="1"/>
     </row>
-    <row r="1216" ht="12.75">
+    <row r="1216" ht="12.75" hidden="1">
       <c r="A1216" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22840,7 +22919,7 @@
       <c r="D1216"/>
       <c r="G1216"/>
     </row>
-    <row r="1217" ht="12.75">
+    <row r="1217" ht="12.75" hidden="1">
       <c r="A1217" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22852,7 +22931,7 @@
       </c>
       <c r="D1217" s="1"/>
     </row>
-    <row r="1218" ht="12.75">
+    <row r="1218" ht="12.75" hidden="1">
       <c r="A1218" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22865,7 +22944,7 @@
       <c r="D1218"/>
       <c r="G1218"/>
     </row>
-    <row r="1219" ht="12.75">
+    <row r="1219" ht="12.75" hidden="1">
       <c r="A1219" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22877,7 +22956,7 @@
       </c>
       <c r="D1219" s="1"/>
     </row>
-    <row r="1220" ht="12.75">
+    <row r="1220" ht="12.75" hidden="1">
       <c r="A1220" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22890,7 +22969,7 @@
       <c r="D1220"/>
       <c r="G1220"/>
     </row>
-    <row r="1221" ht="12.75">
+    <row r="1221" ht="12.75" hidden="1">
       <c r="A1221" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22902,7 +22981,7 @@
       </c>
       <c r="D1221" s="1"/>
     </row>
-    <row r="1222" ht="12.75">
+    <row r="1222" ht="12.75" hidden="1">
       <c r="A1222" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22915,7 +22994,7 @@
       <c r="D1222"/>
       <c r="G1222"/>
     </row>
-    <row r="1223" ht="12.75">
+    <row r="1223" ht="12.75" hidden="1">
       <c r="A1223" s="2" t="s">
         <v>1733</v>
       </c>
@@ -22927,7 +23006,7 @@
       </c>
       <c r="D1223" s="1"/>
     </row>
-    <row r="1224" ht="12.75">
+    <row r="1224" ht="12.75" hidden="1">
       <c r="A1224" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22940,7 +23019,7 @@
       <c r="D1224"/>
       <c r="G1224"/>
     </row>
-    <row r="1225" ht="12.75">
+    <row r="1225" ht="12.75" hidden="1">
       <c r="A1225" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22952,7 +23031,7 @@
       </c>
       <c r="D1225" s="1"/>
     </row>
-    <row r="1226" ht="12.75">
+    <row r="1226" ht="12.75" hidden="1">
       <c r="A1226" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22965,7 +23044,7 @@
       <c r="D1226"/>
       <c r="G1226"/>
     </row>
-    <row r="1227" ht="12.75">
+    <row r="1227" ht="12.75" hidden="1">
       <c r="A1227" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22977,7 +23056,7 @@
       </c>
       <c r="D1227" s="1"/>
     </row>
-    <row r="1228" ht="12.75">
+    <row r="1228" ht="12.75" hidden="1">
       <c r="A1228" s="11" t="s">
         <v>1733</v>
       </c>
@@ -22990,7 +23069,7 @@
       <c r="D1228"/>
       <c r="G1228"/>
     </row>
-    <row r="1229" ht="12.75">
+    <row r="1229" ht="12.75" hidden="1">
       <c r="A1229" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23002,7 +23081,7 @@
       </c>
       <c r="D1229" s="1"/>
     </row>
-    <row r="1230" ht="12.75">
+    <row r="1230" ht="12.75" hidden="1">
       <c r="A1230" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23015,7 +23094,7 @@
       <c r="D1230"/>
       <c r="G1230"/>
     </row>
-    <row r="1231" ht="12.75">
+    <row r="1231" ht="12.75" hidden="1">
       <c r="A1231" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23027,7 +23106,7 @@
       </c>
       <c r="D1231" s="1"/>
     </row>
-    <row r="1232" ht="12.75">
+    <row r="1232" ht="12.75" hidden="1">
       <c r="A1232" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23040,7 +23119,7 @@
       <c r="D1232"/>
       <c r="G1232"/>
     </row>
-    <row r="1233" ht="12.75">
+    <row r="1233" ht="12.75" hidden="1">
       <c r="A1233" s="11" t="s">
         <v>1778</v>
       </c>
@@ -23052,7 +23131,7 @@
       </c>
       <c r="D1233" s="1"/>
     </row>
-    <row r="1234" ht="12.75">
+    <row r="1234" ht="12.75" hidden="1">
       <c r="A1234" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23065,7 +23144,7 @@
       <c r="D1234"/>
       <c r="G1234"/>
     </row>
-    <row r="1235" ht="12.75">
+    <row r="1235" ht="12.75" hidden="1">
       <c r="A1235" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23077,7 +23156,7 @@
       </c>
       <c r="D1235" s="1"/>
     </row>
-    <row r="1236" ht="12.75">
+    <row r="1236" ht="12.75" hidden="1">
       <c r="A1236" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23090,7 +23169,7 @@
       <c r="D1236"/>
       <c r="G1236"/>
     </row>
-    <row r="1237" ht="12.75">
+    <row r="1237" ht="12.75" hidden="1">
       <c r="A1237" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23102,7 +23181,7 @@
       </c>
       <c r="D1237" s="1"/>
     </row>
-    <row r="1238" ht="12.75">
+    <row r="1238" ht="12.75" hidden="1">
       <c r="A1238" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23115,7 +23194,7 @@
       <c r="D1238"/>
       <c r="G1238"/>
     </row>
-    <row r="1239" ht="12.75">
+    <row r="1239" ht="12.75" hidden="1">
       <c r="A1239" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23127,7 +23206,7 @@
       </c>
       <c r="D1239" s="1"/>
     </row>
-    <row r="1240" ht="12.75">
+    <row r="1240" ht="12.75" hidden="1">
       <c r="A1240" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23140,7 +23219,7 @@
       <c r="D1240"/>
       <c r="G1240"/>
     </row>
-    <row r="1241" ht="12.75">
+    <row r="1241" ht="12.75" hidden="1">
       <c r="A1241" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23152,7 +23231,7 @@
       </c>
       <c r="D1241" s="1"/>
     </row>
-    <row r="1242" ht="12.75">
+    <row r="1242" ht="12.75" hidden="1">
       <c r="A1242" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23165,7 +23244,7 @@
       <c r="D1242"/>
       <c r="G1242"/>
     </row>
-    <row r="1243" ht="12.75">
+    <row r="1243" ht="12.75" hidden="1">
       <c r="A1243" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23177,7 +23256,7 @@
       </c>
       <c r="D1243" s="1"/>
     </row>
-    <row r="1244" ht="12.75">
+    <row r="1244" ht="12.75" hidden="1">
       <c r="A1244" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23189,7 +23268,7 @@
       </c>
       <c r="D1244" s="1"/>
     </row>
-    <row r="1245" ht="12.75">
+    <row r="1245" ht="12.75" hidden="1">
       <c r="A1245" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23202,7 +23281,7 @@
       <c r="D1245"/>
       <c r="G1245"/>
     </row>
-    <row r="1246" ht="12.75">
+    <row r="1246" ht="12.75" hidden="1">
       <c r="A1246" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23214,7 +23293,7 @@
       </c>
       <c r="D1246" s="1"/>
     </row>
-    <row r="1247" ht="12.75">
+    <row r="1247" ht="12.75" hidden="1">
       <c r="A1247" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23227,7 +23306,7 @@
       <c r="D1247"/>
       <c r="G1247"/>
     </row>
-    <row r="1248" ht="12.75">
+    <row r="1248" ht="12.75" hidden="1">
       <c r="A1248" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23239,7 +23318,7 @@
       </c>
       <c r="D1248" s="1"/>
     </row>
-    <row r="1249" ht="12.75">
+    <row r="1249" ht="12.75" hidden="1">
       <c r="A1249" s="7" t="s">
         <v>1733</v>
       </c>
@@ -23252,7 +23331,7 @@
       <c r="D1249"/>
       <c r="G1249"/>
     </row>
-    <row r="1250" ht="12.75">
+    <row r="1250" ht="12.75" hidden="1">
       <c r="A1250" s="7" t="s">
         <v>1733</v>
       </c>
@@ -23264,7 +23343,7 @@
       </c>
       <c r="D1250" s="1"/>
     </row>
-    <row r="1251" ht="12.75">
+    <row r="1251" ht="12.75" hidden="1">
       <c r="A1251" s="7" t="s">
         <v>1733</v>
       </c>
@@ -23277,7 +23356,7 @@
       <c r="D1251"/>
       <c r="G1251"/>
     </row>
-    <row r="1252" ht="12.75">
+    <row r="1252" ht="12.75" hidden="1">
       <c r="A1252" s="7" t="s">
         <v>1733</v>
       </c>
@@ -23289,7 +23368,7 @@
       </c>
       <c r="D1252" s="1"/>
     </row>
-    <row r="1253" ht="12.75">
+    <row r="1253" ht="12.75" hidden="1">
       <c r="A1253" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23302,7 +23381,7 @@
       <c r="D1253"/>
       <c r="G1253"/>
     </row>
-    <row r="1254" ht="12.75">
+    <row r="1254" ht="12.75" hidden="1">
       <c r="A1254" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23314,7 +23393,7 @@
       </c>
       <c r="D1254" s="1"/>
     </row>
-    <row r="1255" ht="12.75">
+    <row r="1255" ht="12.75" hidden="1">
       <c r="A1255" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23327,7 +23406,7 @@
       <c r="D1255"/>
       <c r="G1255"/>
     </row>
-    <row r="1256" ht="12.75">
+    <row r="1256" ht="12.75" hidden="1">
       <c r="A1256" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23339,7 +23418,7 @@
       </c>
       <c r="D1256" s="1"/>
     </row>
-    <row r="1257" ht="12.75">
+    <row r="1257" ht="12.75" hidden="1">
       <c r="A1257" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23804,7 +23883,7 @@
       <c r="D1294"/>
       <c r="G1294"/>
     </row>
-    <row r="1295" ht="12.75">
+    <row r="1295" ht="12.75" hidden="1">
       <c r="A1295" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23816,7 +23895,7 @@
       </c>
       <c r="D1295" s="1"/>
     </row>
-    <row r="1296" ht="12.75">
+    <row r="1296" ht="12.75" hidden="1">
       <c r="A1296" s="11" t="s">
         <v>1733</v>
       </c>
@@ -23841,7 +23920,7 @@
       </c>
       <c r="D1297" s="1"/>
     </row>
-    <row r="1298" ht="12.75">
+    <row r="1298" ht="12.75" hidden="1">
       <c r="A1298" s="11" t="s">
         <v>1733</v>
       </c>
@@ -25027,13 +25106,13 @@
       <c r="A1393" s="6" t="s">
         <v>1975</v>
       </c>
-      <c r="B1393" s="14" t="s">
+      <c r="B1393" s="8" t="s">
         <v>1978</v>
       </c>
-      <c r="C1393" s="15" t="s">
+      <c r="C1393" s="8" t="s">
         <v>1979</v>
       </c>
-      <c r="D1393" s="16"/>
+      <c r="D1393" s="1"/>
     </row>
     <row r="1394" ht="12.75" hidden="1">
       <c r="A1394" s="6" t="s">
@@ -25064,13 +25143,13 @@
       <c r="A1396" s="6" t="s">
         <v>1975</v>
       </c>
-      <c r="B1396" s="14" t="s">
+      <c r="B1396" s="8" t="s">
         <v>1983</v>
       </c>
-      <c r="C1396" s="15" t="s">
+      <c r="C1396" s="8" t="s">
         <v>1979</v>
       </c>
-      <c r="D1396" s="16"/>
+      <c r="D1396" s="1"/>
     </row>
     <row r="1397" ht="12.75" hidden="1">
       <c r="A1397" s="6" t="s">
@@ -25310,185 +25389,345 @@
       <c r="D1415"/>
       <c r="G1415"/>
     </row>
-    <row r="1416" ht="12.75">
-      <c r="A1416" s="6"/>
-      <c r="B1416"/>
-      <c r="C1416"/>
+    <row r="1416" ht="12.75" hidden="1">
+      <c r="A1416" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>759</v>
+      </c>
       <c r="D1416" s="1"/>
     </row>
     <row r="1417" ht="12.75">
-      <c r="A1417" s="6"/>
-      <c r="B1417"/>
-      <c r="C1417"/>
+      <c r="A1417" s="14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1417"/>
       <c r="G1417"/>
     </row>
     <row r="1418" ht="12.75">
-      <c r="A1418" s="6"/>
-      <c r="B1418"/>
-      <c r="C1418"/>
+      <c r="A1418" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1418" s="1"/>
     </row>
     <row r="1419" ht="12.75">
-      <c r="A1419" s="6"/>
-      <c r="B1419"/>
-      <c r="C1419"/>
+      <c r="A1419" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1419"/>
       <c r="G1419"/>
     </row>
     <row r="1420" ht="12.75">
-      <c r="A1420" s="6"/>
-      <c r="B1420"/>
-      <c r="C1420"/>
+      <c r="A1420" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C1420" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1420" s="1"/>
     </row>
     <row r="1421" ht="12.75">
-      <c r="A1421" s="6"/>
-      <c r="B1421"/>
-      <c r="C1421"/>
+      <c r="A1421" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1421" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1421"/>
       <c r="G1421"/>
     </row>
     <row r="1422" ht="12.75">
-      <c r="A1422" s="6"/>
-      <c r="B1422"/>
-      <c r="C1422"/>
+      <c r="A1422" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C1422" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1422" s="1"/>
     </row>
     <row r="1423" ht="12.75">
-      <c r="A1423" s="6"/>
-      <c r="B1423"/>
-      <c r="C1423"/>
+      <c r="A1423" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C1423" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1423"/>
       <c r="G1423"/>
     </row>
     <row r="1424" ht="12.75">
-      <c r="A1424" s="6"/>
-      <c r="B1424"/>
-      <c r="C1424"/>
+      <c r="A1424" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C1424" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1424" s="1"/>
     </row>
     <row r="1425" ht="12.75">
-      <c r="A1425" s="6"/>
-      <c r="B1425"/>
-      <c r="C1425"/>
+      <c r="A1425" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C1425" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1425"/>
       <c r="G1425"/>
     </row>
     <row r="1426" ht="12.75">
-      <c r="A1426" s="6"/>
-      <c r="B1426"/>
-      <c r="C1426"/>
+      <c r="A1426" s="14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C1426" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1426" s="1"/>
     </row>
     <row r="1427" ht="12.75">
-      <c r="A1427" s="6"/>
-      <c r="B1427"/>
-      <c r="C1427"/>
+      <c r="A1427" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1427" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1427"/>
       <c r="G1427"/>
     </row>
     <row r="1428" ht="12.75">
-      <c r="A1428" s="6"/>
-      <c r="B1428"/>
-      <c r="C1428"/>
+      <c r="A1428" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C1428" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1428" s="1"/>
     </row>
     <row r="1429" ht="12.75">
-      <c r="A1429" s="6"/>
-      <c r="B1429"/>
-      <c r="C1429"/>
+      <c r="A1429" s="14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C1429" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1429"/>
       <c r="G1429"/>
     </row>
     <row r="1430" ht="12.75">
-      <c r="A1430" s="6"/>
-      <c r="B1430"/>
-      <c r="C1430"/>
+      <c r="A1430" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1430" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1430" s="1"/>
     </row>
     <row r="1431" ht="12.75">
-      <c r="A1431" s="6"/>
-      <c r="B1431"/>
-      <c r="C1431"/>
+      <c r="A1431" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C1431" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1431"/>
       <c r="G1431"/>
     </row>
     <row r="1432" ht="12.75">
-      <c r="A1432" s="6"/>
-      <c r="B1432"/>
-      <c r="C1432"/>
+      <c r="A1432" s="14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C1432" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1432" s="1"/>
     </row>
     <row r="1433" ht="12.75">
-      <c r="A1433" s="6"/>
-      <c r="B1433"/>
-      <c r="C1433"/>
+      <c r="A1433" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C1433" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1433"/>
       <c r="G1433"/>
     </row>
     <row r="1434" ht="12.75">
-      <c r="A1434" s="6"/>
-      <c r="B1434"/>
-      <c r="C1434"/>
+      <c r="A1434" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C1434" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1434" s="1"/>
     </row>
     <row r="1435" ht="12.75">
-      <c r="A1435" s="6"/>
-      <c r="B1435"/>
-      <c r="C1435"/>
+      <c r="A1435" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C1435" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1435"/>
       <c r="G1435"/>
     </row>
     <row r="1436" ht="12.75">
-      <c r="A1436" s="6"/>
-      <c r="B1436"/>
-      <c r="C1436"/>
+      <c r="A1436" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C1436" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1436" s="1"/>
     </row>
     <row r="1437" ht="12.75">
-      <c r="A1437" s="6"/>
-      <c r="B1437"/>
-      <c r="C1437"/>
+      <c r="A1437" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C1437" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1437"/>
       <c r="G1437"/>
     </row>
     <row r="1438" ht="12.75">
-      <c r="A1438" s="6"/>
-      <c r="B1438"/>
-      <c r="C1438"/>
+      <c r="A1438" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C1438" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1438" s="1"/>
     </row>
     <row r="1439" ht="12.75">
-      <c r="A1439" s="6"/>
-      <c r="B1439"/>
-      <c r="C1439"/>
+      <c r="A1439" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C1439" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1439"/>
       <c r="G1439"/>
     </row>
     <row r="1440" ht="12.75">
-      <c r="A1440" s="6"/>
+      <c r="A1440" s="7" t="s">
+        <v>2014</v>
+      </c>
       <c r="B1440"/>
-      <c r="C1440"/>
+      <c r="C1440" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1440" s="1"/>
     </row>
     <row r="1441" ht="12.75">
-      <c r="A1441" s="6"/>
+      <c r="A1441" s="7" t="s">
+        <v>2014</v>
+      </c>
       <c r="B1441"/>
-      <c r="C1441"/>
+      <c r="C1441" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1441"/>
       <c r="G1441"/>
     </row>
     <row r="1442" ht="12.75">
-      <c r="A1442" s="6"/>
+      <c r="A1442" s="7" t="s">
+        <v>2014</v>
+      </c>
       <c r="B1442"/>
-      <c r="C1442"/>
+      <c r="C1442" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1442" s="1"/>
     </row>
     <row r="1443" ht="12.75">
-      <c r="A1443" s="6"/>
+      <c r="A1443" s="7" t="s">
+        <v>2014</v>
+      </c>
       <c r="B1443"/>
-      <c r="C1443"/>
+      <c r="C1443" s="9" t="s">
+        <v>2016</v>
+      </c>
       <c r="D1443"/>
       <c r="G1443"/>
     </row>
@@ -26975,7 +27214,7 @@
     </row>
     <row r="2641" ht="12.75">
       <c r="A2641" s="2"/>
-      <c r="C2641" s="17"/>
+      <c r="C2641" s="15"/>
     </row>
     <row r="2642" ht="12.75">
       <c r="A2642" s="6"/>
@@ -26983,11 +27222,14 @@
     <row r="2643" ht="12.75">
       <c r="A2643" s="7"/>
     </row>
+    <row r="2644" ht="12.75">
+      <c r="A2644" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1415">
+  <autoFilter ref="A1:C1443">
     <filterColumn colId="0">
       <filters>
-        <filter val="(Genre) CityPop"/>
+        <filter val="(This is ...) Morrissey"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/playlists.xlsx
+++ b/playlists.xlsx
@@ -9,8 +9,8 @@
     <sheet name="playlists" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1415</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1462</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="2039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="2059">
   <si>
     <t xml:space="preserve">Playlist Name</t>
   </si>
@@ -4810,6 +4810,9 @@
     <t>Zabadak</t>
   </si>
   <si>
+    <t xml:space="preserve">Itsutsu No Hashi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mizu no Sortilège</t>
   </si>
   <si>
@@ -6137,6 +6140,63 @@
   </si>
   <si>
     <t xml:space="preserve">Certain People i Know</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We Hate it When Our Friends became Successful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasick, yet Still Docked</t>
+  </si>
+  <si>
+    <t>Tomorrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now my heart is full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold on to Your Friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The More you Ignore me, the closer i get</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why dont you find out for yourself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dangenham Dave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do Your Best and Dont worry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trouble Loves Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alma Matters</t>
+  </si>
+  <si>
+    <t>Sunny</t>
+  </si>
+  <si>
+    <t>Boxers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thats Entertaiment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Love Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You're the one for me, Fatty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sister Im a Poet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Girl Least Likely To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyakunen No Mangetsu</t>
   </si>
 </sst>
 </file>
@@ -6212,7 +6272,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6241,6 +6301,9 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
       <protection hidden="0" locked="1"/>
@@ -6250,10 +6313,6 @@
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
@@ -21194,7 +21253,7 @@
       <c r="D1078"/>
       <c r="G1078"/>
     </row>
-    <row r="1079" ht="12.75" hidden="1">
+    <row r="1079" ht="12.75">
       <c r="A1079" s="7" t="s">
         <v>1593</v>
       </c>
@@ -21206,20 +21265,19 @@
       </c>
       <c r="D1079" s="1"/>
     </row>
-    <row r="1080" ht="12.75" hidden="1">
+    <row r="1080" ht="12.75">
       <c r="A1080" s="7" t="s">
         <v>1593</v>
       </c>
-      <c r="B1080" t="s">
+      <c r="B1080" s="11" t="s">
         <v>1596</v>
       </c>
-      <c r="C1080" s="8" t="s">
+      <c r="C1080" s="12" t="s">
         <v>1595</v>
       </c>
-      <c r="D1080"/>
-      <c r="G1080"/>
-    </row>
-    <row r="1081" ht="12.75" hidden="1">
+      <c r="D1080" s="13"/>
+    </row>
+    <row r="1081" ht="12.75">
       <c r="A1081" s="7" t="s">
         <v>1593</v>
       </c>
@@ -21229,24 +21287,24 @@
       <c r="C1081" s="8" t="s">
         <v>1595</v>
       </c>
-      <c r="D1081" s="1"/>
-    </row>
-    <row r="1082" ht="12.75" hidden="1">
+      <c r="D1081"/>
+      <c r="G1081"/>
+    </row>
+    <row r="1082" ht="12.75">
       <c r="A1082" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B1082" t="s">
         <v>1598</v>
       </c>
-      <c r="B1082" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C1082" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1082"/>
-      <c r="G1082"/>
+      <c r="C1082" s="8" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D1082" s="1"/>
     </row>
     <row r="1083" ht="12.75" hidden="1">
       <c r="A1083" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1083" t="s">
         <v>1600</v>
@@ -21254,11 +21312,12 @@
       <c r="C1083" t="s">
         <v>423</v>
       </c>
-      <c r="D1083" s="1"/>
+      <c r="D1083"/>
+      <c r="G1083"/>
     </row>
     <row r="1084" ht="12.75" hidden="1">
       <c r="A1084" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1084" t="s">
         <v>1601</v>
@@ -21266,12 +21325,11 @@
       <c r="C1084" t="s">
         <v>423</v>
       </c>
-      <c r="D1084"/>
-      <c r="G1084"/>
+      <c r="D1084" s="1"/>
     </row>
     <row r="1085" ht="12.75" hidden="1">
       <c r="A1085" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1085" t="s">
         <v>1602</v>
@@ -21279,11 +21337,12 @@
       <c r="C1085" t="s">
         <v>423</v>
       </c>
-      <c r="D1085" s="1"/>
+      <c r="D1085"/>
+      <c r="G1085"/>
     </row>
     <row r="1086" ht="12.75" hidden="1">
       <c r="A1086" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1086" t="s">
         <v>1603</v>
@@ -21291,12 +21350,11 @@
       <c r="C1086" t="s">
         <v>423</v>
       </c>
-      <c r="D1086"/>
-      <c r="G1086"/>
+      <c r="D1086" s="1"/>
     </row>
     <row r="1087" ht="12.75" hidden="1">
       <c r="A1087" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1087" t="s">
         <v>1604</v>
@@ -21304,11 +21362,12 @@
       <c r="C1087" t="s">
         <v>423</v>
       </c>
-      <c r="D1087" s="1"/>
+      <c r="D1087"/>
+      <c r="G1087"/>
     </row>
     <row r="1088" ht="12.75" hidden="1">
       <c r="A1088" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1088" t="s">
         <v>1605</v>
@@ -21316,12 +21375,11 @@
       <c r="C1088" t="s">
         <v>423</v>
       </c>
-      <c r="D1088"/>
-      <c r="G1088"/>
+      <c r="D1088" s="1"/>
     </row>
     <row r="1089" ht="12.75" hidden="1">
       <c r="A1089" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1089" t="s">
         <v>1606</v>
@@ -21329,11 +21387,12 @@
       <c r="C1089" t="s">
         <v>423</v>
       </c>
-      <c r="D1089" s="1"/>
+      <c r="D1089"/>
+      <c r="G1089"/>
     </row>
     <row r="1090" ht="12.75" hidden="1">
       <c r="A1090" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1090" t="s">
         <v>1607</v>
@@ -21341,12 +21400,11 @@
       <c r="C1090" t="s">
         <v>423</v>
       </c>
-      <c r="D1090"/>
-      <c r="G1090"/>
+      <c r="D1090" s="1"/>
     </row>
     <row r="1091" ht="12.75" hidden="1">
       <c r="A1091" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1091" t="s">
         <v>1608</v>
@@ -21354,11 +21412,12 @@
       <c r="C1091" t="s">
         <v>423</v>
       </c>
-      <c r="D1091" s="1"/>
+      <c r="D1091"/>
+      <c r="G1091"/>
     </row>
     <row r="1092" ht="12.75" hidden="1">
       <c r="A1092" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1092" t="s">
         <v>1609</v>
@@ -21366,12 +21425,11 @@
       <c r="C1092" t="s">
         <v>423</v>
       </c>
-      <c r="D1092"/>
-      <c r="G1092"/>
+      <c r="D1092" s="1"/>
     </row>
     <row r="1093" ht="12.75" hidden="1">
       <c r="A1093" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1093" t="s">
         <v>1610</v>
@@ -21379,11 +21437,12 @@
       <c r="C1093" t="s">
         <v>423</v>
       </c>
-      <c r="D1093" s="1"/>
+      <c r="D1093"/>
+      <c r="G1093"/>
     </row>
     <row r="1094" ht="12.75" hidden="1">
       <c r="A1094" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1094" t="s">
         <v>1611</v>
@@ -21391,12 +21450,11 @@
       <c r="C1094" t="s">
         <v>423</v>
       </c>
-      <c r="D1094"/>
-      <c r="G1094"/>
+      <c r="D1094" s="1"/>
     </row>
     <row r="1095" ht="12.75" hidden="1">
       <c r="A1095" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1095" t="s">
         <v>1612</v>
@@ -21404,11 +21462,12 @@
       <c r="C1095" t="s">
         <v>423</v>
       </c>
-      <c r="D1095" s="1"/>
+      <c r="D1095"/>
+      <c r="G1095"/>
     </row>
     <row r="1096" ht="12.75" hidden="1">
       <c r="A1096" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1096" t="s">
         <v>1613</v>
@@ -21416,12 +21475,11 @@
       <c r="C1096" t="s">
         <v>423</v>
       </c>
-      <c r="D1096"/>
-      <c r="G1096"/>
+      <c r="D1096" s="1"/>
     </row>
     <row r="1097" ht="12.75" hidden="1">
       <c r="A1097" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1097" t="s">
         <v>1614</v>
@@ -21429,11 +21487,12 @@
       <c r="C1097" t="s">
         <v>423</v>
       </c>
-      <c r="D1097" s="1"/>
+      <c r="D1097"/>
+      <c r="G1097"/>
     </row>
     <row r="1098" ht="12.75" hidden="1">
       <c r="A1098" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1098" t="s">
         <v>1615</v>
@@ -21441,12 +21500,11 @@
       <c r="C1098" t="s">
         <v>423</v>
       </c>
-      <c r="D1098"/>
-      <c r="G1098"/>
+      <c r="D1098" s="1"/>
     </row>
     <row r="1099" ht="12.75" hidden="1">
       <c r="A1099" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1099" t="s">
         <v>1616</v>
@@ -21454,11 +21512,12 @@
       <c r="C1099" t="s">
         <v>423</v>
       </c>
-      <c r="D1099" s="1"/>
+      <c r="D1099"/>
+      <c r="G1099"/>
     </row>
     <row r="1100" ht="12.75" hidden="1">
       <c r="A1100" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1100" t="s">
         <v>1617</v>
@@ -21466,12 +21525,11 @@
       <c r="C1100" t="s">
         <v>423</v>
       </c>
-      <c r="D1100"/>
-      <c r="G1100"/>
+      <c r="D1100" s="1"/>
     </row>
     <row r="1101" ht="12.75" hidden="1">
       <c r="A1101" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1101" t="s">
         <v>1618</v>
@@ -21479,11 +21537,12 @@
       <c r="C1101" t="s">
         <v>423</v>
       </c>
-      <c r="D1101" s="1"/>
+      <c r="D1101"/>
+      <c r="G1101"/>
     </row>
     <row r="1102" ht="12.75" hidden="1">
       <c r="A1102" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1102" t="s">
         <v>1619</v>
@@ -21491,474 +21550,474 @@
       <c r="C1102" t="s">
         <v>423</v>
       </c>
-      <c r="D1102"/>
-      <c r="G1102"/>
+      <c r="D1102" s="1"/>
     </row>
     <row r="1103" ht="12.75" hidden="1">
       <c r="A1103" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1103" t="s">
-        <v>494</v>
+        <v>1620</v>
       </c>
       <c r="C1103" t="s">
         <v>423</v>
       </c>
-      <c r="D1103" s="1"/>
+      <c r="D1103"/>
+      <c r="G1103"/>
     </row>
     <row r="1104" ht="12.75" hidden="1">
       <c r="A1104" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1104" t="s">
-        <v>1620</v>
+        <v>494</v>
       </c>
       <c r="C1104" t="s">
         <v>423</v>
       </c>
-      <c r="D1104"/>
-      <c r="G1104"/>
+      <c r="D1104" s="1"/>
     </row>
     <row r="1105" ht="12.75" hidden="1">
       <c r="A1105" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1621</v>
       </c>
-      <c r="B1105" t="s">
-        <v>1622</v>
-      </c>
       <c r="C1105" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1105" s="1"/>
+        <v>423</v>
+      </c>
+      <c r="D1105"/>
+      <c r="G1105"/>
     </row>
     <row r="1106" ht="12.75" hidden="1">
       <c r="A1106" s="7" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1106" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C1106" t="s">
         <v>1624</v>
       </c>
-      <c r="C1106" s="8" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1106"/>
-      <c r="G1106"/>
+      <c r="D1106" s="1"/>
     </row>
     <row r="1107" ht="12.75" hidden="1">
       <c r="A1107" s="7" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1107" t="s">
         <v>1625</v>
       </c>
       <c r="C1107" s="8" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1107" s="1"/>
+        <v>1624</v>
+      </c>
+      <c r="D1107"/>
+      <c r="G1107"/>
     </row>
     <row r="1108" ht="12.75" hidden="1">
       <c r="A1108" s="7" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1108" t="s">
         <v>1626</v>
       </c>
       <c r="C1108" s="8" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1108"/>
-      <c r="G1108"/>
+        <v>1624</v>
+      </c>
+      <c r="D1108" s="1"/>
     </row>
     <row r="1109" ht="12.75" hidden="1">
       <c r="A1109" s="7" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1109" t="s">
         <v>1627</v>
       </c>
       <c r="C1109" s="8" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1109" s="1"/>
+        <v>1624</v>
+      </c>
+      <c r="D1109"/>
+      <c r="G1109"/>
     </row>
     <row r="1110" ht="12.75" hidden="1">
       <c r="A1110" s="7" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1110" t="s">
         <v>1628</v>
       </c>
       <c r="C1110" s="8" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1110"/>
-      <c r="G1110"/>
+        <v>1624</v>
+      </c>
+      <c r="D1110" s="1"/>
     </row>
     <row r="1111" ht="12.75" hidden="1">
       <c r="A1111" s="7" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1111" t="s">
         <v>1629</v>
       </c>
       <c r="C1111" s="8" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D1111" s="1"/>
+        <v>1624</v>
+      </c>
+      <c r="D1111"/>
+      <c r="G1111"/>
     </row>
     <row r="1112" ht="12.75" hidden="1">
       <c r="A1112" s="7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1112" t="s">
         <v>1630</v>
       </c>
-      <c r="B1112" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C1112" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1112"/>
-      <c r="G1112"/>
+      <c r="C1112" s="8" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D1112" s="1"/>
     </row>
     <row r="1113" ht="12.75" hidden="1">
       <c r="A1113" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1113" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C1113" t="s">
         <v>1633</v>
       </c>
-      <c r="C1113" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1113" s="1"/>
+      <c r="D1113"/>
+      <c r="G1113"/>
     </row>
     <row r="1114" ht="12.75" hidden="1">
       <c r="A1114" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1114" t="s">
         <v>1634</v>
       </c>
       <c r="C1114" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1114"/>
-      <c r="G1114"/>
+        <v>1633</v>
+      </c>
+      <c r="D1114" s="1"/>
     </row>
     <row r="1115" ht="12.75" hidden="1">
       <c r="A1115" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1115" t="s">
         <v>1635</v>
       </c>
       <c r="C1115" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1115" s="1"/>
+        <v>1633</v>
+      </c>
+      <c r="D1115"/>
+      <c r="G1115"/>
     </row>
     <row r="1116" ht="12.75" hidden="1">
       <c r="A1116" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1116" t="s">
         <v>1636</v>
       </c>
       <c r="C1116" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1116"/>
-      <c r="G1116"/>
+        <v>1633</v>
+      </c>
+      <c r="D1116" s="1"/>
     </row>
     <row r="1117" ht="12.75" hidden="1">
       <c r="A1117" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1117" t="s">
         <v>1637</v>
       </c>
       <c r="C1117" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1117" s="1"/>
+        <v>1633</v>
+      </c>
+      <c r="D1117"/>
+      <c r="G1117"/>
     </row>
     <row r="1118" ht="12.75" hidden="1">
       <c r="A1118" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1118" t="s">
         <v>1638</v>
       </c>
       <c r="C1118" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1118"/>
-      <c r="G1118"/>
+        <v>1633</v>
+      </c>
+      <c r="D1118" s="1"/>
     </row>
     <row r="1119" ht="12.75" hidden="1">
       <c r="A1119" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1119" t="s">
         <v>1639</v>
       </c>
       <c r="C1119" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1119" s="1"/>
+        <v>1633</v>
+      </c>
+      <c r="D1119"/>
+      <c r="G1119"/>
     </row>
     <row r="1120" ht="12.75" hidden="1">
       <c r="A1120" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1120" t="s">
         <v>1640</v>
       </c>
       <c r="C1120" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1120"/>
-      <c r="G1120"/>
+        <v>1633</v>
+      </c>
+      <c r="D1120" s="1"/>
     </row>
     <row r="1121" ht="12.75" hidden="1">
       <c r="A1121" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1121" t="s">
         <v>1641</v>
       </c>
       <c r="C1121" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1121" s="1"/>
+        <v>1633</v>
+      </c>
+      <c r="D1121"/>
+      <c r="G1121"/>
     </row>
     <row r="1122" ht="12.75" hidden="1">
       <c r="A1122" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1122" t="s">
         <v>1642</v>
       </c>
       <c r="C1122" s="8" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1122"/>
-      <c r="G1122"/>
+        <v>1633</v>
+      </c>
+      <c r="D1122" s="1"/>
     </row>
     <row r="1123" ht="12.75" hidden="1">
       <c r="A1123" s="7" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1643</v>
       </c>
-      <c r="B1123" t="s">
-        <v>1644</v>
-      </c>
-      <c r="C1123" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1123" s="1"/>
+      <c r="C1123" s="8" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D1123"/>
+      <c r="G1123"/>
     </row>
     <row r="1124" ht="12.75" hidden="1">
       <c r="A1124" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1124" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C1124" t="s">
         <v>1646</v>
       </c>
-      <c r="C1124" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1124"/>
-      <c r="G1124"/>
+      <c r="D1124" s="1"/>
     </row>
     <row r="1125" ht="12.75" hidden="1">
       <c r="A1125" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1125" t="s">
         <v>1647</v>
       </c>
       <c r="C1125" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1125" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1125"/>
+      <c r="G1125"/>
     </row>
     <row r="1126" ht="12.75" hidden="1">
       <c r="A1126" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1126" t="s">
         <v>1648</v>
       </c>
       <c r="C1126" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1126"/>
-      <c r="G1126"/>
+        <v>1646</v>
+      </c>
+      <c r="D1126" s="1"/>
     </row>
     <row r="1127" ht="12.75" hidden="1">
       <c r="A1127" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1127" t="s">
         <v>1649</v>
       </c>
       <c r="C1127" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1127" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1127"/>
+      <c r="G1127"/>
     </row>
     <row r="1128" ht="12.75" hidden="1">
       <c r="A1128" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1128" t="s">
         <v>1650</v>
       </c>
       <c r="C1128" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1128"/>
-      <c r="G1128"/>
+        <v>1646</v>
+      </c>
+      <c r="D1128" s="1"/>
     </row>
     <row r="1129" ht="12.75" hidden="1">
       <c r="A1129" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1129" t="s">
         <v>1651</v>
       </c>
       <c r="C1129" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1129" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1129"/>
+      <c r="G1129"/>
     </row>
     <row r="1130" ht="12.75" hidden="1">
       <c r="A1130" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1130" t="s">
         <v>1652</v>
       </c>
       <c r="C1130" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1130"/>
-      <c r="G1130"/>
+        <v>1646</v>
+      </c>
+      <c r="D1130" s="1"/>
     </row>
     <row r="1131" ht="12.75" hidden="1">
       <c r="A1131" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1131" t="s">
         <v>1653</v>
       </c>
       <c r="C1131" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1131" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1131"/>
+      <c r="G1131"/>
     </row>
     <row r="1132" ht="12.75" hidden="1">
       <c r="A1132" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1132" t="s">
         <v>1654</v>
       </c>
       <c r="C1132" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1132"/>
-      <c r="G1132"/>
+        <v>1646</v>
+      </c>
+      <c r="D1132" s="1"/>
     </row>
     <row r="1133" ht="12.75" hidden="1">
       <c r="A1133" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1133" t="s">
         <v>1655</v>
       </c>
       <c r="C1133" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1133" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1133"/>
+      <c r="G1133"/>
     </row>
     <row r="1134" ht="12.75" hidden="1">
       <c r="A1134" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1134" t="s">
         <v>1656</v>
       </c>
       <c r="C1134" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1134"/>
-      <c r="G1134"/>
+        <v>1646</v>
+      </c>
+      <c r="D1134" s="1"/>
     </row>
     <row r="1135" ht="12.75" hidden="1">
       <c r="A1135" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1135" t="s">
         <v>1657</v>
       </c>
       <c r="C1135" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1135" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1135"/>
+      <c r="G1135"/>
     </row>
     <row r="1136" ht="12.75" hidden="1">
       <c r="A1136" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1136" t="s">
         <v>1658</v>
       </c>
       <c r="C1136" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1136"/>
-      <c r="G1136"/>
+        <v>1646</v>
+      </c>
+      <c r="D1136" s="1"/>
     </row>
     <row r="1137" ht="12.75" hidden="1">
       <c r="A1137" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1137" t="s">
         <v>1659</v>
       </c>
       <c r="C1137" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1137" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1137"/>
+      <c r="G1137"/>
     </row>
     <row r="1138" ht="12.75" hidden="1">
       <c r="A1138" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1138" t="s">
         <v>1660</v>
       </c>
       <c r="C1138" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1138"/>
-      <c r="G1138"/>
+        <v>1646</v>
+      </c>
+      <c r="D1138" s="1"/>
     </row>
     <row r="1139" ht="12.75" hidden="1">
       <c r="A1139" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1661</v>
       </c>
-      <c r="B1139" t="s">
-        <v>1662</v>
-      </c>
       <c r="C1139" t="s">
-        <v>663</v>
-      </c>
-      <c r="D1139" s="1"/>
+        <v>1646</v>
+      </c>
+      <c r="D1139"/>
+      <c r="G1139"/>
     </row>
     <row r="1140" ht="12.75" hidden="1">
       <c r="A1140" s="7" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1140" t="s">
         <v>1663</v>
@@ -21966,12 +22025,11 @@
       <c r="C1140" t="s">
         <v>663</v>
       </c>
-      <c r="D1140"/>
-      <c r="G1140"/>
+      <c r="D1140" s="1"/>
     </row>
     <row r="1141" ht="12.75" hidden="1">
       <c r="A1141" s="7" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1141" t="s">
         <v>1664</v>
@@ -21979,820 +22037,820 @@
       <c r="C1141" t="s">
         <v>663</v>
       </c>
-      <c r="D1141" s="1"/>
+      <c r="D1141"/>
+      <c r="G1141"/>
     </row>
     <row r="1142" ht="12.75" hidden="1">
       <c r="A1142" s="7" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1665</v>
       </c>
-      <c r="B1142" t="s">
-        <v>1666</v>
-      </c>
       <c r="C1142" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1142"/>
-      <c r="G1142"/>
+        <v>663</v>
+      </c>
+      <c r="D1142" s="1"/>
     </row>
     <row r="1143" ht="12.75" hidden="1">
       <c r="A1143" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1143" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C1143" t="s">
         <v>1668</v>
       </c>
-      <c r="C1143" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1143" s="1"/>
+      <c r="D1143"/>
+      <c r="G1143"/>
     </row>
     <row r="1144" ht="12.75" hidden="1">
       <c r="A1144" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1144" t="s">
         <v>1669</v>
       </c>
       <c r="C1144" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1144"/>
-      <c r="G1144"/>
+        <v>1668</v>
+      </c>
+      <c r="D1144" s="1"/>
     </row>
     <row r="1145" ht="12.75" hidden="1">
       <c r="A1145" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1145" t="s">
         <v>1670</v>
       </c>
       <c r="C1145" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1145" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1145"/>
+      <c r="G1145"/>
     </row>
     <row r="1146" ht="12.75" hidden="1">
       <c r="A1146" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1146" t="s">
         <v>1671</v>
       </c>
       <c r="C1146" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1146"/>
-      <c r="G1146"/>
+        <v>1668</v>
+      </c>
+      <c r="D1146" s="1"/>
     </row>
     <row r="1147" ht="12.75" hidden="1">
       <c r="A1147" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1147" t="s">
         <v>1672</v>
       </c>
       <c r="C1147" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1147" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1147"/>
+      <c r="G1147"/>
     </row>
     <row r="1148" ht="12.75" hidden="1">
       <c r="A1148" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1148" t="s">
         <v>1673</v>
       </c>
       <c r="C1148" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1148"/>
-      <c r="G1148"/>
+        <v>1668</v>
+      </c>
+      <c r="D1148" s="1"/>
     </row>
     <row r="1149" ht="12.75" hidden="1">
       <c r="A1149" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1149" t="s">
         <v>1674</v>
       </c>
       <c r="C1149" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1149" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1149"/>
+      <c r="G1149"/>
     </row>
     <row r="1150" ht="12.75" hidden="1">
       <c r="A1150" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1150" t="s">
         <v>1675</v>
       </c>
       <c r="C1150" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1150"/>
-      <c r="G1150"/>
+        <v>1668</v>
+      </c>
+      <c r="D1150" s="1"/>
     </row>
     <row r="1151" ht="12.75" hidden="1">
       <c r="A1151" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1151" t="s">
         <v>1676</v>
       </c>
       <c r="C1151" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1151" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1151"/>
+      <c r="G1151"/>
     </row>
     <row r="1152" ht="12.75" hidden="1">
       <c r="A1152" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1152" t="s">
         <v>1677</v>
       </c>
       <c r="C1152" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1152"/>
-      <c r="G1152"/>
+        <v>1668</v>
+      </c>
+      <c r="D1152" s="1"/>
     </row>
     <row r="1153" ht="12.75" hidden="1">
       <c r="A1153" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1153" t="s">
         <v>1678</v>
       </c>
       <c r="C1153" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1153" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1153"/>
+      <c r="G1153"/>
     </row>
     <row r="1154" ht="12.75" hidden="1">
       <c r="A1154" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1154" t="s">
         <v>1679</v>
       </c>
       <c r="C1154" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1154"/>
-      <c r="G1154"/>
+        <v>1668</v>
+      </c>
+      <c r="D1154" s="1"/>
     </row>
     <row r="1155" ht="12.75" hidden="1">
       <c r="A1155" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1155" t="s">
         <v>1680</v>
       </c>
       <c r="C1155" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1155" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1155"/>
+      <c r="G1155"/>
     </row>
     <row r="1156" ht="12.75" hidden="1">
       <c r="A1156" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1156" t="s">
         <v>1681</v>
       </c>
       <c r="C1156" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1156"/>
-      <c r="G1156"/>
+        <v>1668</v>
+      </c>
+      <c r="D1156" s="1"/>
     </row>
     <row r="1157" ht="12.75" hidden="1">
       <c r="A1157" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1157" t="s">
         <v>1682</v>
       </c>
       <c r="C1157" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1157" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1157"/>
+      <c r="G1157"/>
     </row>
     <row r="1158" ht="12.75" hidden="1">
       <c r="A1158" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1158" t="s">
         <v>1683</v>
       </c>
       <c r="C1158" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1158"/>
-      <c r="G1158"/>
+        <v>1668</v>
+      </c>
+      <c r="D1158" s="1"/>
     </row>
     <row r="1159" ht="12.75" hidden="1">
       <c r="A1159" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1159" t="s">
         <v>1684</v>
       </c>
       <c r="C1159" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1159" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1159"/>
+      <c r="G1159"/>
     </row>
     <row r="1160" ht="12.75" hidden="1">
       <c r="A1160" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1160" t="s">
         <v>1685</v>
       </c>
       <c r="C1160" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1160"/>
-      <c r="G1160"/>
+        <v>1668</v>
+      </c>
+      <c r="D1160" s="1"/>
     </row>
     <row r="1161" ht="12.75" hidden="1">
       <c r="A1161" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1161" t="s">
         <v>1686</v>
       </c>
       <c r="C1161" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1161" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1161"/>
+      <c r="G1161"/>
     </row>
     <row r="1162" ht="12.75" hidden="1">
       <c r="A1162" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1162" t="s">
         <v>1687</v>
       </c>
       <c r="C1162" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1162"/>
-      <c r="G1162"/>
+        <v>1668</v>
+      </c>
+      <c r="D1162" s="1"/>
     </row>
     <row r="1163" ht="12.75" hidden="1">
       <c r="A1163" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1163" t="s">
         <v>1688</v>
       </c>
       <c r="C1163" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1163" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1163"/>
+      <c r="G1163"/>
     </row>
     <row r="1164" ht="12.75" hidden="1">
       <c r="A1164" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1164" t="s">
         <v>1689</v>
       </c>
       <c r="C1164" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1164"/>
-      <c r="G1164"/>
+        <v>1668</v>
+      </c>
+      <c r="D1164" s="1"/>
     </row>
     <row r="1165" ht="12.75" hidden="1">
       <c r="A1165" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1165" t="s">
         <v>1690</v>
       </c>
       <c r="C1165" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1165" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1165"/>
+      <c r="G1165"/>
     </row>
     <row r="1166" ht="12.75" hidden="1">
       <c r="A1166" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1166" t="s">
         <v>1691</v>
       </c>
       <c r="C1166" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1166"/>
-      <c r="G1166"/>
+        <v>1668</v>
+      </c>
+      <c r="D1166" s="1"/>
     </row>
     <row r="1167" ht="12.75" hidden="1">
       <c r="A1167" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1167" t="s">
         <v>1692</v>
       </c>
       <c r="C1167" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1167" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1167"/>
+      <c r="G1167"/>
     </row>
     <row r="1168" ht="12.75" hidden="1">
       <c r="A1168" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1168" t="s">
         <v>1693</v>
       </c>
       <c r="C1168" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1168"/>
-      <c r="G1168"/>
+        <v>1668</v>
+      </c>
+      <c r="D1168" s="1"/>
     </row>
     <row r="1169" ht="12.75" hidden="1">
       <c r="A1169" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1169" t="s">
         <v>1694</v>
       </c>
       <c r="C1169" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1169" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1169"/>
+      <c r="G1169"/>
     </row>
     <row r="1170" ht="12.75" hidden="1">
       <c r="A1170" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1170" t="s">
         <v>1695</v>
       </c>
       <c r="C1170" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1170"/>
-      <c r="G1170"/>
+        <v>1668</v>
+      </c>
+      <c r="D1170" s="1"/>
     </row>
     <row r="1171" ht="12.75" hidden="1">
       <c r="A1171" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1171" t="s">
         <v>1696</v>
       </c>
       <c r="C1171" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1171" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1171"/>
+      <c r="G1171"/>
     </row>
     <row r="1172" ht="12.75" hidden="1">
       <c r="A1172" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1172" t="s">
         <v>1697</v>
       </c>
       <c r="C1172" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1172"/>
-      <c r="G1172"/>
+        <v>1668</v>
+      </c>
+      <c r="D1172" s="1"/>
     </row>
     <row r="1173" ht="12.75" hidden="1">
       <c r="A1173" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1173" t="s">
         <v>1698</v>
       </c>
       <c r="C1173" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1173" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1173"/>
+      <c r="G1173"/>
     </row>
     <row r="1174" ht="12.75" hidden="1">
       <c r="A1174" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1174" t="s">
         <v>1699</v>
       </c>
       <c r="C1174" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1174"/>
-      <c r="G1174"/>
+        <v>1668</v>
+      </c>
+      <c r="D1174" s="1"/>
     </row>
     <row r="1175" ht="12.75" hidden="1">
       <c r="A1175" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1175" t="s">
         <v>1700</v>
       </c>
       <c r="C1175" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1175" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1175"/>
+      <c r="G1175"/>
     </row>
     <row r="1176" ht="12.75" hidden="1">
       <c r="A1176" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1176" t="s">
         <v>1701</v>
       </c>
       <c r="C1176" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1176"/>
-      <c r="G1176"/>
+        <v>1668</v>
+      </c>
+      <c r="D1176" s="1"/>
     </row>
     <row r="1177" ht="12.75" hidden="1">
       <c r="A1177" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1177" t="s">
         <v>1702</v>
       </c>
       <c r="C1177" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1177" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1177"/>
+      <c r="G1177"/>
     </row>
     <row r="1178" ht="12.75" hidden="1">
       <c r="A1178" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1178" t="s">
         <v>1703</v>
       </c>
       <c r="C1178" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1178"/>
-      <c r="G1178"/>
+        <v>1668</v>
+      </c>
+      <c r="D1178" s="1"/>
     </row>
     <row r="1179" ht="12.75" hidden="1">
       <c r="A1179" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1179" t="s">
         <v>1704</v>
       </c>
       <c r="C1179" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1179" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1179"/>
+      <c r="G1179"/>
     </row>
     <row r="1180" ht="12.75" hidden="1">
       <c r="A1180" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1180" t="s">
         <v>1705</v>
       </c>
       <c r="C1180" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1180"/>
-      <c r="G1180"/>
+        <v>1668</v>
+      </c>
+      <c r="D1180" s="1"/>
     </row>
     <row r="1181" ht="12.75" hidden="1">
       <c r="A1181" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1181" t="s">
         <v>1706</v>
       </c>
       <c r="C1181" s="8" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1181" s="1"/>
+        <v>1668</v>
+      </c>
+      <c r="D1181"/>
+      <c r="G1181"/>
     </row>
     <row r="1182" ht="12.75" hidden="1">
       <c r="A1182" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1182" t="s">
         <v>1707</v>
       </c>
-      <c r="B1182" t="s">
-        <v>1708</v>
-      </c>
-      <c r="C1182" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1182"/>
-      <c r="G1182"/>
+      <c r="C1182" s="8" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D1182" s="1"/>
     </row>
     <row r="1183" ht="12.75" hidden="1">
       <c r="A1183" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1183" t="s">
-        <v>852</v>
-      </c>
-      <c r="C1183" s="8" t="s">
         <v>1709</v>
       </c>
-      <c r="D1183" s="1"/>
+      <c r="C1183" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D1183"/>
+      <c r="G1183"/>
     </row>
     <row r="1184" ht="12.75" hidden="1">
       <c r="A1184" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1184" t="s">
+        <v>852</v>
+      </c>
+      <c r="C1184" s="8" t="s">
         <v>1710</v>
       </c>
-      <c r="C1184" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1184"/>
-      <c r="G1184"/>
+      <c r="D1184" s="1"/>
     </row>
     <row r="1185" ht="12.75" hidden="1">
       <c r="A1185" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1185" t="s">
         <v>1711</v>
       </c>
       <c r="C1185" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1185" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1185"/>
+      <c r="G1185"/>
     </row>
     <row r="1186" ht="12.75" hidden="1">
       <c r="A1186" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1186" t="s">
         <v>1712</v>
       </c>
       <c r="C1186" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1186"/>
-      <c r="G1186"/>
+        <v>1710</v>
+      </c>
+      <c r="D1186" s="1"/>
     </row>
     <row r="1187" ht="12.75" hidden="1">
       <c r="A1187" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1187" t="s">
         <v>1713</v>
       </c>
       <c r="C1187" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1187" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1187"/>
+      <c r="G1187"/>
     </row>
     <row r="1188" ht="12.75" hidden="1">
       <c r="A1188" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1188" t="s">
         <v>1714</v>
       </c>
       <c r="C1188" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1188"/>
-      <c r="G1188"/>
+        <v>1710</v>
+      </c>
+      <c r="D1188" s="1"/>
     </row>
     <row r="1189" ht="12.75" hidden="1">
       <c r="A1189" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1189" t="s">
         <v>1715</v>
       </c>
       <c r="C1189" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1189" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1189"/>
+      <c r="G1189"/>
     </row>
     <row r="1190" ht="12.75" hidden="1">
       <c r="A1190" s="7" t="s">
-        <v>1707</v>
-      </c>
-      <c r="B1190" s="6">
-        <v>530</v>
+        <v>1708</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>1716</v>
       </c>
       <c r="C1190" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1190"/>
-      <c r="G1190"/>
+        <v>1710</v>
+      </c>
+      <c r="D1190" s="1"/>
     </row>
     <row r="1191" ht="12.75" hidden="1">
       <c r="A1191" s="7" t="s">
-        <v>1707</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>1716</v>
+        <v>1708</v>
+      </c>
+      <c r="B1191" s="6">
+        <v>530</v>
       </c>
       <c r="C1191" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1191" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1191"/>
+      <c r="G1191"/>
     </row>
     <row r="1192" ht="12.75" hidden="1">
       <c r="A1192" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1192" t="s">
         <v>1717</v>
       </c>
       <c r="C1192" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1192"/>
-      <c r="G1192"/>
+        <v>1710</v>
+      </c>
+      <c r="D1192" s="1"/>
     </row>
     <row r="1193" ht="12.75" hidden="1">
       <c r="A1193" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1193" t="s">
         <v>1718</v>
       </c>
       <c r="C1193" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1193" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1193"/>
+      <c r="G1193"/>
     </row>
     <row r="1194" ht="12.75" hidden="1">
       <c r="A1194" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1194" t="s">
         <v>1719</v>
       </c>
       <c r="C1194" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1194"/>
-      <c r="G1194"/>
+        <v>1710</v>
+      </c>
+      <c r="D1194" s="1"/>
     </row>
     <row r="1195" ht="12.75" hidden="1">
       <c r="A1195" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1195" t="s">
-        <v>852</v>
+        <v>1720</v>
       </c>
       <c r="C1195" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1195" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1195"/>
+      <c r="G1195"/>
     </row>
     <row r="1196" ht="12.75" hidden="1">
       <c r="A1196" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1196" t="s">
-        <v>1720</v>
+        <v>852</v>
       </c>
       <c r="C1196" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1196"/>
-      <c r="G1196"/>
+        <v>1710</v>
+      </c>
+      <c r="D1196" s="1"/>
     </row>
     <row r="1197" ht="12.75" hidden="1">
       <c r="A1197" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1197" t="s">
         <v>1721</v>
       </c>
       <c r="C1197" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1197" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1197"/>
+      <c r="G1197"/>
     </row>
     <row r="1198" ht="12.75" hidden="1">
       <c r="A1198" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1198" t="s">
-        <v>1713</v>
+        <v>1722</v>
       </c>
       <c r="C1198" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1198"/>
-      <c r="G1198"/>
+        <v>1710</v>
+      </c>
+      <c r="D1198" s="1"/>
     </row>
     <row r="1199" ht="12.75" hidden="1">
       <c r="A1199" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1199" t="s">
-        <v>1722</v>
+        <v>1714</v>
       </c>
       <c r="C1199" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1199" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1199"/>
+      <c r="G1199"/>
     </row>
     <row r="1200" ht="12.75" hidden="1">
       <c r="A1200" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1200" t="s">
         <v>1723</v>
       </c>
       <c r="C1200" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1200"/>
-      <c r="G1200"/>
+        <v>1710</v>
+      </c>
+      <c r="D1200" s="1"/>
     </row>
     <row r="1201" ht="12.75" hidden="1">
       <c r="A1201" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1201" t="s">
         <v>1724</v>
       </c>
       <c r="C1201" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1201" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1201"/>
+      <c r="G1201"/>
     </row>
     <row r="1202" ht="12.75" hidden="1">
       <c r="A1202" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1202" t="s">
         <v>1725</v>
       </c>
       <c r="C1202" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1202"/>
-      <c r="G1202"/>
+        <v>1710</v>
+      </c>
+      <c r="D1202" s="1"/>
     </row>
     <row r="1203" ht="12.75" hidden="1">
       <c r="A1203" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1203" t="s">
         <v>1726</v>
       </c>
       <c r="C1203" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1203" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1203"/>
+      <c r="G1203"/>
     </row>
     <row r="1204" ht="12.75" hidden="1">
       <c r="A1204" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1204" t="s">
         <v>1727</v>
       </c>
       <c r="C1204" s="8" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D1204"/>
-      <c r="G1204"/>
+        <v>1710</v>
+      </c>
+      <c r="D1204" s="1"/>
     </row>
     <row r="1205" ht="12.75" hidden="1">
       <c r="A1205" s="7" t="s">
-        <v>1458</v>
+        <v>1708</v>
       </c>
       <c r="B1205" t="s">
         <v>1728</v>
       </c>
       <c r="C1205" s="8" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D1205" s="1"/>
+        <v>1710</v>
+      </c>
+      <c r="D1205"/>
+      <c r="G1205"/>
     </row>
     <row r="1206" ht="12.75" hidden="1">
       <c r="A1206" s="7" t="s">
         <v>1458</v>
       </c>
       <c r="B1206" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C1206" s="8" t="s">
         <v>1730</v>
       </c>
-      <c r="C1206" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D1206"/>
-      <c r="G1206"/>
+      <c r="D1206" s="1"/>
     </row>
     <row r="1207" ht="12.75" hidden="1">
       <c r="A1207" s="7" t="s">
@@ -22801,1386 +22859,1386 @@
       <c r="B1207" t="s">
         <v>1731</v>
       </c>
-      <c r="C1207" s="9" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D1207" s="1"/>
+      <c r="C1207" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1207"/>
+      <c r="G1207"/>
     </row>
     <row r="1208" ht="12.75" hidden="1">
       <c r="A1208" s="7" t="s">
-        <v>1643</v>
+        <v>1458</v>
       </c>
       <c r="B1208" t="s">
         <v>1732</v>
       </c>
-      <c r="C1208" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D1208"/>
-      <c r="G1208"/>
+      <c r="C1208" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1208" s="1"/>
     </row>
     <row r="1209" ht="12.75" hidden="1">
-      <c r="A1209" s="6" t="s">
+      <c r="A1209" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B1209" t="s">
         <v>1733</v>
       </c>
-      <c r="B1209" t="s">
+      <c r="C1209" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D1209"/>
+      <c r="G1209"/>
+    </row>
+    <row r="1210" ht="12.75" hidden="1">
+      <c r="A1210" s="6" t="s">
         <v>1734</v>
       </c>
-      <c r="C1209" t="s">
+      <c r="B1210" t="s">
         <v>1735</v>
       </c>
-      <c r="D1209" s="1"/>
-    </row>
-    <row r="1210" ht="12.75" hidden="1">
-      <c r="A1210" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1210" t="s">
+      <c r="C1210" t="s">
         <v>1736</v>
       </c>
-      <c r="C1210" t="s">
+      <c r="D1210" s="1"/>
+    </row>
+    <row r="1211" ht="12.75" hidden="1">
+      <c r="A1211" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1211" t="s">
         <v>1737</v>
       </c>
-      <c r="D1210" s="1"/>
-      <c r="G1210" s="1"/>
-    </row>
-    <row r="1211" ht="12.75" hidden="1">
-      <c r="A1211" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1211" t="s">
+      <c r="C1211" t="s">
         <v>1738</v>
       </c>
-      <c r="C1211" t="s">
+      <c r="D1211" s="1"/>
+      <c r="G1211" s="1"/>
+    </row>
+    <row r="1212" ht="12.75" hidden="1">
+      <c r="A1212" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1212" t="s">
         <v>1739</v>
       </c>
-      <c r="D1211" s="1"/>
-    </row>
-    <row r="1212" ht="12.75" hidden="1">
-      <c r="A1212" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1212" t="s">
+      <c r="C1212" t="s">
         <v>1740</v>
       </c>
-      <c r="C1212" t="s">
+      <c r="D1212" s="1"/>
+    </row>
+    <row r="1213" ht="12.75" hidden="1">
+      <c r="A1213" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1213" t="s">
         <v>1741</v>
       </c>
-      <c r="D1212"/>
-      <c r="G1212"/>
-    </row>
-    <row r="1213" ht="12.75" hidden="1">
-      <c r="A1213" s="6" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1213" t="s">
+      <c r="C1213" t="s">
         <v>1742</v>
       </c>
-      <c r="C1213" t="s">
+      <c r="D1213"/>
+      <c r="G1213"/>
+    </row>
+    <row r="1214" ht="12.75" hidden="1">
+      <c r="A1214" s="6" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1214" t="s">
         <v>1743</v>
       </c>
-      <c r="D1213" s="1"/>
-    </row>
-    <row r="1214" ht="12.75" hidden="1">
-      <c r="A1214" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1214" t="s">
+      <c r="C1214" t="s">
         <v>1744</v>
       </c>
-      <c r="C1214" t="s">
+      <c r="D1214" s="1"/>
+    </row>
+    <row r="1215" ht="12.75" hidden="1">
+      <c r="A1215" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1215" t="s">
         <v>1745</v>
       </c>
-      <c r="D1214"/>
-      <c r="G1214"/>
-    </row>
-    <row r="1215" ht="12.75" hidden="1">
-      <c r="A1215" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1215" t="s">
+      <c r="C1215" t="s">
         <v>1746</v>
       </c>
-      <c r="C1215" t="s">
+      <c r="D1215"/>
+      <c r="G1215"/>
+    </row>
+    <row r="1216" ht="12.75" hidden="1">
+      <c r="A1216" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1216" t="s">
         <v>1747</v>
       </c>
-      <c r="D1215" s="1"/>
-    </row>
-    <row r="1216" ht="12.75" hidden="1">
-      <c r="A1216" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1216" t="s">
+      <c r="C1216" t="s">
         <v>1748</v>
       </c>
-      <c r="C1216" t="s">
+      <c r="D1216" s="1"/>
+    </row>
+    <row r="1217" ht="12.75" hidden="1">
+      <c r="A1217" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1217" t="s">
         <v>1749</v>
       </c>
-      <c r="D1216"/>
-      <c r="G1216"/>
-    </row>
-    <row r="1217" ht="12.75" hidden="1">
-      <c r="A1217" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1217" t="s">
+      <c r="C1217" t="s">
         <v>1750</v>
       </c>
-      <c r="C1217" t="s">
+      <c r="D1217"/>
+      <c r="G1217"/>
+    </row>
+    <row r="1218" ht="12.75" hidden="1">
+      <c r="A1218" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1218" t="s">
         <v>1751</v>
       </c>
-      <c r="D1217" s="1"/>
-    </row>
-    <row r="1218" ht="12.75" hidden="1">
-      <c r="A1218" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1218" t="s">
+      <c r="C1218" t="s">
         <v>1752</v>
       </c>
-      <c r="C1218" t="s">
+      <c r="D1218" s="1"/>
+    </row>
+    <row r="1219" ht="12.75" hidden="1">
+      <c r="A1219" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1219" t="s">
         <v>1753</v>
       </c>
-      <c r="D1218"/>
-      <c r="G1218"/>
-    </row>
-    <row r="1219" ht="12.75" hidden="1">
-      <c r="A1219" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1219" t="s">
+      <c r="C1219" t="s">
         <v>1754</v>
       </c>
-      <c r="C1219" t="s">
+      <c r="D1219"/>
+      <c r="G1219"/>
+    </row>
+    <row r="1220" ht="12.75" hidden="1">
+      <c r="A1220" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1220" t="s">
         <v>1755</v>
       </c>
-      <c r="D1219" s="1"/>
-    </row>
-    <row r="1220" ht="12.75" hidden="1">
-      <c r="A1220" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1220" t="s">
+      <c r="C1220" t="s">
         <v>1756</v>
       </c>
-      <c r="C1220" t="s">
+      <c r="D1220" s="1"/>
+    </row>
+    <row r="1221" ht="12.75" hidden="1">
+      <c r="A1221" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1221" t="s">
         <v>1757</v>
       </c>
-      <c r="D1220"/>
-      <c r="G1220"/>
-    </row>
-    <row r="1221" ht="12.75" hidden="1">
-      <c r="A1221" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1221" t="s">
+      <c r="C1221" t="s">
         <v>1758</v>
       </c>
-      <c r="C1221" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D1221" s="1"/>
+      <c r="D1221"/>
+      <c r="G1221"/>
     </row>
     <row r="1222" ht="12.75" hidden="1">
-      <c r="A1222" s="11" t="s">
-        <v>1733</v>
+      <c r="A1222" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1222" t="s">
         <v>1759</v>
       </c>
       <c r="C1222" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D1222" s="1"/>
+    </row>
+    <row r="1223" ht="12.75" hidden="1">
+      <c r="A1223" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1223" t="s">
         <v>1760</v>
       </c>
-      <c r="D1222"/>
-      <c r="G1222"/>
-    </row>
-    <row r="1223" ht="12.75" hidden="1">
-      <c r="A1223" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1223" t="s">
+      <c r="C1223" t="s">
         <v>1761</v>
       </c>
-      <c r="C1223" t="s">
+      <c r="D1223"/>
+      <c r="G1223"/>
+    </row>
+    <row r="1224" ht="12.75" hidden="1">
+      <c r="A1224" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1224" t="s">
         <v>1762</v>
       </c>
-      <c r="D1223" s="1"/>
-    </row>
-    <row r="1224" ht="12.75" hidden="1">
-      <c r="A1224" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1224" t="s">
+      <c r="C1224" t="s">
         <v>1763</v>
       </c>
-      <c r="C1224" t="s">
+      <c r="D1224" s="1"/>
+    </row>
+    <row r="1225" ht="12.75" hidden="1">
+      <c r="A1225" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1225" t="s">
         <v>1764</v>
-      </c>
-      <c r="D1224"/>
-      <c r="G1224"/>
-    </row>
-    <row r="1225" ht="12.75" hidden="1">
-      <c r="A1225" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1225" s="12">
-        <v>0.16666666666666666</v>
       </c>
       <c r="C1225" t="s">
         <v>1765</v>
       </c>
-      <c r="D1225" s="1"/>
+      <c r="D1225"/>
+      <c r="G1225"/>
     </row>
     <row r="1226" ht="12.75" hidden="1">
-      <c r="A1226" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1226" t="s">
+      <c r="A1226" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1226" s="15">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C1226" t="s">
         <v>1766</v>
       </c>
-      <c r="C1226" t="s">
+      <c r="D1226" s="1"/>
+    </row>
+    <row r="1227" ht="12.75" hidden="1">
+      <c r="A1227" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1227" t="s">
         <v>1767</v>
       </c>
-      <c r="D1226"/>
-      <c r="G1226"/>
-    </row>
-    <row r="1227" ht="12.75" hidden="1">
-      <c r="A1227" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1227" t="s">
+      <c r="C1227" t="s">
         <v>1768</v>
       </c>
-      <c r="C1227" t="s">
-        <v>300</v>
-      </c>
-      <c r="D1227" s="1"/>
+      <c r="D1227"/>
+      <c r="G1227"/>
     </row>
     <row r="1228" ht="12.75" hidden="1">
-      <c r="A1228" s="11" t="s">
-        <v>1733</v>
+      <c r="A1228" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1228" t="s">
         <v>1769</v>
       </c>
       <c r="C1228" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1228" s="1"/>
+    </row>
+    <row r="1229" ht="12.75" hidden="1">
+      <c r="A1229" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1229" t="s">
         <v>1770</v>
       </c>
-      <c r="D1228"/>
-      <c r="G1228"/>
-    </row>
-    <row r="1229" ht="12.75" hidden="1">
-      <c r="A1229" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1229" t="s">
+      <c r="C1229" t="s">
         <v>1771</v>
       </c>
-      <c r="C1229" t="s">
+      <c r="D1229"/>
+      <c r="G1229"/>
+    </row>
+    <row r="1230" ht="12.75" hidden="1">
+      <c r="A1230" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1230" t="s">
         <v>1772</v>
       </c>
-      <c r="D1229" s="1"/>
-    </row>
-    <row r="1230" ht="12.75" hidden="1">
-      <c r="A1230" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1230" t="s">
+      <c r="C1230" t="s">
         <v>1773</v>
       </c>
-      <c r="C1230" t="s">
+      <c r="D1230" s="1"/>
+    </row>
+    <row r="1231" ht="12.75" hidden="1">
+      <c r="A1231" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1231" t="s">
         <v>1774</v>
       </c>
-      <c r="D1230"/>
-      <c r="G1230"/>
-    </row>
-    <row r="1231" ht="12.75" hidden="1">
-      <c r="A1231" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1231" t="s">
+      <c r="C1231" t="s">
         <v>1775</v>
       </c>
-      <c r="C1231" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D1231" s="1"/>
+      <c r="D1231"/>
+      <c r="G1231"/>
     </row>
     <row r="1232" ht="12.75" hidden="1">
-      <c r="A1232" s="11" t="s">
-        <v>1733</v>
+      <c r="A1232" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1232" t="s">
         <v>1776</v>
       </c>
       <c r="C1232" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D1232" s="1"/>
+    </row>
+    <row r="1233" ht="12.75" hidden="1">
+      <c r="A1233" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1233" t="s">
         <v>1777</v>
       </c>
-      <c r="D1232"/>
-      <c r="G1232"/>
-    </row>
-    <row r="1233" ht="12.75" hidden="1">
-      <c r="A1233" s="11" t="s">
+      <c r="C1233" t="s">
         <v>1778</v>
       </c>
-      <c r="B1233" t="s">
-        <v>1596</v>
-      </c>
-      <c r="C1233" t="s">
+      <c r="D1233"/>
+      <c r="G1233"/>
+    </row>
+    <row r="1234" ht="12.75" hidden="1">
+      <c r="A1234" s="14" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C1234" t="s">
         <v>1595</v>
       </c>
-      <c r="D1233" s="1"/>
-    </row>
-    <row r="1234" ht="12.75" hidden="1">
-      <c r="A1234" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1234" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C1234" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D1234"/>
-      <c r="G1234"/>
+      <c r="D1234" s="1"/>
     </row>
     <row r="1235" ht="12.75" hidden="1">
-      <c r="A1235" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1235" s="1" t="s">
+      <c r="A1235" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1235" t="s">
         <v>1780</v>
       </c>
       <c r="C1235" t="s">
-        <v>1743</v>
-      </c>
-      <c r="D1235" s="1"/>
+        <v>1746</v>
+      </c>
+      <c r="D1235"/>
+      <c r="G1235"/>
     </row>
     <row r="1236" ht="12.75" hidden="1">
-      <c r="A1236" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1236" t="s">
+      <c r="A1236" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1236" s="1" t="s">
         <v>1781</v>
       </c>
       <c r="C1236" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D1236" s="1"/>
+    </row>
+    <row r="1237" ht="12.75" hidden="1">
+      <c r="A1237" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1237" t="s">
         <v>1782</v>
       </c>
-      <c r="D1236"/>
-      <c r="G1236"/>
-    </row>
-    <row r="1237" ht="12.75" hidden="1">
-      <c r="A1237" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1237" s="8" t="s">
+      <c r="C1237" t="s">
         <v>1783</v>
       </c>
-      <c r="C1237" s="8" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D1237" s="1"/>
+      <c r="D1237"/>
+      <c r="G1237"/>
     </row>
     <row r="1238" ht="12.75" hidden="1">
-      <c r="A1238" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1238" t="s">
+      <c r="A1238" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1238" s="8" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C1238" s="8" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D1238" s="1"/>
+    </row>
+    <row r="1239" ht="12.75" hidden="1">
+      <c r="A1239" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1239" t="s">
         <v>299</v>
       </c>
-      <c r="C1238" s="1" t="s">
+      <c r="C1239" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D1238"/>
-      <c r="G1238"/>
-    </row>
-    <row r="1239" ht="12.75" hidden="1">
-      <c r="A1239" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1239" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C1239" t="s">
+      <c r="D1239"/>
+      <c r="G1239"/>
+    </row>
+    <row r="1240" ht="12.75" hidden="1">
+      <c r="A1240" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1240" t="s">
         <v>1785</v>
       </c>
-      <c r="D1239" s="1"/>
-    </row>
-    <row r="1240" ht="12.75" hidden="1">
-      <c r="A1240" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1240" t="s">
+      <c r="C1240" t="s">
         <v>1786</v>
       </c>
-      <c r="C1240" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D1240"/>
-      <c r="G1240"/>
+      <c r="D1240" s="1"/>
     </row>
     <row r="1241" ht="12.75" hidden="1">
-      <c r="A1241" s="11" t="s">
-        <v>1733</v>
+      <c r="A1241" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1241" t="s">
         <v>1787</v>
       </c>
       <c r="C1241" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D1241" s="1"/>
+        <v>1766</v>
+      </c>
+      <c r="D1241"/>
+      <c r="G1241"/>
     </row>
     <row r="1242" ht="12.75" hidden="1">
-      <c r="A1242" s="11" t="s">
-        <v>1733</v>
+      <c r="A1242" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1242" t="s">
         <v>1788</v>
       </c>
       <c r="C1242" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D1242"/>
-      <c r="G1242"/>
+        <v>1748</v>
+      </c>
+      <c r="D1242" s="1"/>
     </row>
     <row r="1243" ht="12.75" hidden="1">
-      <c r="A1243" s="11" t="s">
-        <v>1733</v>
+      <c r="A1243" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1243" t="s">
         <v>1789</v>
       </c>
-      <c r="C1243" s="1" t="s">
-        <v>1777</v>
-      </c>
-      <c r="D1243" s="1"/>
+      <c r="C1243" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D1243"/>
+      <c r="G1243"/>
     </row>
     <row r="1244" ht="12.75" hidden="1">
-      <c r="A1244" s="11" t="s">
-        <v>1733</v>
+      <c r="A1244" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1244" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C1244" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D1244" s="1"/>
+    </row>
+    <row r="1245" ht="12.75" hidden="1">
+      <c r="A1245" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1245" t="s">
         <v>281</v>
       </c>
-      <c r="C1244" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D1244" s="1"/>
-    </row>
-    <row r="1245" ht="12.75" hidden="1">
-      <c r="A1245" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1245" t="s">
-        <v>1790</v>
-      </c>
       <c r="C1245" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D1245" s="1"/>
+    </row>
+    <row r="1246" ht="12.75" hidden="1">
+      <c r="A1246" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C1246" t="s">
         <v>278</v>
       </c>
-      <c r="D1245"/>
-      <c r="G1245"/>
-    </row>
-    <row r="1246" ht="12.75" hidden="1">
-      <c r="A1246" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1246" s="8" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C1246" s="8" t="s">
+      <c r="D1246"/>
+      <c r="G1246"/>
+    </row>
+    <row r="1247" ht="12.75" hidden="1">
+      <c r="A1247" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1247" s="8" t="s">
         <v>1792</v>
       </c>
-      <c r="D1246" s="1"/>
-    </row>
-    <row r="1247" ht="12.75" hidden="1">
-      <c r="A1247" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1247" t="s">
+      <c r="C1247" s="8" t="s">
         <v>1793</v>
       </c>
-      <c r="C1247" s="13" t="s">
-        <v>1737</v>
-      </c>
-      <c r="D1247"/>
-      <c r="G1247"/>
+      <c r="D1247" s="1"/>
     </row>
     <row r="1248" ht="12.75" hidden="1">
-      <c r="A1248" s="11" t="s">
-        <v>1733</v>
+      <c r="A1248" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1248" t="s">
         <v>1794</v>
       </c>
-      <c r="C1248" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D1248" s="1"/>
+      <c r="C1248" s="16" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D1248"/>
+      <c r="G1248"/>
     </row>
     <row r="1249" ht="12.75" hidden="1">
-      <c r="A1249" s="7" t="s">
-        <v>1733</v>
+      <c r="A1249" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1249" t="s">
         <v>1795</v>
       </c>
       <c r="C1249" t="s">
-        <v>1796</v>
-      </c>
-      <c r="D1249"/>
-      <c r="G1249"/>
+        <v>1746</v>
+      </c>
+      <c r="D1249" s="1"/>
     </row>
     <row r="1250" ht="12.75" hidden="1">
       <c r="A1250" s="7" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1250" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C1250" t="s">
         <v>1797</v>
       </c>
-      <c r="C1250" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D1250" s="1"/>
+      <c r="D1250"/>
+      <c r="G1250"/>
     </row>
     <row r="1251" ht="12.75" hidden="1">
       <c r="A1251" s="7" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1251" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C1251" t="s">
         <v>1799</v>
       </c>
-      <c r="C1251" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D1251"/>
-      <c r="G1251"/>
+      <c r="D1251" s="1"/>
     </row>
     <row r="1252" ht="12.75" hidden="1">
       <c r="A1252" s="7" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1252" t="s">
         <v>1800</v>
       </c>
       <c r="C1252" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D1252"/>
+      <c r="G1252"/>
+    </row>
+    <row r="1253" ht="12.75" hidden="1">
+      <c r="A1253" s="7" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1253" t="s">
         <v>1801</v>
       </c>
-      <c r="D1252" s="1"/>
-    </row>
-    <row r="1253" ht="12.75" hidden="1">
-      <c r="A1253" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1253" t="s">
+      <c r="C1253" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D1253" s="1"/>
+    </row>
+    <row r="1254" ht="12.75" hidden="1">
+      <c r="A1254" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1254" t="s">
         <v>295</v>
       </c>
-      <c r="C1253" t="s">
+      <c r="C1254" t="s">
         <v>296</v>
       </c>
-      <c r="D1253"/>
-      <c r="G1253"/>
-    </row>
-    <row r="1254" ht="12.75" hidden="1">
-      <c r="A1254" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1254" t="s">
-        <v>1802</v>
-      </c>
-      <c r="C1254" t="s">
+      <c r="D1254"/>
+      <c r="G1254"/>
+    </row>
+    <row r="1255" ht="12.75" hidden="1">
+      <c r="A1255" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1255" t="s">
         <v>1803</v>
       </c>
-      <c r="D1254" s="1"/>
-    </row>
-    <row r="1255" ht="12.75" hidden="1">
-      <c r="A1255" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1255" t="s">
+      <c r="C1255" t="s">
         <v>1804</v>
       </c>
-      <c r="C1255" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D1255"/>
-      <c r="G1255"/>
+      <c r="D1255" s="1"/>
     </row>
     <row r="1256" ht="12.75" hidden="1">
-      <c r="A1256" s="11" t="s">
-        <v>1733</v>
+      <c r="A1256" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1256" t="s">
         <v>1805</v>
       </c>
       <c r="C1256" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D1256" s="1"/>
+        <v>1748</v>
+      </c>
+      <c r="D1256"/>
+      <c r="G1256"/>
     </row>
     <row r="1257" ht="12.75" hidden="1">
-      <c r="A1257" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1257" s="1" t="s">
+      <c r="A1257" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1257" t="s">
         <v>1806</v>
       </c>
-      <c r="C1257" s="1" t="s">
+      <c r="C1257" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D1257" s="1"/>
+    </row>
+    <row r="1258" ht="12.75" hidden="1">
+      <c r="A1258" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1258" s="1" t="s">
         <v>1807</v>
       </c>
-      <c r="D1257"/>
-      <c r="G1257"/>
-    </row>
-    <row r="1258" ht="12.75" hidden="1">
-      <c r="A1258" s="6" t="s">
-        <v>1586</v>
-      </c>
-      <c r="B1258" t="s">
+      <c r="C1258" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="C1258" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D1258" s="1"/>
+      <c r="D1258"/>
+      <c r="G1258"/>
     </row>
     <row r="1259" ht="12.75" hidden="1">
       <c r="A1259" s="6" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1259" t="s">
         <v>1809</v>
       </c>
-      <c r="B1259" t="s">
+      <c r="C1259" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D1259" s="1"/>
+    </row>
+    <row r="1260" ht="12.75" hidden="1">
+      <c r="A1260" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="C1259" t="s">
+      <c r="B1260" t="s">
         <v>1811</v>
       </c>
-      <c r="D1259"/>
-      <c r="G1259"/>
-    </row>
-    <row r="1260" ht="12.75" hidden="1">
-      <c r="A1260" s="6"/>
-      <c r="B1260"/>
-      <c r="C1260"/>
-      <c r="D1260" s="1"/>
+      <c r="C1260" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D1260"/>
+      <c r="G1260"/>
     </row>
     <row r="1261" ht="12.75" hidden="1">
-      <c r="A1261" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1261" s="9" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C1261" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1261"/>
-      <c r="G1261"/>
+      <c r="A1261" s="6"/>
+      <c r="B1261"/>
+      <c r="C1261"/>
+      <c r="D1261" s="1"/>
     </row>
     <row r="1262" ht="12.75" hidden="1">
       <c r="A1262" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1262" s="1" t="s">
-        <v>1812</v>
-      </c>
-      <c r="C1262" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="D1262" s="1"/>
+        <v>1810</v>
+      </c>
+      <c r="B1262" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1262"/>
+      <c r="G1262"/>
     </row>
     <row r="1263" ht="12.75" hidden="1">
       <c r="A1263" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1263" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1263" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C1263" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="C1263" t="s">
+      <c r="D1263" s="1"/>
+    </row>
+    <row r="1264" ht="12.75" hidden="1">
+      <c r="A1264" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C1264" t="s">
         <v>423</v>
       </c>
-      <c r="D1263" s="1"/>
-    </row>
-    <row r="1264" ht="12.75" hidden="1">
-      <c r="A1264" s="7" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1264" s="1" t="s">
-        <v>1815</v>
-      </c>
-      <c r="C1264" s="1" t="s">
+      <c r="D1264" s="1"/>
+    </row>
+    <row r="1265" ht="12.75" hidden="1">
+      <c r="A1265" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1265" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C1265" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="D1264"/>
-      <c r="G1264"/>
-    </row>
-    <row r="1265" ht="12.75" hidden="1">
-      <c r="A1265" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1265" s="9" t="s">
-        <v>1600</v>
-      </c>
-      <c r="C1265" t="s">
-        <v>423</v>
       </c>
       <c r="D1265"/>
       <c r="G1265"/>
     </row>
     <row r="1266" ht="12.75" hidden="1">
       <c r="A1266" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1266" s="1" t="s">
-        <v>1816</v>
-      </c>
-      <c r="C1266" s="1" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D1266" s="1"/>
+        <v>1810</v>
+      </c>
+      <c r="B1266" s="9" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1266"/>
+      <c r="G1266"/>
     </row>
     <row r="1267" ht="12.75" hidden="1">
       <c r="A1267" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1267" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1267" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C1267" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D1267" s="1"/>
+    </row>
+    <row r="1268" ht="12.75" hidden="1">
+      <c r="A1268" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1268" t="s">
         <v>428</v>
       </c>
-      <c r="C1267" t="s">
+      <c r="C1268" t="s">
         <v>423</v>
       </c>
-      <c r="D1267" s="1"/>
-    </row>
-    <row r="1268" ht="12.75" hidden="1">
-      <c r="A1268" s="7" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1268" t="s">
-        <v>1818</v>
-      </c>
-      <c r="C1268" t="s">
+      <c r="D1268" s="1"/>
+    </row>
+    <row r="1269" ht="12.75" hidden="1">
+      <c r="A1269" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C1269" t="s">
         <v>956</v>
       </c>
-      <c r="D1268"/>
-      <c r="G1268"/>
-    </row>
-    <row r="1269" ht="12.75" hidden="1">
-      <c r="A1269" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1269" s="9" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C1269" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1269" s="1"/>
+      <c r="D1269"/>
+      <c r="G1269"/>
     </row>
     <row r="1270" ht="12.75" hidden="1">
       <c r="A1270" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1270" t="s">
-        <v>1819</v>
+        <v>1810</v>
+      </c>
+      <c r="B1270" s="9" t="s">
+        <v>1606</v>
       </c>
       <c r="C1270" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D1270"/>
-      <c r="G1270"/>
+        <v>423</v>
+      </c>
+      <c r="D1270" s="1"/>
     </row>
     <row r="1271" ht="12.75" hidden="1">
       <c r="A1271" s="6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1271" t="s">
         <v>1820</v>
       </c>
-      <c r="C1271" s="9" t="s">
+      <c r="C1271" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D1271"/>
+      <c r="G1271"/>
+    </row>
+    <row r="1272" ht="12.75" hidden="1">
+      <c r="A1272" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1272" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="D1271" s="1"/>
-    </row>
-    <row r="1272" ht="12.75" hidden="1">
-      <c r="A1272" s="7" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1272" s="1" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C1272" s="1" t="s">
+      <c r="D1272" s="1"/>
+    </row>
+    <row r="1273" ht="12.75" hidden="1">
+      <c r="A1273" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1273" s="1" t="s">
         <v>1822</v>
       </c>
-      <c r="D1272" s="1"/>
-    </row>
-    <row r="1273" ht="12.75" hidden="1">
-      <c r="A1273" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B1273" t="s">
+      <c r="C1273" s="1" t="s">
         <v>1823</v>
       </c>
-      <c r="C1273" s="9" t="s">
-        <v>423</v>
-      </c>
       <c r="D1273" s="1"/>
-      <c r="G1273" s="1"/>
     </row>
     <row r="1274" ht="12.75" hidden="1">
-      <c r="A1274" s="7" t="s">
-        <v>1598</v>
-      </c>
-      <c r="B1274" s="1" t="s">
+      <c r="A1274" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1274" t="s">
         <v>1824</v>
       </c>
       <c r="C1274" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="D1274"/>
-      <c r="G1274"/>
+      <c r="D1274" s="1"/>
+      <c r="G1274" s="1"/>
     </row>
     <row r="1275" ht="12.75" hidden="1">
-      <c r="A1275" s="11" t="s">
+      <c r="A1275" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1275" s="1" t="s">
         <v>1825</v>
       </c>
-      <c r="B1275" s="8" t="s">
+      <c r="C1275" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1275"/>
+      <c r="G1275"/>
+    </row>
+    <row r="1276" ht="12.75" hidden="1">
+      <c r="A1276" s="14" t="s">
         <v>1826</v>
       </c>
-      <c r="C1275" s="8" t="s">
+      <c r="B1276" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="D1275" s="1"/>
-    </row>
-    <row r="1276" ht="12.75" hidden="1">
-      <c r="A1276" s="7" t="s">
-        <v>1665</v>
-      </c>
-      <c r="B1276" s="1" t="s">
+      <c r="C1276" s="8" t="s">
         <v>1828</v>
       </c>
-      <c r="C1276" s="1" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1276"/>
-      <c r="G1276"/>
+      <c r="D1276" s="1"/>
     </row>
     <row r="1277" ht="12.75" hidden="1">
-      <c r="A1277" s="6" t="s">
+      <c r="A1277" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1277" s="1" t="s">
         <v>1829</v>
       </c>
-      <c r="B1277" t="s">
-        <v>1830</v>
-      </c>
-      <c r="C1277" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D1277" s="1"/>
+      <c r="C1277" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D1277"/>
+      <c r="G1277"/>
     </row>
     <row r="1278" ht="12.75" hidden="1">
       <c r="A1278" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1278" t="s">
         <v>1831</v>
       </c>
       <c r="C1278" t="s">
-        <v>1832</v>
-      </c>
-      <c r="D1278"/>
-      <c r="G1278"/>
+        <v>1542</v>
+      </c>
+      <c r="D1278" s="1"/>
     </row>
     <row r="1279" ht="12.75" hidden="1">
       <c r="A1279" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1279" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C1279" t="s">
         <v>1833</v>
       </c>
-      <c r="C1279"/>
-      <c r="D1279" s="1"/>
+      <c r="D1279"/>
+      <c r="G1279"/>
     </row>
     <row r="1280" ht="12.75" hidden="1">
       <c r="A1280" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1280" t="s">
         <v>1834</v>
       </c>
-      <c r="C1280" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1280"/>
-      <c r="G1280"/>
+      <c r="C1280"/>
+      <c r="D1280" s="1"/>
     </row>
     <row r="1281" ht="12.75" hidden="1">
-      <c r="A1281" s="7" t="s">
-        <v>1665</v>
+      <c r="A1281" s="6" t="s">
+        <v>1830</v>
       </c>
       <c r="B1281" t="s">
         <v>1835</v>
       </c>
-      <c r="C1281" s="1" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1281" s="1"/>
+      <c r="C1281" t="s">
+        <v>432</v>
+      </c>
+      <c r="D1281"/>
+      <c r="G1281"/>
     </row>
     <row r="1282" ht="12.75" hidden="1">
-      <c r="A1282" s="6" t="s">
+      <c r="A1282" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1282" t="s">
         <v>1836</v>
       </c>
-      <c r="B1282" t="s">
-        <v>1837</v>
-      </c>
-      <c r="C1282" t="s">
-        <v>1838</v>
-      </c>
-      <c r="D1282"/>
-      <c r="G1282"/>
+      <c r="C1282" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D1282" s="1"/>
     </row>
     <row r="1283" ht="12.75" hidden="1">
       <c r="A1283" s="6" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B1283" s="8" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1283" t="s">
         <v>1839</v>
       </c>
-      <c r="C1283" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1283" s="1"/>
+      <c r="D1283"/>
+      <c r="G1283"/>
     </row>
     <row r="1284" ht="12.75" hidden="1">
       <c r="A1284" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1284" s="8" t="s">
         <v>1840</v>
       </c>
       <c r="C1284" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D1284"/>
-      <c r="G1284"/>
+        <v>432</v>
+      </c>
+      <c r="D1284" s="1"/>
     </row>
     <row r="1285" ht="12.75" hidden="1">
       <c r="A1285" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1285" s="8" t="s">
         <v>1841</v>
       </c>
       <c r="C1285" t="s">
-        <v>497</v>
-      </c>
-      <c r="D1285" s="1"/>
+        <v>1112</v>
+      </c>
+      <c r="D1285"/>
+      <c r="G1285"/>
     </row>
     <row r="1286" ht="12.75" hidden="1">
       <c r="A1286" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1286" s="8" t="s">
         <v>1842</v>
       </c>
       <c r="C1286" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D1286"/>
-      <c r="G1286"/>
+        <v>497</v>
+      </c>
+      <c r="D1286" s="1"/>
     </row>
     <row r="1287" ht="12.75" hidden="1">
       <c r="A1287" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1287" s="8" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C1287" t="s">
         <v>1844</v>
       </c>
-      <c r="C1287" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D1287" s="1"/>
+      <c r="D1287"/>
+      <c r="G1287"/>
     </row>
     <row r="1288" ht="12.75" hidden="1">
       <c r="A1288" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1288" s="8" t="s">
         <v>1845</v>
       </c>
       <c r="C1288" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1288"/>
-      <c r="G1288"/>
+        <v>1123</v>
+      </c>
+      <c r="D1288" s="1"/>
     </row>
     <row r="1289" ht="12.75" hidden="1">
       <c r="A1289" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1289" s="8" t="s">
         <v>1846</v>
       </c>
       <c r="C1289" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D1289" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="D1289"/>
+      <c r="G1289"/>
     </row>
     <row r="1290" ht="12.75" hidden="1">
       <c r="A1290" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1290" s="8" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C1290" t="s">
         <v>1848</v>
       </c>
-      <c r="C1290" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D1290"/>
-      <c r="G1290"/>
+      <c r="D1290" s="1"/>
     </row>
     <row r="1291" ht="12.75" hidden="1">
       <c r="A1291" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1291" s="8" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C1291" t="s">
         <v>1850</v>
       </c>
-      <c r="C1291" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D1291" s="1"/>
+      <c r="D1291"/>
+      <c r="G1291"/>
     </row>
     <row r="1292" ht="12.75" hidden="1">
       <c r="A1292" s="6" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B1292" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1292" s="8" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C1292" t="s">
         <v>1852</v>
       </c>
-      <c r="C1292"/>
-      <c r="D1292"/>
-      <c r="G1292"/>
+      <c r="D1292" s="1"/>
     </row>
     <row r="1293" ht="12.75" hidden="1">
       <c r="A1293" s="6" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B1293" s="8" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1293" t="s">
         <v>1853</v>
       </c>
-      <c r="C1293" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D1293" s="1"/>
+      <c r="C1293"/>
+      <c r="D1293"/>
+      <c r="G1293"/>
     </row>
     <row r="1294" ht="12.75" hidden="1">
       <c r="A1294" s="6" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B1294" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1294" s="8" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C1294" t="s">
         <v>1855</v>
       </c>
-      <c r="C1294" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1294"/>
-      <c r="G1294"/>
+      <c r="D1294" s="1"/>
     </row>
     <row r="1295" ht="12.75" hidden="1">
-      <c r="A1295" s="11" t="s">
-        <v>1733</v>
+      <c r="A1295" s="6" t="s">
+        <v>1837</v>
       </c>
       <c r="B1295" t="s">
         <v>1856</v>
       </c>
       <c r="C1295" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D1295" s="1"/>
+        <v>423</v>
+      </c>
+      <c r="D1295"/>
+      <c r="G1295"/>
     </row>
     <row r="1296" ht="12.75" hidden="1">
-      <c r="A1296" s="11" t="s">
-        <v>1733</v>
+      <c r="A1296" s="14" t="s">
+        <v>1734</v>
       </c>
       <c r="B1296" t="s">
         <v>1857</v>
       </c>
       <c r="C1296" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D1296" s="1"/>
+    </row>
+    <row r="1297" ht="12.75" hidden="1">
+      <c r="A1297" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1297" t="s">
         <v>1858</v>
       </c>
-      <c r="D1296"/>
-      <c r="G1296"/>
-    </row>
-    <row r="1297" ht="12.75" hidden="1">
-      <c r="A1297" s="7" t="s">
+      <c r="C1297" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D1297"/>
+      <c r="G1297"/>
+    </row>
+    <row r="1298" ht="12.75" hidden="1">
+      <c r="A1298" s="7" t="s">
         <v>1342</v>
       </c>
-      <c r="B1297" t="s">
-        <v>1859</v>
-      </c>
-      <c r="C1297" t="s">
+      <c r="B1298" t="s">
         <v>1860</v>
       </c>
-      <c r="D1297" s="1"/>
-    </row>
-    <row r="1298" ht="12.75" hidden="1">
-      <c r="A1298" s="11" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B1298" t="s">
+      <c r="C1298" t="s">
         <v>1861</v>
       </c>
-      <c r="C1298" t="s">
+      <c r="D1298" s="1"/>
+    </row>
+    <row r="1299" ht="12.75" hidden="1">
+      <c r="A1299" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1299" t="s">
         <v>1862</v>
       </c>
-      <c r="D1298"/>
-      <c r="G1298"/>
-    </row>
-    <row r="1299" ht="12.75" hidden="1">
-      <c r="A1299" s="6" t="s">
+      <c r="C1299" t="s">
         <v>1863</v>
       </c>
-      <c r="B1299" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C1299" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1299" s="8"/>
-      <c r="G1299" s="8"/>
+      <c r="D1299"/>
+      <c r="G1299"/>
     </row>
     <row r="1300" ht="12.75" hidden="1">
       <c r="A1300" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1300" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1300" t="s">
         <v>1866</v>
       </c>
-      <c r="C1300" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1300" s="1"/>
+      <c r="D1300" s="8"/>
+      <c r="G1300" s="8"/>
     </row>
     <row r="1301" ht="12.75" hidden="1">
       <c r="A1301" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1301" t="s">
         <v>1867</v>
       </c>
       <c r="C1301" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1301"/>
-      <c r="G1301"/>
+        <v>1866</v>
+      </c>
+      <c r="D1301" s="1"/>
     </row>
     <row r="1302" ht="12.75" hidden="1">
       <c r="A1302" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1302" t="s">
         <v>1868</v>
       </c>
       <c r="C1302" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1302" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1302"/>
+      <c r="G1302"/>
     </row>
     <row r="1303" ht="12.75" hidden="1">
       <c r="A1303" s="6" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B1303" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1303" t="s">
         <v>1869</v>
       </c>
       <c r="C1303" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1303"/>
-      <c r="G1303"/>
+        <v>1866</v>
+      </c>
+      <c r="D1303" s="1"/>
     </row>
     <row r="1304" ht="12.75" hidden="1">
       <c r="A1304" s="6" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B1304" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1304" s="1" t="s">
         <v>1870</v>
       </c>
       <c r="C1304" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1304" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1304"/>
+      <c r="G1304"/>
     </row>
     <row r="1305" ht="12.75" hidden="1">
       <c r="A1305" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1305" t="s">
         <v>1871</v>
       </c>
       <c r="C1305" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1305"/>
-      <c r="G1305"/>
+        <v>1866</v>
+      </c>
+      <c r="D1305" s="1"/>
     </row>
     <row r="1306" ht="12.75" hidden="1">
       <c r="A1306" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1306" t="s">
         <v>1872</v>
       </c>
       <c r="C1306" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="D1306"/>
       <c r="G1306"/>
     </row>
     <row r="1307" ht="12.75" hidden="1">
       <c r="A1307" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1307" t="s">
         <v>1873</v>
       </c>
       <c r="C1307" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1307" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1307"/>
+      <c r="G1307"/>
     </row>
     <row r="1308" ht="12.75" hidden="1">
       <c r="A1308" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1308" t="s">
         <v>1874</v>
       </c>
       <c r="C1308" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1308"/>
-      <c r="G1308"/>
+        <v>1866</v>
+      </c>
+      <c r="D1308" s="1"/>
     </row>
     <row r="1309" ht="12.75" hidden="1">
       <c r="A1309" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1309" t="s">
         <v>1875</v>
       </c>
       <c r="C1309" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1309" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1309"/>
+      <c r="G1309"/>
     </row>
     <row r="1310" ht="12.75" hidden="1">
       <c r="A1310" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1310" t="s">
         <v>1876</v>
       </c>
-      <c r="C1310" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1310"/>
-      <c r="G1310"/>
+      <c r="C1310" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D1310" s="1"/>
     </row>
     <row r="1311" ht="12.75" hidden="1">
       <c r="A1311" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1311" t="s">
         <v>1877</v>
       </c>
       <c r="C1311" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1311" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1311"/>
+      <c r="G1311"/>
     </row>
     <row r="1312" ht="12.75" hidden="1">
       <c r="A1312" s="6" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B1312" s="8" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1312" t="s">
         <v>1878</v>
       </c>
       <c r="C1312" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1312"/>
-      <c r="G1312"/>
+        <v>1866</v>
+      </c>
+      <c r="D1312" s="1"/>
     </row>
     <row r="1313" ht="12.75" hidden="1">
       <c r="A1313" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1313" s="8" t="s">
         <v>1879</v>
       </c>
       <c r="C1313" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1313" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1313"/>
+      <c r="G1313"/>
     </row>
     <row r="1314" ht="12.75" hidden="1">
       <c r="A1314" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1314" s="8" t="s">
         <v>1880</v>
       </c>
       <c r="C1314" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1314"/>
-      <c r="G1314"/>
+        <v>1866</v>
+      </c>
+      <c r="D1314" s="1"/>
     </row>
     <row r="1315" ht="12.75" hidden="1">
       <c r="A1315" s="6" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B1315" s="8"/>
+        <v>1864</v>
+      </c>
+      <c r="B1315" s="8" t="s">
+        <v>1881</v>
+      </c>
       <c r="C1315" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1315" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1315"/>
+      <c r="G1315"/>
     </row>
     <row r="1316" ht="12.75" hidden="1">
       <c r="A1316" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1316" s="8"/>
       <c r="C1316" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1316"/>
-      <c r="G1316"/>
+        <v>1866</v>
+      </c>
+      <c r="D1316" s="1"/>
     </row>
     <row r="1317" ht="12.75" hidden="1">
       <c r="A1317" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1317" s="8"/>
       <c r="C1317" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1317" s="1"/>
+        <v>1866</v>
+      </c>
+      <c r="D1317"/>
+      <c r="G1317"/>
     </row>
     <row r="1318" ht="12.75" hidden="1">
       <c r="A1318" s="6" t="s">
-        <v>1881</v>
-      </c>
-      <c r="B1318" t="s">
-        <v>1882</v>
-      </c>
-      <c r="C1318" t="s">
-        <v>1226</v>
+        <v>1864</v>
+      </c>
+      <c r="B1318" s="8"/>
+      <c r="C1318" s="9" t="s">
+        <v>1866</v>
       </c>
       <c r="D1318" s="1"/>
-      <c r="G1318" s="1"/>
     </row>
     <row r="1319" ht="12.75" hidden="1">
       <c r="A1319" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1319" t="s">
         <v>1883</v>
@@ -24188,24 +24246,25 @@
       <c r="C1319" t="s">
         <v>1226</v>
       </c>
-      <c r="D1319"/>
-      <c r="G1319"/>
+      <c r="D1319" s="1"/>
+      <c r="G1319" s="1"/>
     </row>
     <row r="1320" ht="12.75" hidden="1">
       <c r="A1320" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1320" t="s">
         <v>1884</v>
       </c>
-      <c r="C1320" s="9" t="s">
+      <c r="C1320" t="s">
         <v>1226</v>
       </c>
-      <c r="D1320" s="1"/>
+      <c r="D1320"/>
+      <c r="G1320"/>
     </row>
     <row r="1321" ht="12.75" hidden="1">
       <c r="A1321" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1321" t="s">
         <v>1885</v>
@@ -24213,12 +24272,11 @@
       <c r="C1321" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1321"/>
-      <c r="G1321"/>
+      <c r="D1321" s="1"/>
     </row>
     <row r="1322" ht="12.75" hidden="1">
       <c r="A1322" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1322" t="s">
         <v>1886</v>
@@ -24226,11 +24284,12 @@
       <c r="C1322" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1322" s="1"/>
+      <c r="D1322"/>
+      <c r="G1322"/>
     </row>
     <row r="1323" ht="12.75" hidden="1">
       <c r="A1323" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1323" t="s">
         <v>1887</v>
@@ -24238,12 +24297,11 @@
       <c r="C1323" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1323"/>
-      <c r="G1323"/>
+      <c r="D1323" s="1"/>
     </row>
     <row r="1324" ht="12.75" hidden="1">
       <c r="A1324" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1324" t="s">
         <v>1888</v>
@@ -24251,11 +24309,12 @@
       <c r="C1324" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1324" s="1"/>
+      <c r="D1324"/>
+      <c r="G1324"/>
     </row>
     <row r="1325" ht="12.75" hidden="1">
       <c r="A1325" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1325" t="s">
         <v>1889</v>
@@ -24263,12 +24322,11 @@
       <c r="C1325" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1325"/>
-      <c r="G1325"/>
+      <c r="D1325" s="1"/>
     </row>
     <row r="1326" ht="12.75" hidden="1">
       <c r="A1326" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1326" t="s">
         <v>1890</v>
@@ -24281,7 +24339,7 @@
     </row>
     <row r="1327" ht="12.75" hidden="1">
       <c r="A1327" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1327" t="s">
         <v>1891</v>
@@ -24289,1919 +24347,2042 @@
       <c r="C1327" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1327" s="1"/>
+      <c r="D1327"/>
+      <c r="G1327"/>
     </row>
     <row r="1328" ht="12.75" hidden="1">
       <c r="A1328" s="6" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1328" t="s">
         <v>1892</v>
       </c>
-      <c r="B1328" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C1328" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D1328"/>
-      <c r="G1328"/>
+      <c r="C1328" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D1328" s="1"/>
     </row>
     <row r="1329" ht="12.75" hidden="1">
       <c r="A1329" s="6" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1329" t="s">
-        <v>1882</v>
+        <v>1894</v>
       </c>
       <c r="C1329" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1329" s="1"/>
-      <c r="G1329" s="1"/>
+        <v>1895</v>
+      </c>
+      <c r="D1329"/>
+      <c r="G1329"/>
     </row>
     <row r="1330" ht="12.75" hidden="1">
       <c r="A1330" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1330" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="C1330" s="8" t="s">
-        <v>1895</v>
+        <v>1893</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>1226</v>
       </c>
       <c r="D1330" s="1"/>
       <c r="G1330" s="1"/>
     </row>
     <row r="1331" ht="12.75" hidden="1">
       <c r="A1331" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1331" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C1331" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1331"/>
-      <c r="G1331"/>
+        <v>1893</v>
+      </c>
+      <c r="B1331" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1331" s="8" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D1331" s="1"/>
+      <c r="G1331" s="1"/>
     </row>
     <row r="1332" ht="12.75" hidden="1">
       <c r="A1332" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1332" s="8" t="s">
-        <v>1896</v>
+        <v>1893</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>1884</v>
       </c>
       <c r="C1332" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D1332" s="8"/>
-      <c r="G1332" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1332"/>
+      <c r="G1332"/>
     </row>
     <row r="1333" ht="12.75" hidden="1">
       <c r="A1333" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1333" t="s">
-        <v>1884</v>
+        <v>1893</v>
+      </c>
+      <c r="B1333" s="8" t="s">
+        <v>1897</v>
       </c>
       <c r="C1333" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1333" s="1"/>
+        <v>514</v>
+      </c>
+      <c r="D1333" s="8"/>
+      <c r="G1333" s="8"/>
     </row>
     <row r="1334" ht="12.75" hidden="1">
       <c r="A1334" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1334" s="8" t="s">
-        <v>1897</v>
+        <v>1893</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>1885</v>
       </c>
       <c r="C1334" s="9" t="s">
-        <v>1894</v>
+        <v>1226</v>
       </c>
       <c r="D1334" s="1"/>
     </row>
     <row r="1335" ht="12.75" hidden="1">
       <c r="A1335" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1335" t="s">
-        <v>1885</v>
+        <v>1893</v>
+      </c>
+      <c r="B1335" s="8" t="s">
+        <v>1898</v>
       </c>
       <c r="C1335" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1335"/>
-      <c r="G1335"/>
+        <v>1895</v>
+      </c>
+      <c r="D1335" s="1"/>
     </row>
     <row r="1336" ht="12.75" hidden="1">
       <c r="A1336" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1336" s="8" t="s">
-        <v>1898</v>
+        <v>1893</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>1886</v>
       </c>
       <c r="C1336" s="9" t="s">
-        <v>1899</v>
-      </c>
-      <c r="D1336" s="8"/>
-      <c r="G1336" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1336"/>
+      <c r="G1336"/>
     </row>
     <row r="1337" ht="12.75" hidden="1">
       <c r="A1337" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1337" t="s">
-        <v>1886</v>
+        <v>1893</v>
+      </c>
+      <c r="B1337" s="8" t="s">
+        <v>1899</v>
       </c>
       <c r="C1337" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1337" s="1"/>
+        <v>1900</v>
+      </c>
+      <c r="D1337" s="8"/>
+      <c r="G1337" s="8"/>
     </row>
     <row r="1338" ht="12.75" hidden="1">
       <c r="A1338" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1338" s="8" t="s">
-        <v>1900</v>
+        <v>1893</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>1887</v>
       </c>
       <c r="C1338" s="9" t="s">
-        <v>1901</v>
+        <v>1226</v>
       </c>
       <c r="D1338" s="1"/>
     </row>
     <row r="1339" ht="12.75" hidden="1">
       <c r="A1339" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1339" t="s">
-        <v>1887</v>
+        <v>1893</v>
+      </c>
+      <c r="B1339" s="8" t="s">
+        <v>1901</v>
       </c>
       <c r="C1339" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1339"/>
-      <c r="G1339"/>
+        <v>1902</v>
+      </c>
+      <c r="D1339" s="1"/>
     </row>
     <row r="1340" ht="12.75" hidden="1">
       <c r="A1340" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1340" s="8" t="s">
-        <v>1902</v>
+        <v>1893</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>1888</v>
       </c>
       <c r="C1340" s="9" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D1340" s="8"/>
-      <c r="G1340" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1340"/>
+      <c r="G1340"/>
     </row>
     <row r="1341" ht="12.75" hidden="1">
       <c r="A1341" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1341" t="s">
-        <v>1888</v>
+        <v>1893</v>
+      </c>
+      <c r="B1341" s="8" t="s">
+        <v>1903</v>
       </c>
       <c r="C1341" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1341" s="1"/>
+        <v>1904</v>
+      </c>
+      <c r="D1341" s="8"/>
+      <c r="G1341" s="8"/>
     </row>
     <row r="1342" ht="12.75" hidden="1">
       <c r="A1342" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1342" s="8" t="s">
-        <v>1141</v>
+        <v>1893</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>1889</v>
       </c>
       <c r="C1342" s="9" t="s">
-        <v>1904</v>
+        <v>1226</v>
       </c>
       <c r="D1342" s="1"/>
     </row>
     <row r="1343" ht="12.75" hidden="1">
       <c r="A1343" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1343" t="s">
-        <v>1889</v>
+        <v>1893</v>
+      </c>
+      <c r="B1343" s="8" t="s">
+        <v>1141</v>
       </c>
       <c r="C1343" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1343"/>
-      <c r="G1343"/>
+        <v>1905</v>
+      </c>
+      <c r="D1343" s="1"/>
     </row>
     <row r="1344" ht="12.75" hidden="1">
       <c r="A1344" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1344" s="8" t="s">
-        <v>1905</v>
+        <v>1893</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>1890</v>
       </c>
       <c r="C1344" s="9" t="s">
-        <v>1904</v>
-      </c>
-      <c r="D1344" s="8"/>
-      <c r="G1344" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1344"/>
+      <c r="G1344"/>
     </row>
     <row r="1345" ht="12.75" hidden="1">
       <c r="A1345" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1345" t="s">
-        <v>1890</v>
+        <v>1893</v>
+      </c>
+      <c r="B1345" s="8" t="s">
+        <v>1906</v>
       </c>
       <c r="C1345" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1345" s="1"/>
+        <v>1905</v>
+      </c>
+      <c r="D1345" s="8"/>
+      <c r="G1345" s="8"/>
     </row>
     <row r="1346" ht="12.75" hidden="1">
       <c r="A1346" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1346"/>
-      <c r="C1346" s="9"/>
+        <v>1893</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1346" s="9" t="s">
+        <v>1226</v>
+      </c>
       <c r="D1346" s="1"/>
     </row>
     <row r="1347" ht="12.75" hidden="1">
       <c r="A1347" s="6" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1347"/>
+      <c r="C1347" s="9"/>
+      <c r="D1347" s="1"/>
+    </row>
+    <row r="1348" ht="12.75" hidden="1">
+      <c r="A1348" s="6" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1348" t="s">
         <v>1892</v>
       </c>
-      <c r="B1347" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C1347" s="9" t="s">
+      <c r="C1348" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1347"/>
-      <c r="G1347"/>
-    </row>
-    <row r="1348" ht="12.75" hidden="1">
-      <c r="A1348" s="7" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B1348" t="s">
-        <v>1906</v>
-      </c>
-      <c r="C1348" t="s">
+      <c r="D1348"/>
+      <c r="G1348"/>
+    </row>
+    <row r="1349" ht="12.75" hidden="1">
+      <c r="A1349" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C1349" t="s">
         <v>1531</v>
       </c>
-      <c r="D1348" s="1"/>
-    </row>
-    <row r="1349" ht="12.75" hidden="1">
-      <c r="A1349" s="6" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B1349" t="s">
-        <v>1908</v>
-      </c>
-      <c r="C1349" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1349"/>
-      <c r="G1349"/>
+      <c r="D1349" s="1"/>
     </row>
     <row r="1350" ht="12.75" hidden="1">
       <c r="A1350" s="6" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B1350" s="8" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1350" t="s">
         <v>1909</v>
       </c>
       <c r="C1350" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1350" s="1"/>
+        <v>1793</v>
+      </c>
+      <c r="D1350"/>
+      <c r="G1350"/>
     </row>
     <row r="1351" ht="12.75" hidden="1">
       <c r="A1351" s="6" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B1351" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1351" s="8" t="s">
         <v>1910</v>
       </c>
       <c r="C1351" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1351"/>
-      <c r="G1351"/>
+        <v>1793</v>
+      </c>
+      <c r="D1351" s="1"/>
     </row>
     <row r="1352" ht="12.75" hidden="1">
       <c r="A1352" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1352" t="s">
         <v>1911</v>
       </c>
       <c r="C1352" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1352" s="1"/>
+        <v>1793</v>
+      </c>
+      <c r="D1352"/>
+      <c r="G1352"/>
     </row>
     <row r="1353" ht="12.75" hidden="1">
       <c r="A1353" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1353" t="s">
         <v>1912</v>
       </c>
       <c r="C1353" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1353"/>
-      <c r="G1353"/>
+        <v>1793</v>
+      </c>
+      <c r="D1353" s="1"/>
     </row>
     <row r="1354" ht="12.75" hidden="1">
       <c r="A1354" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1354" t="s">
         <v>1913</v>
       </c>
       <c r="C1354" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D1354"/>
       <c r="G1354"/>
     </row>
     <row r="1355" ht="12.75" hidden="1">
-      <c r="A1355" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1355" s="8" t="s">
+      <c r="A1355" s="6" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1355" t="s">
         <v>1914</v>
       </c>
-      <c r="C1355" s="8" t="s">
+      <c r="C1355" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1355"/>
+      <c r="G1355"/>
+    </row>
+    <row r="1356" ht="12.75" hidden="1">
+      <c r="A1356" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1356" s="8" t="s">
         <v>1915</v>
       </c>
-      <c r="D1355" s="1"/>
-    </row>
-    <row r="1356" ht="12.75" hidden="1">
-      <c r="A1356" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1356" s="8" t="s">
+      <c r="C1356" s="8" t="s">
         <v>1916</v>
       </c>
-      <c r="C1356" t="s">
+      <c r="D1356" s="1"/>
+    </row>
+    <row r="1357" ht="12.75" hidden="1">
+      <c r="A1357" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1357" s="8" t="s">
         <v>1917</v>
       </c>
-      <c r="D1356"/>
-      <c r="G1356"/>
-    </row>
-    <row r="1357" ht="12.75" hidden="1">
-      <c r="A1357" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1357" s="8" t="s">
+      <c r="C1357" t="s">
         <v>1918</v>
       </c>
-      <c r="C1357" t="s">
-        <v>1753</v>
-      </c>
-      <c r="D1357" s="1"/>
+      <c r="D1357"/>
+      <c r="G1357"/>
     </row>
     <row r="1358" ht="12.75" hidden="1">
-      <c r="A1358" s="11" t="s">
-        <v>1825</v>
+      <c r="A1358" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1358" s="8" t="s">
         <v>1919</v>
       </c>
       <c r="C1358" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D1358" s="1"/>
+    </row>
+    <row r="1359" ht="12.75" hidden="1">
+      <c r="A1359" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1359" s="8" t="s">
         <v>1920</v>
       </c>
-      <c r="D1358"/>
-      <c r="G1358"/>
-    </row>
-    <row r="1359" ht="12.75" hidden="1">
-      <c r="A1359" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1359" s="8" t="s">
+      <c r="C1359" t="s">
         <v>1921</v>
       </c>
-      <c r="C1359" t="s">
-        <v>1920</v>
-      </c>
-      <c r="D1359" s="1"/>
+      <c r="D1359"/>
+      <c r="G1359"/>
     </row>
     <row r="1360" ht="12.75" hidden="1">
-      <c r="A1360" s="11" t="s">
-        <v>1825</v>
+      <c r="A1360" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1360" s="8" t="s">
         <v>1922</v>
       </c>
       <c r="C1360" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1360" s="1"/>
+    </row>
+    <row r="1361" ht="12.75" hidden="1">
+      <c r="A1361" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1361" s="8" t="s">
         <v>1923</v>
       </c>
-      <c r="D1360"/>
-      <c r="G1360"/>
-    </row>
-    <row r="1361" ht="12.75" hidden="1">
-      <c r="A1361" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1361" t="s">
+      <c r="C1361" t="s">
         <v>1924</v>
       </c>
-      <c r="C1361" t="s">
+      <c r="D1361"/>
+      <c r="G1361"/>
+    </row>
+    <row r="1362" ht="12.75" hidden="1">
+      <c r="A1362" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1362" t="s">
         <v>1925</v>
       </c>
-      <c r="D1361" s="1"/>
-    </row>
-    <row r="1362" ht="12.75" hidden="1">
-      <c r="A1362" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1362" s="8" t="s">
+      <c r="C1362" t="s">
         <v>1926</v>
       </c>
-      <c r="C1362" t="s">
+      <c r="D1362" s="1"/>
+    </row>
+    <row r="1363" ht="12.75" hidden="1">
+      <c r="A1363" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1363" s="8" t="s">
         <v>1927</v>
       </c>
-      <c r="D1362"/>
-      <c r="G1362"/>
-    </row>
-    <row r="1363" ht="12.75" hidden="1">
-      <c r="A1363" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1363" s="8" t="s">
+      <c r="C1363" t="s">
         <v>1928</v>
       </c>
-      <c r="C1363" t="s">
+      <c r="D1363"/>
+      <c r="G1363"/>
+    </row>
+    <row r="1364" ht="12.75" hidden="1">
+      <c r="A1364" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1364" s="8" t="s">
         <v>1929</v>
       </c>
-      <c r="D1363" s="1"/>
-    </row>
-    <row r="1364" ht="12.75" hidden="1">
-      <c r="A1364" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1364" s="8" t="s">
+      <c r="C1364" t="s">
         <v>1930</v>
       </c>
-      <c r="C1364" t="s">
+      <c r="D1364" s="1"/>
+    </row>
+    <row r="1365" ht="12.75" hidden="1">
+      <c r="A1365" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1365" s="8" t="s">
         <v>1931</v>
       </c>
-      <c r="D1364"/>
-      <c r="G1364"/>
-    </row>
-    <row r="1365" ht="12.75" hidden="1">
-      <c r="A1365" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1365" s="8" t="s">
+      <c r="C1365" t="s">
         <v>1932</v>
       </c>
-      <c r="C1365" t="s">
+      <c r="D1365"/>
+      <c r="G1365"/>
+    </row>
+    <row r="1366" ht="12.75" hidden="1">
+      <c r="A1366" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1366" s="8" t="s">
         <v>1933</v>
       </c>
-      <c r="D1365" s="1"/>
-    </row>
-    <row r="1366" ht="12.75" hidden="1">
-      <c r="A1366" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1366" s="8" t="s">
+      <c r="C1366" t="s">
         <v>1934</v>
       </c>
-      <c r="C1366" s="8" t="s">
+      <c r="D1366" s="1"/>
+    </row>
+    <row r="1367" ht="12.75" hidden="1">
+      <c r="A1367" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1367" s="8" t="s">
         <v>1935</v>
       </c>
-      <c r="D1366"/>
-      <c r="G1366"/>
-    </row>
-    <row r="1367" ht="12.75" hidden="1">
-      <c r="A1367" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1367" s="8" t="s">
+      <c r="C1367" s="8" t="s">
         <v>1936</v>
       </c>
-      <c r="C1367" s="8" t="s">
+      <c r="D1367"/>
+      <c r="G1367"/>
+    </row>
+    <row r="1368" ht="12.75" hidden="1">
+      <c r="A1368" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1368" s="8" t="s">
         <v>1937</v>
-      </c>
-      <c r="D1367" s="1"/>
-    </row>
-    <row r="1368" ht="12.75" hidden="1">
-      <c r="A1368" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1368" s="8" t="s">
-        <v>251</v>
       </c>
       <c r="C1368" s="8" t="s">
         <v>1938</v>
       </c>
-      <c r="D1368"/>
-      <c r="G1368"/>
+      <c r="D1368" s="1"/>
     </row>
     <row r="1369" ht="12.75" hidden="1">
-      <c r="A1369" s="11" t="s">
-        <v>1825</v>
+      <c r="A1369" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1369" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1369" s="8" t="s">
         <v>1939</v>
       </c>
-      <c r="C1369" s="8" t="s">
+      <c r="D1369"/>
+      <c r="G1369"/>
+    </row>
+    <row r="1370" ht="12.75" hidden="1">
+      <c r="A1370" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1370" s="8" t="s">
         <v>1940</v>
       </c>
-      <c r="D1369" s="1"/>
-    </row>
-    <row r="1370" ht="12.75" hidden="1">
-      <c r="A1370" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1370" s="8" t="s">
+      <c r="C1370" s="8" t="s">
         <v>1941</v>
       </c>
-      <c r="C1370" s="8" t="s">
+      <c r="D1370" s="1"/>
+    </row>
+    <row r="1371" ht="12.75" hidden="1">
+      <c r="A1371" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1371" s="8" t="s">
         <v>1942</v>
       </c>
-      <c r="D1370"/>
-      <c r="G1370"/>
-    </row>
-    <row r="1371" ht="12.75" hidden="1">
-      <c r="A1371" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1371" s="8" t="s">
+      <c r="C1371" s="8" t="s">
         <v>1943</v>
       </c>
-      <c r="C1371" s="8" t="s">
+      <c r="D1371"/>
+      <c r="G1371"/>
+    </row>
+    <row r="1372" ht="12.75" hidden="1">
+      <c r="A1372" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1372" s="8" t="s">
         <v>1944</v>
       </c>
-      <c r="D1371" s="1"/>
-    </row>
-    <row r="1372" ht="12.75" hidden="1">
-      <c r="A1372" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1372" s="8" t="s">
+      <c r="C1372" s="8" t="s">
         <v>1945</v>
       </c>
-      <c r="C1372" s="8" t="s">
+      <c r="D1372" s="1"/>
+    </row>
+    <row r="1373" ht="12.75" hidden="1">
+      <c r="A1373" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1373" s="8" t="s">
         <v>1946</v>
       </c>
-      <c r="D1372"/>
-      <c r="G1372"/>
-    </row>
-    <row r="1373" ht="12.75" hidden="1">
-      <c r="A1373" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1373" s="8" t="s">
+      <c r="C1373" s="8" t="s">
         <v>1947</v>
       </c>
-      <c r="C1373" s="8" t="s">
+      <c r="D1373"/>
+      <c r="G1373"/>
+    </row>
+    <row r="1374" ht="12.75" hidden="1">
+      <c r="A1374" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1374" s="8" t="s">
         <v>1948</v>
       </c>
-      <c r="D1373" s="1"/>
-    </row>
-    <row r="1374" ht="12.75" hidden="1">
-      <c r="A1374" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1374" s="8" t="s">
+      <c r="C1374" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="C1374" t="s">
+      <c r="D1374" s="1"/>
+    </row>
+    <row r="1375" ht="12.75" hidden="1">
+      <c r="A1375" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1375" s="8" t="s">
         <v>1950</v>
       </c>
-      <c r="D1374"/>
-      <c r="G1374"/>
-    </row>
-    <row r="1375" ht="12.75" hidden="1">
-      <c r="A1375" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1375" s="8" t="s">
+      <c r="C1375" t="s">
         <v>1951</v>
       </c>
-      <c r="C1375" s="8" t="s">
+      <c r="D1375"/>
+      <c r="G1375"/>
+    </row>
+    <row r="1376" ht="12.75" hidden="1">
+      <c r="A1376" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1376" s="8" t="s">
         <v>1952</v>
       </c>
-      <c r="D1375" s="1"/>
-    </row>
-    <row r="1376" ht="12.75" hidden="1">
-      <c r="A1376" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1376" s="8" t="s">
+      <c r="C1376" s="8" t="s">
         <v>1953</v>
       </c>
-      <c r="C1376" t="s">
-        <v>1777</v>
-      </c>
-      <c r="D1376"/>
-      <c r="G1376"/>
+      <c r="D1376" s="1"/>
     </row>
     <row r="1377" ht="12.75" hidden="1">
-      <c r="A1377" s="11" t="s">
-        <v>1825</v>
+      <c r="A1377" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1377" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="C1377" s="8" t="s">
+      <c r="C1377" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D1377"/>
+      <c r="G1377"/>
+    </row>
+    <row r="1378" ht="12.75" hidden="1">
+      <c r="A1378" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1378" s="8" t="s">
         <v>1955</v>
       </c>
-      <c r="D1377" s="1"/>
-    </row>
-    <row r="1378" ht="12.75" hidden="1">
-      <c r="A1378" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1378" s="8" t="s">
+      <c r="C1378" s="8" t="s">
         <v>1956</v>
       </c>
-      <c r="C1378" t="s">
+      <c r="D1378" s="1"/>
+    </row>
+    <row r="1379" ht="12.75" hidden="1">
+      <c r="A1379" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1379" s="8" t="s">
         <v>1957</v>
       </c>
-      <c r="D1378"/>
-      <c r="G1378"/>
-    </row>
-    <row r="1379" ht="12.75" hidden="1">
-      <c r="A1379" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1379" s="8" t="s">
+      <c r="C1379" t="s">
         <v>1958</v>
       </c>
-      <c r="C1379" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D1379" s="1"/>
+      <c r="D1379"/>
+      <c r="G1379"/>
     </row>
     <row r="1380" ht="12.75" hidden="1">
-      <c r="A1380" s="11" t="s">
-        <v>1825</v>
+      <c r="A1380" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1380" s="8" t="s">
         <v>1959</v>
       </c>
       <c r="C1380" t="s">
-        <v>1955</v>
-      </c>
-      <c r="D1380"/>
-      <c r="G1380"/>
+        <v>1828</v>
+      </c>
+      <c r="D1380" s="1"/>
     </row>
     <row r="1381" ht="12.75" hidden="1">
-      <c r="A1381" s="11" t="s">
-        <v>1825</v>
+      <c r="A1381" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1381" s="8" t="s">
         <v>1960</v>
       </c>
       <c r="C1381" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D1381"/>
+      <c r="G1381"/>
+    </row>
+    <row r="1382" ht="12.75" hidden="1">
+      <c r="A1382" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1382" s="8" t="s">
         <v>1961</v>
       </c>
-      <c r="D1381" s="1"/>
-    </row>
-    <row r="1382" ht="12.75" hidden="1">
-      <c r="A1382" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1382" s="8" t="s">
+      <c r="C1382" t="s">
         <v>1962</v>
       </c>
-      <c r="C1382" t="s">
-        <v>1937</v>
-      </c>
-      <c r="D1382"/>
-      <c r="G1382"/>
+      <c r="D1382" s="1"/>
     </row>
     <row r="1383" ht="12.75" hidden="1">
-      <c r="A1383" s="11" t="s">
-        <v>1825</v>
+      <c r="A1383" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1383" s="8" t="s">
         <v>1963</v>
       </c>
       <c r="C1383" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D1383"/>
+      <c r="G1383"/>
+    </row>
+    <row r="1384" ht="12.75" hidden="1">
+      <c r="A1384" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1384" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="D1383" s="1"/>
-    </row>
-    <row r="1384" ht="12.75" hidden="1">
-      <c r="A1384" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1384" s="8" t="s">
+      <c r="C1384" t="s">
         <v>1965</v>
       </c>
-      <c r="C1384" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D1384"/>
-      <c r="G1384"/>
+      <c r="D1384" s="1"/>
     </row>
     <row r="1385" ht="12.75" hidden="1">
-      <c r="A1385" s="11" t="s">
-        <v>1825</v>
+      <c r="A1385" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1385" s="8" t="s">
         <v>1966</v>
       </c>
       <c r="C1385" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1385"/>
+      <c r="G1385"/>
+    </row>
+    <row r="1386" ht="12.75" hidden="1">
+      <c r="A1386" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1386" s="8" t="s">
         <v>1967</v>
       </c>
-      <c r="D1385" s="1"/>
-    </row>
-    <row r="1386" ht="12.75" hidden="1">
-      <c r="A1386" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1386" s="8" t="s">
+      <c r="C1386" t="s">
         <v>1968</v>
       </c>
-      <c r="C1386" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D1386"/>
-      <c r="G1386"/>
+      <c r="D1386" s="1"/>
     </row>
     <row r="1387" ht="12.75" hidden="1">
-      <c r="A1387" s="11" t="s">
-        <v>1825</v>
+      <c r="A1387" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1387" s="8" t="s">
         <v>1969</v>
       </c>
       <c r="C1387" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D1387"/>
+      <c r="G1387"/>
+    </row>
+    <row r="1388" ht="12.75" hidden="1">
+      <c r="A1388" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1388" s="8" t="s">
         <v>1970</v>
       </c>
-      <c r="D1387" s="1"/>
-    </row>
-    <row r="1388" ht="12.75" hidden="1">
-      <c r="A1388" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1388" s="8" t="s">
+      <c r="C1388" t="s">
         <v>1971</v>
       </c>
-      <c r="C1388" t="s">
+      <c r="D1388" s="1"/>
+    </row>
+    <row r="1389" ht="12.75" hidden="1">
+      <c r="A1389" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1389" s="8" t="s">
         <v>1972</v>
       </c>
-      <c r="D1388"/>
-      <c r="G1388"/>
-    </row>
-    <row r="1389" ht="12.75" hidden="1">
-      <c r="A1389" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1389" s="8" t="s">
+      <c r="C1389" t="s">
         <v>1973</v>
       </c>
-      <c r="C1389" t="s">
-        <v>1955</v>
-      </c>
-      <c r="D1389" s="1"/>
+      <c r="D1389"/>
+      <c r="G1389"/>
     </row>
     <row r="1390" ht="12.75" hidden="1">
-      <c r="A1390" s="11" t="s">
-        <v>1825</v>
+      <c r="A1390" s="14" t="s">
+        <v>1826</v>
       </c>
       <c r="B1390" s="8" t="s">
         <v>1974</v>
       </c>
-      <c r="C1390" s="8" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D1390"/>
-      <c r="G1390"/>
+      <c r="C1390" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D1390" s="1"/>
     </row>
     <row r="1391" ht="12.75" hidden="1">
-      <c r="A1391" s="6" t="s">
+      <c r="A1391" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1391" s="8" t="s">
         <v>1975</v>
       </c>
-      <c r="B1391" s="8" t="s">
-        <v>1976</v>
-      </c>
-      <c r="C1391" t="s">
-        <v>1977</v>
+      <c r="C1391" s="8" t="s">
+        <v>1934</v>
       </c>
       <c r="D1391"/>
       <c r="G1391"/>
     </row>
     <row r="1392" ht="12.75" hidden="1">
       <c r="A1392" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1392" s="8" t="s">
-        <v>1438</v>
+        <v>1977</v>
       </c>
       <c r="C1392" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D1392" s="1"/>
+        <v>1978</v>
+      </c>
+      <c r="D1392"/>
+      <c r="G1392"/>
     </row>
     <row r="1393" ht="12.75" hidden="1">
       <c r="A1393" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1393" s="8" t="s">
-        <v>1978</v>
-      </c>
-      <c r="C1393" s="8" t="s">
-        <v>1979</v>
+        <v>1438</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>1439</v>
       </c>
       <c r="D1393" s="1"/>
     </row>
     <row r="1394" ht="12.75" hidden="1">
       <c r="A1394" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1394" s="8" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C1394" s="8" t="s">
         <v>1980</v>
       </c>
-      <c r="C1394" s="8" t="s">
-        <v>1981</v>
-      </c>
-      <c r="D1394"/>
-      <c r="G1394"/>
+      <c r="D1394" s="1"/>
     </row>
     <row r="1395" ht="12.75" hidden="1">
       <c r="A1395" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1395" s="8" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C1395" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C1395" s="8" t="s">
         <v>1982</v>
       </c>
-      <c r="D1395" s="1"/>
+      <c r="D1395"/>
+      <c r="G1395"/>
     </row>
     <row r="1396" ht="12.75" hidden="1">
       <c r="A1396" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1396" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C1396" t="s">
         <v>1983</v>
-      </c>
-      <c r="C1396" s="8" t="s">
-        <v>1979</v>
       </c>
       <c r="D1396" s="1"/>
     </row>
     <row r="1397" ht="12.75" hidden="1">
       <c r="A1397" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1397" s="8" t="s">
         <v>1984</v>
       </c>
-      <c r="C1397" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D1397"/>
-      <c r="G1397"/>
+      <c r="C1397" s="8" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D1397" s="1"/>
     </row>
     <row r="1398" ht="12.75" hidden="1">
       <c r="A1398" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1398" s="8" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C1398" t="s">
         <v>1986</v>
       </c>
-      <c r="C1398" t="s">
-        <v>1987</v>
-      </c>
-      <c r="D1398" s="1"/>
+      <c r="D1398"/>
+      <c r="G1398"/>
     </row>
     <row r="1399" ht="12.75" hidden="1">
       <c r="A1399" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1399" s="8" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C1399" t="s">
         <v>1988</v>
       </c>
-      <c r="C1399" s="8" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D1399"/>
-      <c r="G1399"/>
+      <c r="D1399" s="1"/>
     </row>
     <row r="1400" ht="12.75" hidden="1">
       <c r="A1400" s="6" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B1400" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1400" s="8" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C1400" s="8" t="s">
         <v>1990</v>
       </c>
-      <c r="C1400" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1400" s="1"/>
+      <c r="D1400"/>
+      <c r="G1400"/>
     </row>
     <row r="1401" ht="12.75" hidden="1">
       <c r="A1401" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1401" t="s">
         <v>1991</v>
       </c>
       <c r="C1401" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1401"/>
-      <c r="G1401"/>
+        <v>1793</v>
+      </c>
+      <c r="D1401" s="1"/>
     </row>
     <row r="1402" ht="12.75" hidden="1">
       <c r="A1402" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1402" t="s">
         <v>1992</v>
       </c>
       <c r="C1402" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D1402"/>
       <c r="G1402"/>
     </row>
     <row r="1403" ht="12.75" hidden="1">
       <c r="A1403" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1403" t="s">
         <v>1993</v>
       </c>
       <c r="C1403" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1403" s="1"/>
+        <v>1793</v>
+      </c>
+      <c r="D1403"/>
+      <c r="G1403"/>
     </row>
     <row r="1404" ht="12.75" hidden="1">
       <c r="A1404" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1404" t="s">
         <v>1994</v>
       </c>
-      <c r="C1404" s="9" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D1404"/>
-      <c r="G1404"/>
+      <c r="C1404" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1404" s="1"/>
     </row>
     <row r="1405" ht="12.75" hidden="1">
-      <c r="A1405" s="7" t="s">
-        <v>1598</v>
-      </c>
-      <c r="B1405" s="9" t="s">
-        <v>1820</v>
+      <c r="A1405" s="6" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1995</v>
       </c>
       <c r="C1405" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1405" s="1"/>
+        <v>1793</v>
+      </c>
+      <c r="D1405"/>
+      <c r="G1405"/>
     </row>
     <row r="1406" ht="12.75" hidden="1">
       <c r="A1406" s="7" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B1406" t="s">
-        <v>1995</v>
-      </c>
-      <c r="C1406" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D1406"/>
-      <c r="G1406"/>
+        <v>1599</v>
+      </c>
+      <c r="B1406" s="9" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1406" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1406" s="1"/>
     </row>
     <row r="1407" ht="12.75" hidden="1">
       <c r="A1407" s="7" t="s">
         <v>1420</v>
       </c>
       <c r="B1407" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1407" t="s">
         <v>1997</v>
       </c>
-      <c r="C1407" t="s">
+      <c r="D1407"/>
+      <c r="G1407"/>
+    </row>
+    <row r="1408" ht="12.75" hidden="1">
+      <c r="A1408" s="7" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B1408" t="s">
         <v>1998</v>
       </c>
-      <c r="D1407" s="1"/>
-    </row>
-    <row r="1408" ht="12.75" hidden="1">
-      <c r="A1408" s="6" t="s">
+      <c r="C1408" t="s">
         <v>1999</v>
       </c>
-      <c r="B1408" t="s">
-        <v>2000</v>
-      </c>
-      <c r="C1408" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D1408"/>
-      <c r="G1408"/>
+      <c r="D1408" s="1"/>
     </row>
     <row r="1409" ht="12.75" hidden="1">
       <c r="A1409" s="6" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B1409" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C1409" t="s">
         <v>2002</v>
       </c>
-      <c r="C1409" t="s">
-        <v>2003</v>
-      </c>
-      <c r="D1409" s="1"/>
+      <c r="D1409"/>
+      <c r="G1409"/>
     </row>
     <row r="1410" ht="12.75" hidden="1">
       <c r="A1410" s="6" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1410" t="s">
         <v>2004</v>
       </c>
-      <c r="B1410" t="s">
-        <v>2005</v>
-      </c>
-      <c r="C1410" s="8" t="s">
-        <v>2006</v>
-      </c>
       <c r="D1410" s="1"/>
-      <c r="G1410" s="1"/>
     </row>
     <row r="1411" ht="12.75" hidden="1">
       <c r="A1411" s="6" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B1411" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C1411" s="8" t="s">
         <v>2007</v>
       </c>
-      <c r="C1411" t="s">
-        <v>2008</v>
-      </c>
-      <c r="D1411"/>
-      <c r="G1411"/>
+      <c r="D1411" s="1"/>
+      <c r="G1411" s="1"/>
     </row>
     <row r="1412" ht="12.75" hidden="1">
       <c r="A1412" s="6" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B1412" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C1412" t="s">
         <v>2009</v>
       </c>
-      <c r="C1412" t="s">
+      <c r="D1412"/>
+      <c r="G1412"/>
+    </row>
+    <row r="1413" ht="12.75" hidden="1">
+      <c r="A1413" s="6" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1413" t="s">
         <v>2010</v>
       </c>
-      <c r="D1412" s="1"/>
-      <c r="G1412" s="1"/>
-    </row>
-    <row r="1413" ht="12.75" hidden="1">
-      <c r="A1413" s="6"/>
-      <c r="B1413" t="s">
+      <c r="C1413" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D1413" s="1"/>
+      <c r="G1413" s="1"/>
+    </row>
+    <row r="1414" ht="12.75" hidden="1">
+      <c r="A1414" s="6"/>
+      <c r="B1414" t="s">
         <v>1471</v>
       </c>
-      <c r="C1413" t="s">
+      <c r="C1414" t="s">
         <v>1472</v>
       </c>
-      <c r="D1413"/>
-      <c r="G1413"/>
-    </row>
-    <row r="1414" ht="12.75" hidden="1">
-      <c r="A1414" s="6" t="s">
-        <v>1975</v>
-      </c>
-      <c r="B1414" t="s">
-        <v>2011</v>
-      </c>
-      <c r="C1414" s="9" t="s">
-        <v>1977</v>
-      </c>
-      <c r="D1414" s="1"/>
+      <c r="D1414"/>
+      <c r="G1414"/>
     </row>
     <row r="1415" ht="12.75" hidden="1">
       <c r="A1415" s="6" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1415" t="s">
         <v>2012</v>
       </c>
-      <c r="C1415" t="s">
-        <v>1979</v>
-      </c>
-      <c r="D1415"/>
-      <c r="G1415"/>
+      <c r="C1415" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D1415" s="1"/>
     </row>
     <row r="1416" ht="12.75" hidden="1">
-      <c r="A1416" s="7" t="s">
-        <v>749</v>
+      <c r="A1416" s="6" t="s">
+        <v>1976</v>
       </c>
       <c r="B1416" t="s">
         <v>2013</v>
       </c>
       <c r="C1416" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D1416"/>
+      <c r="G1416"/>
+    </row>
+    <row r="1417" ht="12.75" hidden="1">
+      <c r="A1417" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1417" t="s">
         <v>759</v>
       </c>
-      <c r="D1416" s="1"/>
-    </row>
-    <row r="1417" ht="12.75">
-      <c r="A1417" s="14" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B1417" t="s">
+      <c r="D1417" s="1"/>
+    </row>
+    <row r="1418" ht="12.75" hidden="1">
+      <c r="A1418" s="7" t="s">
         <v>2015</v>
       </c>
-      <c r="C1417" t="s">
+      <c r="B1418" t="s">
         <v>2016</v>
       </c>
-      <c r="D1417"/>
-      <c r="G1417"/>
-    </row>
-    <row r="1418" ht="12.75">
-      <c r="A1418" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B1418" t="s">
+      <c r="C1418" t="s">
         <v>2017</v>
       </c>
-      <c r="C1418" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1418" s="1"/>
-    </row>
-    <row r="1419" ht="12.75">
+      <c r="D1418"/>
+      <c r="G1418"/>
+    </row>
+    <row r="1419" ht="12.75" hidden="1">
       <c r="A1419" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1419" t="s">
         <v>2018</v>
       </c>
       <c r="C1419" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1419"/>
-      <c r="G1419"/>
-    </row>
-    <row r="1420" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1419" s="1"/>
+    </row>
+    <row r="1420" ht="12.75" hidden="1">
       <c r="A1420" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1420" t="s">
         <v>2019</v>
       </c>
-      <c r="C1420" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1420" s="1"/>
-    </row>
-    <row r="1421" ht="12.75">
+      <c r="C1420" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1420"/>
+      <c r="G1420"/>
+    </row>
+    <row r="1421" ht="12.75" hidden="1">
       <c r="A1421" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1421" t="s">
         <v>2020</v>
       </c>
       <c r="C1421" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1421"/>
-      <c r="G1421"/>
-    </row>
-    <row r="1422" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1421" s="1"/>
+    </row>
+    <row r="1422" ht="12.75" hidden="1">
       <c r="A1422" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1422" t="s">
         <v>2021</v>
       </c>
       <c r="C1422" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1422" s="1"/>
-    </row>
-    <row r="1423" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1422"/>
+      <c r="G1422"/>
+    </row>
+    <row r="1423" ht="12.75" hidden="1">
       <c r="A1423" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1423" t="s">
         <v>2022</v>
       </c>
       <c r="C1423" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1423"/>
-      <c r="G1423"/>
-    </row>
-    <row r="1424" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1423" s="1"/>
+    </row>
+    <row r="1424" ht="12.75" hidden="1">
       <c r="A1424" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1424" t="s">
         <v>2023</v>
       </c>
       <c r="C1424" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1424" s="1"/>
-    </row>
-    <row r="1425" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1424"/>
+      <c r="G1424"/>
+    </row>
+    <row r="1425" ht="12.75" hidden="1">
       <c r="A1425" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1425" t="s">
         <v>2024</v>
       </c>
       <c r="C1425" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1425"/>
-      <c r="G1425"/>
-    </row>
-    <row r="1426" ht="12.75">
-      <c r="A1426" s="14" t="s">
-        <v>2014</v>
+        <v>2017</v>
+      </c>
+      <c r="D1425" s="1"/>
+    </row>
+    <row r="1426" ht="12.75" hidden="1">
+      <c r="A1426" s="7" t="s">
+        <v>2015</v>
       </c>
       <c r="B1426" t="s">
         <v>2025</v>
       </c>
       <c r="C1426" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1426" s="1"/>
-    </row>
-    <row r="1427" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1426"/>
+      <c r="G1426"/>
+    </row>
+    <row r="1427" ht="12.75" hidden="1">
       <c r="A1427" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1427" t="s">
         <v>2026</v>
       </c>
       <c r="C1427" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1427"/>
-      <c r="G1427"/>
-    </row>
-    <row r="1428" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1427" s="1"/>
+    </row>
+    <row r="1428" ht="12.75" hidden="1">
       <c r="A1428" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1428" t="s">
         <v>2027</v>
       </c>
       <c r="C1428" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1428" s="1"/>
-    </row>
-    <row r="1429" ht="12.75">
-      <c r="A1429" s="14" t="s">
-        <v>2014</v>
+        <v>2017</v>
+      </c>
+      <c r="D1428"/>
+      <c r="G1428"/>
+    </row>
+    <row r="1429" ht="12.75" hidden="1">
+      <c r="A1429" s="7" t="s">
+        <v>2015</v>
       </c>
       <c r="B1429" t="s">
         <v>2028</v>
       </c>
       <c r="C1429" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1429"/>
-      <c r="G1429"/>
-    </row>
-    <row r="1430" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1429" s="1"/>
+    </row>
+    <row r="1430" ht="12.75" hidden="1">
       <c r="A1430" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1430" t="s">
         <v>2029</v>
       </c>
       <c r="C1430" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1430" s="1"/>
-    </row>
-    <row r="1431" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1430"/>
+      <c r="G1430"/>
+    </row>
+    <row r="1431" ht="12.75" hidden="1">
       <c r="A1431" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1431" t="s">
         <v>2030</v>
       </c>
       <c r="C1431" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1431"/>
-      <c r="G1431"/>
-    </row>
-    <row r="1432" ht="12.75">
-      <c r="A1432" s="14" t="s">
-        <v>2014</v>
+        <v>2017</v>
+      </c>
+      <c r="D1431" s="1"/>
+    </row>
+    <row r="1432" ht="12.75" hidden="1">
+      <c r="A1432" s="7" t="s">
+        <v>2015</v>
       </c>
       <c r="B1432" t="s">
         <v>2031</v>
       </c>
       <c r="C1432" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1432" s="1"/>
-    </row>
-    <row r="1433" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1432"/>
+      <c r="G1432"/>
+    </row>
+    <row r="1433" ht="12.75" hidden="1">
       <c r="A1433" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1433" t="s">
         <v>2032</v>
       </c>
       <c r="C1433" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1433"/>
-      <c r="G1433"/>
-    </row>
-    <row r="1434" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1433" s="1"/>
+    </row>
+    <row r="1434" ht="12.75" hidden="1">
       <c r="A1434" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1434" t="s">
         <v>2033</v>
       </c>
       <c r="C1434" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1434" s="1"/>
-    </row>
-    <row r="1435" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1434"/>
+      <c r="G1434"/>
+    </row>
+    <row r="1435" ht="12.75" hidden="1">
       <c r="A1435" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1435" t="s">
         <v>2034</v>
       </c>
       <c r="C1435" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1435"/>
-      <c r="G1435"/>
-    </row>
-    <row r="1436" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1435" s="1"/>
+    </row>
+    <row r="1436" ht="12.75" hidden="1">
       <c r="A1436" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1436" t="s">
         <v>2035</v>
       </c>
       <c r="C1436" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1436" s="1"/>
-    </row>
-    <row r="1437" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1436"/>
+      <c r="G1436"/>
+    </row>
+    <row r="1437" ht="12.75" hidden="1">
       <c r="A1437" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1437" t="s">
         <v>2036</v>
       </c>
       <c r="C1437" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1437"/>
-      <c r="G1437"/>
-    </row>
-    <row r="1438" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1437" s="1"/>
+    </row>
+    <row r="1438" ht="12.75" hidden="1">
       <c r="A1438" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1438" t="s">
         <v>2037</v>
       </c>
       <c r="C1438" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1438" s="1"/>
-    </row>
-    <row r="1439" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1438"/>
+      <c r="G1438"/>
+    </row>
+    <row r="1439" ht="12.75" hidden="1">
       <c r="A1439" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1439" t="s">
         <v>2038</v>
       </c>
       <c r="C1439" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1439"/>
-      <c r="G1439"/>
-    </row>
-    <row r="1440" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1439" s="1"/>
+    </row>
+    <row r="1440" ht="12.75" hidden="1">
       <c r="A1440" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B1440"/>
+        <v>2015</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>2039</v>
+      </c>
       <c r="C1440" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1440" s="1"/>
-    </row>
-    <row r="1441" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1440"/>
+      <c r="G1440"/>
+    </row>
+    <row r="1441" ht="12.75" hidden="1">
       <c r="A1441" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B1441"/>
+        <v>2015</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>2040</v>
+      </c>
       <c r="C1441" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1441"/>
-      <c r="G1441"/>
-    </row>
-    <row r="1442" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1441" s="1"/>
+    </row>
+    <row r="1442" ht="12.75" hidden="1">
       <c r="A1442" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B1442"/>
+        <v>2015</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>2041</v>
+      </c>
       <c r="C1442" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1442" s="1"/>
-    </row>
-    <row r="1443" ht="12.75">
+        <v>2017</v>
+      </c>
+      <c r="D1442"/>
+      <c r="G1442"/>
+    </row>
+    <row r="1443" ht="12.75" hidden="1">
       <c r="A1443" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B1443"/>
+        <v>2015</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>2042</v>
+      </c>
       <c r="C1443" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D1443"/>
-      <c r="G1443"/>
-    </row>
-    <row r="1444" ht="12.75">
-      <c r="A1444" s="6"/>
-      <c r="B1444"/>
-      <c r="C1444"/>
-      <c r="D1444" s="1"/>
-    </row>
-    <row r="1445" ht="12.75">
-      <c r="A1445" s="6"/>
-      <c r="B1445"/>
-      <c r="C1445"/>
-      <c r="D1445"/>
-      <c r="G1445"/>
-    </row>
-    <row r="1446" ht="12.75">
-      <c r="A1446" s="6"/>
-      <c r="B1446"/>
-      <c r="C1446"/>
-      <c r="D1446" s="1"/>
-    </row>
-    <row r="1447" ht="12.75">
-      <c r="A1447" s="6"/>
-      <c r="B1447"/>
-      <c r="C1447"/>
-      <c r="D1447"/>
-      <c r="G1447"/>
-    </row>
-    <row r="1448" ht="12.75">
-      <c r="A1448" s="6"/>
-      <c r="B1448"/>
-      <c r="C1448"/>
-      <c r="D1448" s="1"/>
-    </row>
-    <row r="1449" ht="12.75">
-      <c r="A1449" s="6"/>
-      <c r="B1449"/>
-      <c r="C1449"/>
-      <c r="D1449"/>
-      <c r="G1449"/>
-    </row>
-    <row r="1450" ht="12.75">
-      <c r="A1450" s="6"/>
-      <c r="B1450"/>
-      <c r="C1450"/>
-      <c r="D1450" s="1"/>
-    </row>
-    <row r="1451" ht="12.75">
-      <c r="A1451" s="6"/>
-      <c r="B1451"/>
-      <c r="C1451"/>
-      <c r="D1451"/>
-      <c r="G1451"/>
-    </row>
-    <row r="1452" ht="12.75">
-      <c r="A1452" s="6"/>
-      <c r="B1452"/>
-      <c r="C1452"/>
-      <c r="D1452" s="1"/>
-    </row>
-    <row r="1453" ht="12.75">
-      <c r="A1453" s="6"/>
-      <c r="B1453"/>
-      <c r="C1453"/>
-      <c r="D1453"/>
-      <c r="G1453"/>
-    </row>
-    <row r="1454" ht="12.75">
-      <c r="A1454" s="6"/>
-      <c r="B1454"/>
-      <c r="C1454"/>
-      <c r="D1454" s="1"/>
-    </row>
-    <row r="1455" ht="12.75">
-      <c r="A1455" s="6"/>
-      <c r="B1455"/>
-      <c r="C1455"/>
-      <c r="D1455"/>
-      <c r="G1455"/>
-    </row>
-    <row r="1456" ht="12.75">
-      <c r="A1456" s="6"/>
-      <c r="B1456"/>
-      <c r="C1456"/>
-      <c r="D1456" s="1"/>
-    </row>
-    <row r="1457" ht="12.75">
-      <c r="A1457" s="6"/>
-      <c r="B1457"/>
-      <c r="C1457"/>
-      <c r="D1457"/>
-      <c r="G1457"/>
-    </row>
-    <row r="1458" ht="12.75">
-      <c r="A1458" s="6"/>
-      <c r="B1458"/>
-      <c r="C1458"/>
-      <c r="D1458" s="1"/>
-    </row>
-    <row r="1459" ht="12.75">
-      <c r="A1459" s="6"/>
-      <c r="B1459"/>
-      <c r="C1459"/>
-      <c r="D1459"/>
-      <c r="G1459"/>
-    </row>
-    <row r="1460" ht="12.75">
-      <c r="A1460" s="6"/>
-      <c r="B1460"/>
-      <c r="C1460"/>
-      <c r="D1460" s="1"/>
-    </row>
-    <row r="1461" ht="12.75">
-      <c r="A1461" s="6"/>
-      <c r="B1461"/>
-      <c r="C1461"/>
-      <c r="D1461"/>
-      <c r="G1461"/>
-    </row>
-    <row r="1462" ht="12.75">
-      <c r="A1462" s="6"/>
-      <c r="B1462"/>
-      <c r="C1462"/>
-      <c r="D1462" s="1"/>
+        <v>2017</v>
+      </c>
+      <c r="D1443" s="1"/>
+    </row>
+    <row r="1444" ht="12.75" hidden="1">
+      <c r="A1444" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1444" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1444"/>
+      <c r="G1444"/>
+    </row>
+    <row r="1445" ht="12.75" hidden="1">
+      <c r="A1445" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C1445" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1445" s="1"/>
+    </row>
+    <row r="1446" ht="12.75" hidden="1">
+      <c r="A1446" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1446" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1446"/>
+      <c r="G1446"/>
+    </row>
+    <row r="1447" ht="12.75" hidden="1">
+      <c r="A1447" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C1447" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1447" s="1"/>
+    </row>
+    <row r="1448" ht="12.75" hidden="1">
+      <c r="A1448" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C1448" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1448"/>
+      <c r="G1448"/>
+    </row>
+    <row r="1449" ht="12.75" hidden="1">
+      <c r="A1449" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C1449" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1449" s="1"/>
+    </row>
+    <row r="1450" ht="12.75" hidden="1">
+      <c r="A1450" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C1450" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1450"/>
+      <c r="G1450"/>
+    </row>
+    <row r="1451" ht="12.75" hidden="1">
+      <c r="A1451" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C1451" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1451" s="1"/>
+    </row>
+    <row r="1452" ht="12.75" hidden="1">
+      <c r="A1452" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C1452" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1452"/>
+      <c r="G1452"/>
+    </row>
+    <row r="1453" ht="12.75" hidden="1">
+      <c r="A1453" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1453" s="8" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C1453" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1453" s="1"/>
+    </row>
+    <row r="1454" ht="12.75" hidden="1">
+      <c r="A1454" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1454" s="8" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1454" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1454"/>
+      <c r="G1454"/>
+    </row>
+    <row r="1455" ht="12.75" hidden="1">
+      <c r="A1455" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1455" s="8" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C1455" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1455" s="1"/>
+    </row>
+    <row r="1456" ht="12.75" hidden="1">
+      <c r="A1456" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1456" s="8" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C1456" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1456"/>
+      <c r="G1456"/>
+    </row>
+    <row r="1457" ht="12.75" hidden="1">
+      <c r="A1457" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1457" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C1457" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1457" s="1"/>
+    </row>
+    <row r="1458" ht="12.75" hidden="1">
+      <c r="A1458" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1458" s="8" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C1458" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1458"/>
+      <c r="G1458"/>
+    </row>
+    <row r="1459" ht="12.75" hidden="1">
+      <c r="A1459" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1459" s="8"/>
+      <c r="C1459" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1459" s="1"/>
+    </row>
+    <row r="1460" ht="12.75" hidden="1">
+      <c r="A1460" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1460" s="8"/>
+      <c r="C1460" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1460"/>
+      <c r="G1460"/>
+    </row>
+    <row r="1461" ht="12.75" hidden="1">
+      <c r="A1461" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1461" s="8"/>
+      <c r="C1461" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1461" s="1"/>
+    </row>
+    <row r="1462" ht="12.75" hidden="1">
+      <c r="A1462" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1462" s="8"/>
+      <c r="C1462" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1462"/>
+      <c r="G1462"/>
     </row>
     <row r="1463" ht="12.75">
-      <c r="A1463" s="6"/>
-      <c r="B1463"/>
-      <c r="C1463"/>
-      <c r="D1463"/>
-      <c r="G1463"/>
+      <c r="A1463" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D1463" s="1"/>
     </row>
     <row r="1464" ht="12.75">
       <c r="A1464" s="6"/>
       <c r="B1464"/>
       <c r="C1464"/>
-      <c r="D1464" s="1"/>
+      <c r="D1464"/>
+      <c r="G1464"/>
     </row>
     <row r="1465" ht="12.75">
       <c r="A1465" s="6"/>
       <c r="B1465"/>
       <c r="C1465"/>
-      <c r="D1465"/>
-      <c r="G1465"/>
+      <c r="D1465" s="1"/>
     </row>
     <row r="1466" ht="12.75">
       <c r="A1466" s="6"/>
       <c r="B1466"/>
       <c r="C1466"/>
-      <c r="D1466" s="1"/>
+      <c r="D1466"/>
+      <c r="G1466"/>
     </row>
     <row r="1467" ht="12.75">
       <c r="A1467" s="6"/>
       <c r="B1467"/>
       <c r="C1467"/>
-      <c r="D1467"/>
-      <c r="G1467"/>
+      <c r="D1467" s="1"/>
     </row>
     <row r="1468" ht="12.75">
       <c r="A1468" s="6"/>
       <c r="B1468"/>
       <c r="C1468"/>
-      <c r="D1468" s="1"/>
+      <c r="D1468"/>
+      <c r="G1468"/>
     </row>
     <row r="1469" ht="12.75">
       <c r="A1469" s="6"/>
       <c r="B1469"/>
       <c r="C1469"/>
-      <c r="D1469"/>
-      <c r="G1469"/>
+      <c r="D1469" s="1"/>
     </row>
     <row r="1470" ht="12.75">
       <c r="A1470" s="6"/>
       <c r="B1470"/>
       <c r="C1470"/>
-      <c r="D1470" s="1"/>
+      <c r="D1470"/>
+      <c r="G1470"/>
     </row>
     <row r="1471" ht="12.75">
       <c r="A1471" s="6"/>
       <c r="B1471"/>
       <c r="C1471"/>
-      <c r="D1471"/>
-      <c r="G1471"/>
+      <c r="D1471" s="1"/>
     </row>
     <row r="1472" ht="12.75">
       <c r="A1472" s="6"/>
       <c r="B1472"/>
       <c r="C1472"/>
-      <c r="D1472" s="1"/>
+      <c r="D1472"/>
+      <c r="G1472"/>
     </row>
     <row r="1473" ht="12.75">
       <c r="A1473" s="6"/>
       <c r="B1473"/>
       <c r="C1473"/>
-      <c r="D1473"/>
-      <c r="G1473"/>
+      <c r="D1473" s="1"/>
     </row>
     <row r="1474" ht="12.75">
       <c r="A1474" s="6"/>
       <c r="B1474"/>
       <c r="C1474"/>
-      <c r="D1474" s="1"/>
+      <c r="D1474"/>
+      <c r="G1474"/>
     </row>
     <row r="1475" ht="12.75">
       <c r="A1475" s="6"/>
       <c r="B1475"/>
       <c r="C1475"/>
-      <c r="D1475"/>
-      <c r="G1475"/>
+      <c r="D1475" s="1"/>
     </row>
     <row r="1476" ht="12.75">
       <c r="A1476" s="6"/>
       <c r="B1476"/>
       <c r="C1476"/>
-      <c r="D1476" s="1"/>
+      <c r="D1476"/>
+      <c r="G1476"/>
     </row>
     <row r="1477" ht="12.75">
       <c r="A1477" s="6"/>
       <c r="B1477"/>
       <c r="C1477"/>
-      <c r="D1477"/>
-      <c r="G1477"/>
+      <c r="D1477" s="1"/>
     </row>
     <row r="1478" ht="12.75">
       <c r="A1478" s="6"/>
       <c r="B1478"/>
       <c r="C1478"/>
-      <c r="D1478" s="1"/>
+      <c r="D1478"/>
+      <c r="G1478"/>
     </row>
     <row r="1479" ht="12.75">
       <c r="A1479" s="6"/>
       <c r="B1479"/>
       <c r="C1479"/>
-      <c r="D1479"/>
-      <c r="G1479"/>
+      <c r="D1479" s="1"/>
     </row>
     <row r="1480" ht="12.75">
       <c r="A1480" s="6"/>
       <c r="B1480"/>
       <c r="C1480"/>
-      <c r="D1480" s="1"/>
+      <c r="D1480"/>
+      <c r="G1480"/>
     </row>
     <row r="1481" ht="12.75">
       <c r="A1481" s="6"/>
       <c r="B1481"/>
       <c r="C1481"/>
-      <c r="D1481"/>
-      <c r="G1481"/>
+      <c r="D1481" s="1"/>
     </row>
     <row r="1482" ht="12.75">
       <c r="A1482" s="6"/>
       <c r="B1482"/>
       <c r="C1482"/>
-      <c r="D1482" s="1"/>
+      <c r="D1482"/>
+      <c r="G1482"/>
     </row>
     <row r="1483" ht="12.75">
       <c r="A1483" s="6"/>
       <c r="B1483"/>
       <c r="C1483"/>
-      <c r="D1483"/>
-      <c r="G1483"/>
+      <c r="D1483" s="1"/>
     </row>
     <row r="1484" ht="12.75">
       <c r="A1484" s="6"/>
       <c r="B1484"/>
       <c r="C1484"/>
-      <c r="D1484" s="1"/>
+      <c r="D1484"/>
+      <c r="G1484"/>
     </row>
     <row r="1485" ht="12.75">
       <c r="A1485" s="6"/>
       <c r="B1485"/>
       <c r="C1485"/>
-      <c r="D1485"/>
-      <c r="G1485"/>
+      <c r="D1485" s="1"/>
     </row>
     <row r="1486" ht="12.75">
       <c r="A1486" s="6"/>
       <c r="B1486"/>
       <c r="C1486"/>
-      <c r="D1486" s="1"/>
+      <c r="D1486"/>
+      <c r="G1486"/>
     </row>
     <row r="1487" ht="12.75">
       <c r="A1487" s="6"/>
       <c r="B1487"/>
       <c r="C1487"/>
-      <c r="D1487"/>
-      <c r="G1487"/>
+      <c r="D1487" s="1"/>
     </row>
     <row r="1488" ht="12.75">
       <c r="A1488" s="6"/>
       <c r="B1488"/>
       <c r="C1488"/>
-      <c r="D1488" s="1"/>
+      <c r="D1488"/>
+      <c r="G1488"/>
     </row>
     <row r="1489" ht="12.75">
       <c r="A1489" s="6"/>
       <c r="B1489"/>
       <c r="C1489"/>
-      <c r="D1489"/>
-      <c r="G1489"/>
+      <c r="D1489" s="1"/>
     </row>
     <row r="1490" ht="12.75">
       <c r="A1490" s="6"/>
       <c r="B1490"/>
       <c r="C1490"/>
-      <c r="D1490" s="1"/>
+      <c r="D1490"/>
+      <c r="G1490"/>
     </row>
     <row r="1491" ht="12.75">
       <c r="A1491" s="6"/>
       <c r="B1491"/>
       <c r="C1491"/>
-      <c r="D1491"/>
-      <c r="G1491"/>
+      <c r="D1491" s="1"/>
     </row>
     <row r="1492" ht="12.75">
       <c r="A1492" s="6"/>
       <c r="B1492"/>
       <c r="C1492"/>
-      <c r="D1492" s="1"/>
+      <c r="D1492"/>
+      <c r="G1492"/>
     </row>
     <row r="1493" ht="12.75">
       <c r="A1493" s="6"/>
       <c r="B1493"/>
       <c r="C1493"/>
-      <c r="D1493"/>
-      <c r="G1493"/>
+      <c r="D1493" s="1"/>
     </row>
     <row r="1494" ht="12.75">
       <c r="A1494" s="6"/>
       <c r="B1494"/>
       <c r="C1494"/>
-      <c r="D1494" s="1"/>
+      <c r="D1494"/>
+      <c r="G1494"/>
     </row>
     <row r="1495" ht="12.75">
       <c r="A1495" s="6"/>
       <c r="B1495"/>
       <c r="C1495"/>
-      <c r="D1495"/>
-      <c r="G1495"/>
+      <c r="D1495" s="1"/>
     </row>
     <row r="1496" ht="12.75">
       <c r="A1496" s="6"/>
       <c r="B1496"/>
       <c r="C1496"/>
-      <c r="D1496" s="1"/>
+      <c r="D1496"/>
+      <c r="G1496"/>
     </row>
     <row r="1497" ht="12.75">
       <c r="A1497" s="6"/>
       <c r="B1497"/>
       <c r="C1497"/>
-      <c r="D1497"/>
-      <c r="G1497"/>
+      <c r="D1497" s="1"/>
     </row>
     <row r="1498" ht="12.75">
       <c r="A1498" s="6"/>
       <c r="B1498"/>
       <c r="C1498"/>
-      <c r="D1498" s="1"/>
+      <c r="D1498"/>
+      <c r="G1498"/>
     </row>
     <row r="1499" ht="12.75">
       <c r="A1499" s="6"/>
       <c r="B1499"/>
       <c r="C1499"/>
-      <c r="D1499"/>
-      <c r="G1499"/>
+      <c r="D1499" s="1"/>
     </row>
     <row r="1500" ht="12.75">
       <c r="A1500" s="6"/>
       <c r="B1500"/>
       <c r="C1500"/>
-      <c r="D1500" s="1"/>
+      <c r="D1500"/>
+      <c r="G1500"/>
     </row>
     <row r="1501" ht="12.75">
       <c r="A1501" s="6"/>
       <c r="B1501"/>
       <c r="C1501"/>
-      <c r="D1501"/>
-      <c r="G1501"/>
+      <c r="D1501" s="1"/>
     </row>
     <row r="1502" ht="12.75">
       <c r="A1502" s="6"/>
       <c r="B1502"/>
       <c r="C1502"/>
-      <c r="D1502" s="1"/>
+      <c r="D1502"/>
+      <c r="G1502"/>
     </row>
     <row r="1503" ht="12.75">
       <c r="A1503" s="6"/>
       <c r="B1503"/>
       <c r="C1503"/>
-      <c r="D1503"/>
-      <c r="G1503"/>
+      <c r="D1503" s="1"/>
     </row>
     <row r="1504" ht="12.75">
       <c r="A1504" s="6"/>
       <c r="B1504"/>
       <c r="C1504"/>
-      <c r="D1504" s="1"/>
+      <c r="D1504"/>
+      <c r="G1504"/>
     </row>
     <row r="1505" ht="12.75">
       <c r="A1505" s="6"/>
       <c r="B1505"/>
       <c r="C1505"/>
-      <c r="D1505"/>
-      <c r="G1505"/>
+      <c r="D1505" s="1"/>
     </row>
     <row r="1506" ht="12.75">
       <c r="A1506" s="6"/>
       <c r="B1506"/>
       <c r="C1506"/>
-      <c r="D1506" s="1"/>
+      <c r="D1506"/>
+      <c r="G1506"/>
     </row>
     <row r="1507" ht="12.75">
       <c r="A1507" s="6"/>
       <c r="B1507"/>
       <c r="C1507"/>
-      <c r="D1507"/>
-      <c r="G1507"/>
+      <c r="D1507" s="1"/>
     </row>
     <row r="1508" ht="12.75">
       <c r="A1508" s="6"/>
       <c r="B1508"/>
       <c r="C1508"/>
-      <c r="D1508" s="1"/>
+      <c r="D1508"/>
+      <c r="G1508"/>
     </row>
     <row r="1509" ht="12.75">
       <c r="A1509" s="6"/>
       <c r="B1509"/>
       <c r="C1509"/>
-      <c r="D1509"/>
-      <c r="G1509"/>
+      <c r="D1509" s="1"/>
     </row>
     <row r="1510" ht="12.75">
       <c r="A1510" s="6"/>
       <c r="B1510"/>
       <c r="C1510"/>
-      <c r="D1510" s="1"/>
+      <c r="D1510"/>
+      <c r="G1510"/>
     </row>
     <row r="1511" ht="12.75">
       <c r="A1511" s="6"/>
       <c r="B1511"/>
       <c r="C1511"/>
-      <c r="D1511"/>
-      <c r="G1511"/>
+      <c r="D1511" s="1"/>
     </row>
     <row r="1512" ht="12.75">
       <c r="A1512" s="6"/>
       <c r="B1512"/>
       <c r="C1512"/>
-      <c r="D1512" s="1"/>
+      <c r="D1512"/>
+      <c r="G1512"/>
     </row>
     <row r="1513" ht="12.75">
       <c r="A1513" s="6"/>
       <c r="B1513"/>
       <c r="C1513"/>
-      <c r="D1513"/>
-      <c r="G1513"/>
+      <c r="D1513" s="1"/>
     </row>
     <row r="1514" ht="12.75">
       <c r="A1514" s="6"/>
       <c r="B1514"/>
       <c r="C1514"/>
-      <c r="D1514" s="1"/>
+      <c r="D1514"/>
+      <c r="G1514"/>
     </row>
     <row r="1515" ht="12.75">
       <c r="A1515" s="6"/>
       <c r="B1515"/>
       <c r="C1515"/>
-      <c r="D1515"/>
-      <c r="G1515"/>
+      <c r="D1515" s="1"/>
     </row>
     <row r="1516" ht="12.75">
       <c r="A1516" s="6"/>
-      <c r="D1516" s="1"/>
+      <c r="B1516"/>
+      <c r="C1516"/>
+      <c r="D1516"/>
+      <c r="G1516"/>
     </row>
     <row r="1517" ht="12.75">
       <c r="A1517" s="6"/>
@@ -26293,6 +26474,7 @@
     </row>
     <row r="1539" ht="12.75">
       <c r="A1539" s="6"/>
+      <c r="D1539" s="1"/>
     </row>
     <row r="1540" ht="12.75">
       <c r="A1540" s="6"/>
@@ -26303,79 +26485,78 @@
     <row r="1542" ht="12.75">
       <c r="A1542" s="6"/>
     </row>
-    <row r="1813" ht="12.75">
-      <c r="A1813" s="6"/>
-      <c r="B1813"/>
-      <c r="C1813"/>
-      <c r="D1813" s="1"/>
+    <row r="1543" ht="12.75">
+      <c r="A1543" s="6"/>
     </row>
     <row r="1814" ht="12.75">
       <c r="A1814" s="6"/>
       <c r="B1814"/>
       <c r="C1814"/>
-      <c r="D1814"/>
-      <c r="G1814"/>
+      <c r="D1814" s="1"/>
     </row>
     <row r="1815" ht="12.75">
       <c r="A1815" s="6"/>
       <c r="B1815"/>
       <c r="C1815"/>
-      <c r="D1815" s="1"/>
+      <c r="D1815"/>
+      <c r="G1815"/>
     </row>
     <row r="1816" ht="12.75">
       <c r="A1816" s="6"/>
       <c r="B1816"/>
       <c r="C1816"/>
-      <c r="D1816"/>
-      <c r="G1816"/>
+      <c r="D1816" s="1"/>
     </row>
     <row r="1817" ht="12.75">
       <c r="A1817" s="6"/>
       <c r="B1817"/>
       <c r="C1817"/>
-      <c r="D1817" s="1"/>
+      <c r="D1817"/>
+      <c r="G1817"/>
     </row>
     <row r="1818" ht="12.75">
       <c r="A1818" s="6"/>
       <c r="B1818"/>
       <c r="C1818"/>
-      <c r="D1818"/>
-      <c r="G1818"/>
+      <c r="D1818" s="1"/>
     </row>
     <row r="1819" ht="12.75">
       <c r="A1819" s="6"/>
       <c r="B1819"/>
       <c r="C1819"/>
-      <c r="D1819" s="1"/>
+      <c r="D1819"/>
+      <c r="G1819"/>
     </row>
     <row r="1820" ht="12.75">
       <c r="A1820" s="6"/>
       <c r="B1820"/>
       <c r="C1820"/>
-      <c r="D1820"/>
-      <c r="G1820"/>
+      <c r="D1820" s="1"/>
     </row>
     <row r="1821" ht="12.75">
       <c r="A1821" s="6"/>
       <c r="B1821"/>
       <c r="C1821"/>
-      <c r="D1821" s="1"/>
+      <c r="D1821"/>
+      <c r="G1821"/>
     </row>
     <row r="1822" ht="12.75">
       <c r="A1822" s="6"/>
       <c r="B1822"/>
       <c r="C1822"/>
-      <c r="D1822"/>
-      <c r="G1822"/>
-    </row>
-    <row r="1836" ht="12.75">
-      <c r="D1836" s="1"/>
+      <c r="D1822" s="1"/>
+    </row>
+    <row r="1823" ht="12.75">
+      <c r="A1823" s="6"/>
+      <c r="B1823"/>
+      <c r="C1823"/>
+      <c r="D1823"/>
+      <c r="G1823"/>
     </row>
     <row r="1837" ht="12.75">
       <c r="D1837" s="1"/>
     </row>
     <row r="1838" ht="12.75">
-      <c r="A1838" s="6"/>
       <c r="D1838" s="1"/>
     </row>
     <row r="1839" ht="12.75">
@@ -26396,23 +26577,24 @@
     </row>
     <row r="1843" ht="12.75">
       <c r="A1843" s="6"/>
-      <c r="B1843"/>
-      <c r="C1843"/>
       <c r="D1843" s="1"/>
     </row>
     <row r="1844" ht="12.75">
       <c r="A1844" s="6"/>
       <c r="B1844"/>
       <c r="C1844"/>
-      <c r="D1844"/>
-      <c r="G1844"/>
+      <c r="D1844" s="1"/>
     </row>
     <row r="1845" ht="12.75">
       <c r="A1845" s="6"/>
-      <c r="D1845" s="1"/>
+      <c r="B1845"/>
+      <c r="C1845"/>
+      <c r="D1845"/>
+      <c r="G1845"/>
     </row>
     <row r="1846" ht="12.75">
       <c r="A1846" s="6"/>
+      <c r="D1846" s="1"/>
     </row>
     <row r="1847" ht="12.75">
       <c r="A1847" s="6"/>
@@ -26458,12 +26640,12 @@
     </row>
     <row r="1861" ht="12.75">
       <c r="A1861" s="6"/>
-      <c r="B1861"/>
-      <c r="C1861"/>
-      <c r="D1861" s="1"/>
     </row>
     <row r="1862" ht="12.75">
       <c r="A1862" s="6"/>
+      <c r="B1862"/>
+      <c r="C1862"/>
+      <c r="D1862" s="1"/>
     </row>
     <row r="1863" ht="12.75">
       <c r="A1863" s="6"/>
@@ -26473,45 +26655,45 @@
     </row>
     <row r="1865" ht="12.75">
       <c r="A1865" s="6"/>
-      <c r="B1865"/>
-      <c r="C1865"/>
-      <c r="D1865" s="1"/>
     </row>
     <row r="1866" ht="12.75">
       <c r="A1866" s="6"/>
       <c r="B1866"/>
       <c r="C1866"/>
-      <c r="D1866"/>
-      <c r="G1866"/>
+      <c r="D1866" s="1"/>
     </row>
     <row r="1867" ht="12.75">
       <c r="A1867" s="6"/>
       <c r="B1867"/>
       <c r="C1867"/>
-      <c r="D1867" s="1"/>
+      <c r="D1867"/>
+      <c r="G1867"/>
     </row>
     <row r="1868" ht="12.75">
       <c r="A1868" s="6"/>
       <c r="B1868"/>
       <c r="C1868"/>
-      <c r="D1868"/>
-      <c r="G1868"/>
+      <c r="D1868" s="1"/>
     </row>
     <row r="1869" ht="12.75">
       <c r="A1869" s="6"/>
       <c r="B1869"/>
       <c r="C1869"/>
-      <c r="D1869" s="1"/>
+      <c r="D1869"/>
+      <c r="G1869"/>
     </row>
     <row r="1870" ht="12.75">
       <c r="A1870" s="6"/>
       <c r="B1870"/>
       <c r="C1870"/>
-      <c r="D1870"/>
-      <c r="G1870"/>
+      <c r="D1870" s="1"/>
     </row>
     <row r="1871" ht="12.75">
       <c r="A1871" s="6"/>
+      <c r="B1871"/>
+      <c r="C1871"/>
+      <c r="D1871"/>
+      <c r="G1871"/>
     </row>
     <row r="1872" ht="12.75">
       <c r="A1872" s="6"/>
@@ -26530,142 +26712,142 @@
     </row>
     <row r="1877" ht="12.75">
       <c r="A1877" s="6"/>
-      <c r="B1877"/>
-      <c r="C1877"/>
-      <c r="D1877" s="1"/>
     </row>
     <row r="1878" ht="12.75">
       <c r="A1878" s="6"/>
       <c r="B1878"/>
       <c r="C1878"/>
-      <c r="D1878"/>
-      <c r="G1878"/>
+      <c r="D1878" s="1"/>
     </row>
     <row r="1879" ht="12.75">
       <c r="A1879" s="6"/>
       <c r="B1879"/>
       <c r="C1879"/>
-      <c r="D1879" s="1"/>
+      <c r="D1879"/>
+      <c r="G1879"/>
     </row>
     <row r="1880" ht="12.75">
       <c r="A1880" s="6"/>
       <c r="B1880"/>
       <c r="C1880"/>
-      <c r="D1880"/>
-      <c r="G1880"/>
+      <c r="D1880" s="1"/>
     </row>
     <row r="1881" ht="12.75">
       <c r="A1881" s="6"/>
       <c r="B1881"/>
       <c r="C1881"/>
-      <c r="D1881" s="1"/>
+      <c r="D1881"/>
+      <c r="G1881"/>
     </row>
     <row r="1882" ht="12.75">
       <c r="A1882" s="6"/>
       <c r="B1882"/>
       <c r="C1882"/>
-      <c r="D1882"/>
-      <c r="G1882"/>
+      <c r="D1882" s="1"/>
     </row>
     <row r="1883" ht="12.75">
       <c r="A1883" s="6"/>
       <c r="B1883"/>
       <c r="C1883"/>
-      <c r="D1883" s="1"/>
+      <c r="D1883"/>
+      <c r="G1883"/>
     </row>
     <row r="1884" ht="12.75">
       <c r="A1884" s="6"/>
       <c r="B1884"/>
       <c r="C1884"/>
-      <c r="D1884"/>
-      <c r="G1884"/>
+      <c r="D1884" s="1"/>
     </row>
     <row r="1885" ht="12.75">
       <c r="A1885" s="6"/>
       <c r="B1885"/>
       <c r="C1885"/>
-      <c r="D1885" s="1"/>
+      <c r="D1885"/>
+      <c r="G1885"/>
     </row>
     <row r="1886" ht="12.75">
       <c r="A1886" s="6"/>
       <c r="B1886"/>
       <c r="C1886"/>
-      <c r="D1886"/>
-      <c r="G1886"/>
+      <c r="D1886" s="1"/>
     </row>
     <row r="1887" ht="12.75">
       <c r="A1887" s="6"/>
       <c r="B1887"/>
       <c r="C1887"/>
-      <c r="D1887" s="1"/>
+      <c r="D1887"/>
+      <c r="G1887"/>
     </row>
     <row r="1888" ht="12.75">
       <c r="A1888" s="6"/>
       <c r="B1888"/>
       <c r="C1888"/>
-      <c r="D1888"/>
-      <c r="G1888"/>
+      <c r="D1888" s="1"/>
     </row>
     <row r="1889" ht="12.75">
       <c r="A1889" s="6"/>
       <c r="B1889"/>
       <c r="C1889"/>
-      <c r="D1889" s="1"/>
+      <c r="D1889"/>
+      <c r="G1889"/>
     </row>
     <row r="1890" ht="12.75">
       <c r="A1890" s="6"/>
       <c r="B1890"/>
       <c r="C1890"/>
-      <c r="D1890"/>
-      <c r="G1890"/>
+      <c r="D1890" s="1"/>
     </row>
     <row r="1891" ht="12.75">
       <c r="A1891" s="6"/>
       <c r="B1891"/>
       <c r="C1891"/>
-      <c r="D1891" s="1"/>
+      <c r="D1891"/>
+      <c r="G1891"/>
     </row>
     <row r="1892" ht="12.75">
       <c r="A1892" s="6"/>
       <c r="B1892"/>
       <c r="C1892"/>
-      <c r="D1892"/>
-      <c r="G1892"/>
+      <c r="D1892" s="1"/>
     </row>
     <row r="1893" ht="12.75">
       <c r="A1893" s="6"/>
       <c r="B1893"/>
       <c r="C1893"/>
-      <c r="D1893" s="1"/>
+      <c r="D1893"/>
+      <c r="G1893"/>
     </row>
     <row r="1894" ht="12.75">
       <c r="A1894" s="6"/>
       <c r="B1894"/>
       <c r="C1894"/>
-      <c r="D1894"/>
-      <c r="G1894"/>
+      <c r="D1894" s="1"/>
     </row>
     <row r="1895" ht="12.75">
       <c r="A1895" s="6"/>
       <c r="B1895"/>
       <c r="C1895"/>
-      <c r="D1895" s="1"/>
+      <c r="D1895"/>
+      <c r="G1895"/>
     </row>
     <row r="1896" ht="12.75">
       <c r="A1896" s="6"/>
       <c r="B1896"/>
       <c r="C1896"/>
-      <c r="D1896"/>
-      <c r="G1896"/>
+      <c r="D1896" s="1"/>
     </row>
     <row r="1897" ht="12.75">
       <c r="A1897" s="6"/>
       <c r="B1897"/>
       <c r="C1897"/>
-      <c r="D1897" s="1"/>
-    </row>
-    <row r="1900" ht="12.75">
-      <c r="D1900" s="1"/>
+      <c r="D1897"/>
+      <c r="G1897"/>
+    </row>
+    <row r="1898" ht="12.75">
+      <c r="A1898" s="6"/>
+      <c r="B1898"/>
+      <c r="C1898"/>
+      <c r="D1898" s="1"/>
     </row>
     <row r="1901" ht="12.75">
       <c r="D1901" s="1"/>
@@ -26727,8 +26909,8 @@
     <row r="1920" ht="12.75">
       <c r="D1920" s="1"/>
     </row>
-    <row r="1944" ht="12.75">
-      <c r="A1944" s="6"/>
+    <row r="1921" ht="12.75">
+      <c r="D1921" s="1"/>
     </row>
     <row r="1945" ht="12.75">
       <c r="A1945" s="6"/>
@@ -26853,67 +27035,67 @@
     <row r="1985" ht="12.75">
       <c r="A1985" s="6"/>
     </row>
-    <row r="2078" ht="12.75">
-      <c r="A2078" s="6"/>
-      <c r="B2078"/>
-      <c r="C2078"/>
-      <c r="D2078"/>
-      <c r="G2078"/>
+    <row r="1986" ht="12.75">
+      <c r="A1986" s="6"/>
     </row>
     <row r="2079" ht="12.75">
       <c r="A2079" s="6"/>
       <c r="B2079"/>
       <c r="C2079"/>
-      <c r="D2079" s="1"/>
+      <c r="D2079"/>
+      <c r="G2079"/>
     </row>
     <row r="2080" ht="12.75">
       <c r="A2080" s="6"/>
       <c r="B2080"/>
       <c r="C2080"/>
-      <c r="D2080"/>
-      <c r="G2080"/>
+      <c r="D2080" s="1"/>
     </row>
     <row r="2081" ht="12.75">
       <c r="A2081" s="6"/>
       <c r="B2081"/>
       <c r="C2081"/>
-      <c r="D2081" s="1"/>
+      <c r="D2081"/>
+      <c r="G2081"/>
     </row>
     <row r="2082" ht="12.75">
       <c r="A2082" s="6"/>
       <c r="B2082"/>
       <c r="C2082"/>
-      <c r="D2082"/>
-      <c r="G2082"/>
+      <c r="D2082" s="1"/>
     </row>
     <row r="2083" ht="12.75">
       <c r="A2083" s="6"/>
       <c r="B2083"/>
       <c r="C2083"/>
-      <c r="D2083" s="1"/>
+      <c r="D2083"/>
+      <c r="G2083"/>
     </row>
     <row r="2084" ht="12.75">
       <c r="A2084" s="6"/>
       <c r="B2084"/>
       <c r="C2084"/>
-      <c r="D2084"/>
-      <c r="G2084"/>
+      <c r="D2084" s="1"/>
     </row>
     <row r="2085" ht="12.75">
       <c r="A2085" s="6"/>
       <c r="B2085"/>
       <c r="C2085"/>
-      <c r="D2085" s="1"/>
+      <c r="D2085"/>
+      <c r="G2085"/>
     </row>
     <row r="2086" ht="12.75">
       <c r="A2086" s="6"/>
       <c r="B2086"/>
       <c r="C2086"/>
-      <c r="D2086"/>
-      <c r="G2086"/>
-    </row>
-    <row r="2101" ht="12.75">
-      <c r="D2101" s="1"/>
+      <c r="D2086" s="1"/>
+    </row>
+    <row r="2087" ht="12.75">
+      <c r="A2087" s="6"/>
+      <c r="B2087"/>
+      <c r="C2087"/>
+      <c r="D2087"/>
+      <c r="G2087"/>
     </row>
     <row r="2102" ht="12.75">
       <c r="D2102" s="1"/>
@@ -26937,11 +27119,11 @@
       <c r="D2108" s="1"/>
     </row>
     <row r="2109" ht="12.75">
-      <c r="A2109" s="6"/>
       <c r="D2109" s="1"/>
     </row>
     <row r="2110" ht="12.75">
       <c r="A2110" s="6"/>
+      <c r="D2110" s="1"/>
     </row>
     <row r="2111" ht="12.75">
       <c r="A2111" s="6"/>
@@ -26985,8 +27167,8 @@
     <row r="2124" ht="12.75">
       <c r="A2124" s="6"/>
     </row>
-    <row r="2395" ht="12.75">
-      <c r="A2395" s="6"/>
+    <row r="2125" ht="12.75">
+      <c r="A2125" s="6"/>
     </row>
     <row r="2396" ht="12.75">
       <c r="A2396" s="6"/>
@@ -27003,8 +27185,8 @@
     <row r="2400" ht="12.75">
       <c r="A2400" s="6"/>
     </row>
-    <row r="2453" ht="12.75">
-      <c r="A2453" s="6"/>
+    <row r="2401" ht="12.75">
+      <c r="A2401" s="6"/>
     </row>
     <row r="2454" ht="12.75">
       <c r="A2454" s="6"/>
@@ -27033,8 +27215,8 @@
     <row r="2462" ht="12.75">
       <c r="A2462" s="6"/>
     </row>
-    <row r="2590" ht="12.75">
-      <c r="A2590" s="6"/>
+    <row r="2463" ht="12.75">
+      <c r="A2463" s="6"/>
     </row>
     <row r="2591" ht="12.75">
       <c r="A2591" s="6"/>
@@ -27126,24 +27308,22 @@
     <row r="2620" ht="12.75">
       <c r="A2620" s="6"/>
     </row>
-    <row r="2622" ht="12.75">
-      <c r="A2622" s="6"/>
+    <row r="2621" ht="12.75">
+      <c r="A2621" s="6"/>
     </row>
     <row r="2623" ht="12.75">
       <c r="A2623" s="6"/>
-      <c r="B2623"/>
-      <c r="C2623"/>
     </row>
     <row r="2624" ht="12.75">
       <c r="A2624" s="6"/>
+      <c r="B2624"/>
+      <c r="C2624"/>
     </row>
     <row r="2625" ht="12.75">
       <c r="A2625" s="6"/>
     </row>
     <row r="2626" ht="12.75">
       <c r="A2626" s="6"/>
-      <c r="B2626"/>
-      <c r="C2626"/>
     </row>
     <row r="2627" ht="12.75">
       <c r="A2627" s="6"/>
@@ -27198,6 +27378,7 @@
     <row r="2637" ht="12.75">
       <c r="A2637" s="6"/>
       <c r="B2637"/>
+      <c r="C2637"/>
     </row>
     <row r="2638" ht="12.75">
       <c r="A2638" s="6"/>
@@ -27210,26 +27391,30 @@
     <row r="2640" ht="12.75">
       <c r="A2640" s="6"/>
       <c r="B2640"/>
-      <c r="C2640"/>
     </row>
     <row r="2641" ht="12.75">
-      <c r="A2641" s="2"/>
-      <c r="C2641" s="15"/>
+      <c r="A2641" s="6"/>
+      <c r="B2641"/>
+      <c r="C2641"/>
     </row>
     <row r="2642" ht="12.75">
-      <c r="A2642" s="6"/>
+      <c r="A2642" s="2"/>
+      <c r="C2642" s="17"/>
     </row>
     <row r="2643" ht="12.75">
-      <c r="A2643" s="7"/>
+      <c r="A2643" s="6"/>
     </row>
     <row r="2644" ht="12.75">
       <c r="A2644" s="7"/>
     </row>
+    <row r="2645" ht="12.75">
+      <c r="A2645" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1443">
+  <autoFilter ref="A1:C1462">
     <filterColumn colId="0">
       <filters>
-        <filter val="(This is ...) Morrissey"/>
+        <filter val="(This is ...) Zabadak"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/playlists.xlsx
+++ b/playlists.xlsx
@@ -9,8 +9,8 @@
     <sheet name="playlists" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1444</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1464</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">playlists!$A$1:$C$1476</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="2059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="2077">
   <si>
     <t xml:space="preserve">Playlist Name</t>
   </si>
@@ -2290,7 +2290,7 @@
     <t xml:space="preserve">Dr. Dre</t>
   </si>
   <si>
-    <t xml:space="preserve">Hit 'Em Up - Single Version</t>
+    <t xml:space="preserve">Hit 'Em Up</t>
   </si>
   <si>
     <t>2Pac</t>
@@ -6197,6 +6197,60 @@
   </si>
   <si>
     <t xml:space="preserve">Hyakunen No Mangetsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hate It Or Love It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Game, 50 Cent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Go Round This World!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(This is ...) Vacations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Exit</t>
+  </si>
+  <si>
+    <t>Steady</t>
+  </si>
+  <si>
+    <t>Honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Your Own</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day Dreamin</t>
+  </si>
+  <si>
+    <t>Away</t>
+  </si>
+  <si>
+    <t>Moments</t>
+  </si>
+  <si>
+    <t>Relax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moving Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be There</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Hold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Club Social</t>
+  </si>
+  <si>
+    <t>Soft</t>
+  </si>
+  <si>
+    <t>Home</t>
   </si>
 </sst>
 </file>
@@ -6272,7 +6326,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6301,9 +6355,6 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
       <protection hidden="0" locked="1"/>
@@ -6831,7 +6882,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" style="2" width="28.7109375"/>
-    <col customWidth="1" min="2" max="2" style="1" width="50.57421875"/>
+    <col customWidth="1" min="2" max="2" style="1" width="49.28125"/>
     <col customWidth="1" min="3" max="3" style="1" width="40.8515625"/>
     <col customWidth="1" min="4" max="4" style="1" width="28.8515625"/>
     <col min="5" max="16384" style="1" width="9.140625"/>
@@ -21253,7 +21304,7 @@
       <c r="D1078"/>
       <c r="G1078"/>
     </row>
-    <row r="1079" ht="12.75">
+    <row r="1079" ht="12.75" hidden="1">
       <c r="A1079" s="7" t="s">
         <v>1593</v>
       </c>
@@ -21265,19 +21316,19 @@
       </c>
       <c r="D1079" s="1"/>
     </row>
-    <row r="1080" ht="12.75">
+    <row r="1080" ht="12.75" hidden="1">
       <c r="A1080" s="7" t="s">
         <v>1593</v>
       </c>
-      <c r="B1080" s="11" t="s">
+      <c r="B1080" s="8" t="s">
         <v>1596</v>
       </c>
-      <c r="C1080" s="12" t="s">
+      <c r="C1080" s="8" t="s">
         <v>1595</v>
       </c>
-      <c r="D1080" s="13"/>
-    </row>
-    <row r="1081" ht="12.75">
+      <c r="D1080" s="1"/>
+    </row>
+    <row r="1081" ht="12.75" hidden="1">
       <c r="A1081" s="7" t="s">
         <v>1593</v>
       </c>
@@ -21290,7 +21341,7 @@
       <c r="D1081"/>
       <c r="G1081"/>
     </row>
-    <row r="1082" ht="12.75">
+    <row r="1082" ht="12.75" hidden="1">
       <c r="A1082" s="7" t="s">
         <v>1593</v>
       </c>
@@ -22903,7 +22954,7 @@
       <c r="D1210" s="1"/>
     </row>
     <row r="1211" ht="12.75" hidden="1">
-      <c r="A1211" s="14" t="s">
+      <c r="A1211" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1211" t="s">
@@ -22916,7 +22967,7 @@
       <c r="G1211" s="1"/>
     </row>
     <row r="1212" ht="12.75" hidden="1">
-      <c r="A1212" s="14" t="s">
+      <c r="A1212" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1212" t="s">
@@ -22953,7 +23004,7 @@
       <c r="D1214" s="1"/>
     </row>
     <row r="1215" ht="12.75" hidden="1">
-      <c r="A1215" s="14" t="s">
+      <c r="A1215" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1215" t="s">
@@ -22978,7 +23029,7 @@
       <c r="D1216" s="1"/>
     </row>
     <row r="1217" ht="12.75" hidden="1">
-      <c r="A1217" s="14" t="s">
+      <c r="A1217" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1217" t="s">
@@ -22991,7 +23042,7 @@
       <c r="G1217"/>
     </row>
     <row r="1218" ht="12.75" hidden="1">
-      <c r="A1218" s="14" t="s">
+      <c r="A1218" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1218" t="s">
@@ -23003,7 +23054,7 @@
       <c r="D1218" s="1"/>
     </row>
     <row r="1219" ht="12.75" hidden="1">
-      <c r="A1219" s="14" t="s">
+      <c r="A1219" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1219" t="s">
@@ -23028,7 +23079,7 @@
       <c r="D1220" s="1"/>
     </row>
     <row r="1221" ht="12.75" hidden="1">
-      <c r="A1221" s="14" t="s">
+      <c r="A1221" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1221" t="s">
@@ -23041,7 +23092,7 @@
       <c r="G1221"/>
     </row>
     <row r="1222" ht="12.75" hidden="1">
-      <c r="A1222" s="14" t="s">
+      <c r="A1222" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1222" t="s">
@@ -23053,7 +23104,7 @@
       <c r="D1222" s="1"/>
     </row>
     <row r="1223" ht="12.75" hidden="1">
-      <c r="A1223" s="14" t="s">
+      <c r="A1223" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1223" t="s">
@@ -23078,7 +23129,7 @@
       <c r="D1224" s="1"/>
     </row>
     <row r="1225" ht="12.75" hidden="1">
-      <c r="A1225" s="14" t="s">
+      <c r="A1225" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1225" t="s">
@@ -23091,10 +23142,10 @@
       <c r="G1225"/>
     </row>
     <row r="1226" ht="12.75" hidden="1">
-      <c r="A1226" s="14" t="s">
+      <c r="A1226" s="11" t="s">
         <v>1734</v>
       </c>
-      <c r="B1226" s="15">
+      <c r="B1226" s="12">
         <v>0.16666666666666666</v>
       </c>
       <c r="C1226" t="s">
@@ -23103,7 +23154,7 @@
       <c r="D1226" s="1"/>
     </row>
     <row r="1227" ht="12.75" hidden="1">
-      <c r="A1227" s="14" t="s">
+      <c r="A1227" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1227" t="s">
@@ -23116,7 +23167,7 @@
       <c r="G1227"/>
     </row>
     <row r="1228" ht="12.75" hidden="1">
-      <c r="A1228" s="14" t="s">
+      <c r="A1228" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1228" t="s">
@@ -23128,7 +23179,7 @@
       <c r="D1228" s="1"/>
     </row>
     <row r="1229" ht="12.75" hidden="1">
-      <c r="A1229" s="14" t="s">
+      <c r="A1229" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1229" t="s">
@@ -23141,7 +23192,7 @@
       <c r="G1229"/>
     </row>
     <row r="1230" ht="12.75" hidden="1">
-      <c r="A1230" s="14" t="s">
+      <c r="A1230" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1230" t="s">
@@ -23153,7 +23204,7 @@
       <c r="D1230" s="1"/>
     </row>
     <row r="1231" ht="12.75" hidden="1">
-      <c r="A1231" s="14" t="s">
+      <c r="A1231" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1231" t="s">
@@ -23166,7 +23217,7 @@
       <c r="G1231"/>
     </row>
     <row r="1232" ht="12.75" hidden="1">
-      <c r="A1232" s="14" t="s">
+      <c r="A1232" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1232" t="s">
@@ -23178,7 +23229,7 @@
       <c r="D1232" s="1"/>
     </row>
     <row r="1233" ht="12.75" hidden="1">
-      <c r="A1233" s="14" t="s">
+      <c r="A1233" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1233" t="s">
@@ -23191,7 +23242,7 @@
       <c r="G1233"/>
     </row>
     <row r="1234" ht="12.75" hidden="1">
-      <c r="A1234" s="14" t="s">
+      <c r="A1234" s="11" t="s">
         <v>1779</v>
       </c>
       <c r="B1234" t="s">
@@ -23203,7 +23254,7 @@
       <c r="D1234" s="1"/>
     </row>
     <row r="1235" ht="12.75" hidden="1">
-      <c r="A1235" s="14" t="s">
+      <c r="A1235" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1235" t="s">
@@ -23216,7 +23267,7 @@
       <c r="G1235"/>
     </row>
     <row r="1236" ht="12.75" hidden="1">
-      <c r="A1236" s="14" t="s">
+      <c r="A1236" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1236" s="1" t="s">
@@ -23228,7 +23279,7 @@
       <c r="D1236" s="1"/>
     </row>
     <row r="1237" ht="12.75" hidden="1">
-      <c r="A1237" s="14" t="s">
+      <c r="A1237" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1237" t="s">
@@ -23241,7 +23292,7 @@
       <c r="G1237"/>
     </row>
     <row r="1238" ht="12.75" hidden="1">
-      <c r="A1238" s="14" t="s">
+      <c r="A1238" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1238" s="8" t="s">
@@ -23253,7 +23304,7 @@
       <c r="D1238" s="1"/>
     </row>
     <row r="1239" ht="12.75" hidden="1">
-      <c r="A1239" s="14" t="s">
+      <c r="A1239" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1239" t="s">
@@ -23266,7 +23317,7 @@
       <c r="G1239"/>
     </row>
     <row r="1240" ht="12.75" hidden="1">
-      <c r="A1240" s="14" t="s">
+      <c r="A1240" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1240" t="s">
@@ -23278,7 +23329,7 @@
       <c r="D1240" s="1"/>
     </row>
     <row r="1241" ht="12.75" hidden="1">
-      <c r="A1241" s="14" t="s">
+      <c r="A1241" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1241" t="s">
@@ -23291,7 +23342,7 @@
       <c r="G1241"/>
     </row>
     <row r="1242" ht="12.75" hidden="1">
-      <c r="A1242" s="14" t="s">
+      <c r="A1242" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1242" t="s">
@@ -23303,7 +23354,7 @@
       <c r="D1242" s="1"/>
     </row>
     <row r="1243" ht="12.75" hidden="1">
-      <c r="A1243" s="14" t="s">
+      <c r="A1243" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1243" t="s">
@@ -23316,7 +23367,7 @@
       <c r="G1243"/>
     </row>
     <row r="1244" ht="12.75" hidden="1">
-      <c r="A1244" s="14" t="s">
+      <c r="A1244" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1244" t="s">
@@ -23328,7 +23379,7 @@
       <c r="D1244" s="1"/>
     </row>
     <row r="1245" ht="12.75" hidden="1">
-      <c r="A1245" s="14" t="s">
+      <c r="A1245" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1245" t="s">
@@ -23340,7 +23391,7 @@
       <c r="D1245" s="1"/>
     </row>
     <row r="1246" ht="12.75" hidden="1">
-      <c r="A1246" s="14" t="s">
+      <c r="A1246" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1246" t="s">
@@ -23353,7 +23404,7 @@
       <c r="G1246"/>
     </row>
     <row r="1247" ht="12.75" hidden="1">
-      <c r="A1247" s="14" t="s">
+      <c r="A1247" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1247" s="8" t="s">
@@ -23365,20 +23416,20 @@
       <c r="D1247" s="1"/>
     </row>
     <row r="1248" ht="12.75" hidden="1">
-      <c r="A1248" s="14" t="s">
+      <c r="A1248" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1248" t="s">
         <v>1794</v>
       </c>
-      <c r="C1248" s="16" t="s">
+      <c r="C1248" s="13" t="s">
         <v>1738</v>
       </c>
       <c r="D1248"/>
       <c r="G1248"/>
     </row>
     <row r="1249" ht="12.75" hidden="1">
-      <c r="A1249" s="14" t="s">
+      <c r="A1249" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1249" t="s">
@@ -23440,7 +23491,7 @@
       <c r="D1253" s="1"/>
     </row>
     <row r="1254" ht="12.75" hidden="1">
-      <c r="A1254" s="14" t="s">
+      <c r="A1254" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1254" t="s">
@@ -23453,7 +23504,7 @@
       <c r="G1254"/>
     </row>
     <row r="1255" ht="12.75" hidden="1">
-      <c r="A1255" s="14" t="s">
+      <c r="A1255" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1255" t="s">
@@ -23465,7 +23516,7 @@
       <c r="D1255" s="1"/>
     </row>
     <row r="1256" ht="12.75" hidden="1">
-      <c r="A1256" s="14" t="s">
+      <c r="A1256" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1256" t="s">
@@ -23478,7 +23529,7 @@
       <c r="G1256"/>
     </row>
     <row r="1257" ht="12.75" hidden="1">
-      <c r="A1257" s="14" t="s">
+      <c r="A1257" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1257" t="s">
@@ -23490,7 +23541,7 @@
       <c r="D1257" s="1"/>
     </row>
     <row r="1258" ht="12.75" hidden="1">
-      <c r="A1258" s="14" t="s">
+      <c r="A1258" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1258" s="1" t="s">
@@ -23528,57 +23579,64 @@
       <c r="G1260"/>
     </row>
     <row r="1261" ht="12.75" hidden="1">
-      <c r="A1261" s="6"/>
-      <c r="B1261"/>
-      <c r="C1261"/>
-      <c r="D1261" s="1"/>
+      <c r="A1261" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1261" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1261"/>
+      <c r="G1261"/>
     </row>
     <row r="1262" ht="12.75" hidden="1">
       <c r="A1262" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="B1262" s="9" t="s">
-        <v>1600</v>
-      </c>
-      <c r="C1262" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1262"/>
-      <c r="G1262"/>
+      <c r="B1262" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C1262" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D1262" s="1"/>
     </row>
     <row r="1263" ht="12.75" hidden="1">
       <c r="A1263" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="B1263" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="C1263" s="1" t="s">
-        <v>1814</v>
+      <c r="B1263" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>423</v>
       </c>
       <c r="D1263" s="1"/>
     </row>
     <row r="1264" ht="12.75" hidden="1">
-      <c r="A1264" s="6" t="s">
+      <c r="A1264" s="7" t="s">
         <v>1810</v>
       </c>
-      <c r="B1264" t="s">
-        <v>1815</v>
-      </c>
-      <c r="C1264" t="s">
+      <c r="B1264" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C1264" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D1264"/>
+      <c r="G1264"/>
+    </row>
+    <row r="1265" ht="12.75" hidden="1">
+      <c r="A1265" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1265" s="9" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C1265" t="s">
         <v>423</v>
-      </c>
-      <c r="D1264" s="1"/>
-    </row>
-    <row r="1265" ht="12.75" hidden="1">
-      <c r="A1265" s="7" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B1265" s="1" t="s">
-        <v>1816</v>
-      </c>
-      <c r="C1265" s="1" t="s">
-        <v>1145</v>
       </c>
       <c r="D1265"/>
       <c r="G1265"/>
@@ -23587,504 +23645,504 @@
       <c r="A1266" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="B1266" s="9" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C1266" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1266"/>
-      <c r="G1266"/>
+      <c r="B1266" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C1266" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D1266" s="1"/>
     </row>
     <row r="1267" ht="12.75" hidden="1">
       <c r="A1267" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="B1267" s="1" t="s">
-        <v>1817</v>
-      </c>
-      <c r="C1267" s="1" t="s">
-        <v>1818</v>
+      <c r="B1267" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>423</v>
       </c>
       <c r="D1267" s="1"/>
     </row>
     <row r="1268" ht="12.75" hidden="1">
-      <c r="A1268" s="6" t="s">
+      <c r="A1268" s="7" t="s">
         <v>1810</v>
       </c>
       <c r="B1268" t="s">
-        <v>428</v>
+        <v>1819</v>
       </c>
       <c r="C1268" t="s">
+        <v>956</v>
+      </c>
+      <c r="D1268"/>
+      <c r="G1268"/>
+    </row>
+    <row r="1269" ht="12.75" hidden="1">
+      <c r="A1269" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1269" s="9" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C1269" t="s">
         <v>423</v>
       </c>
-      <c r="D1268" s="1"/>
-    </row>
-    <row r="1269" ht="12.75" hidden="1">
-      <c r="A1269" s="7" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B1269" t="s">
-        <v>1819</v>
-      </c>
-      <c r="C1269" t="s">
-        <v>956</v>
-      </c>
-      <c r="D1269"/>
-      <c r="G1269"/>
+      <c r="D1269" s="1"/>
     </row>
     <row r="1270" ht="12.75" hidden="1">
       <c r="A1270" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="B1270" s="9" t="s">
-        <v>1606</v>
+      <c r="B1270" t="s">
+        <v>1820</v>
       </c>
       <c r="C1270" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1270" s="1"/>
+        <v>1145</v>
+      </c>
+      <c r="D1270"/>
+      <c r="G1270"/>
     </row>
     <row r="1271" ht="12.75" hidden="1">
       <c r="A1271" s="6" t="s">
         <v>1810</v>
       </c>
       <c r="B1271" t="s">
-        <v>1820</v>
-      </c>
-      <c r="C1271" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D1271"/>
-      <c r="G1271"/>
+        <v>1821</v>
+      </c>
+      <c r="C1271" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1271" s="1"/>
     </row>
     <row r="1272" ht="12.75" hidden="1">
-      <c r="A1272" s="6" t="s">
+      <c r="A1272" s="7" t="s">
         <v>1810</v>
       </c>
-      <c r="B1272" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C1272" s="9" t="s">
+      <c r="B1272" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C1272" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D1272" s="1"/>
+    </row>
+    <row r="1273" ht="12.75" hidden="1">
+      <c r="A1273" s="6" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C1273" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="D1272" s="1"/>
-    </row>
-    <row r="1273" ht="12.75" hidden="1">
-      <c r="A1273" s="7" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B1273" s="1" t="s">
-        <v>1822</v>
-      </c>
-      <c r="C1273" s="1" t="s">
-        <v>1823</v>
-      </c>
       <c r="D1273" s="1"/>
+      <c r="G1273" s="1"/>
     </row>
     <row r="1274" ht="12.75" hidden="1">
-      <c r="A1274" s="6" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B1274" t="s">
-        <v>1824</v>
+      <c r="A1274" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1274" s="1" t="s">
+        <v>1825</v>
       </c>
       <c r="C1274" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="D1274" s="1"/>
-      <c r="G1274" s="1"/>
+      <c r="D1274"/>
+      <c r="G1274"/>
     </row>
     <row r="1275" ht="12.75" hidden="1">
-      <c r="A1275" s="7" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B1275" s="1" t="s">
-        <v>1825</v>
-      </c>
-      <c r="C1275" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1275"/>
-      <c r="G1275"/>
+      <c r="A1275" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1275" s="8" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C1275" s="8" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1275" s="1"/>
     </row>
     <row r="1276" ht="12.75" hidden="1">
-      <c r="A1276" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1276" s="8" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C1276" s="8" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D1276" s="1"/>
+      <c r="A1276" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1276" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C1276" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D1276"/>
+      <c r="G1276"/>
     </row>
     <row r="1277" ht="12.75" hidden="1">
-      <c r="A1277" s="7" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B1277" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="C1277" s="1" t="s">
-        <v>1668</v>
-      </c>
-      <c r="D1277"/>
-      <c r="G1277"/>
+      <c r="A1277" s="6" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1277" s="1"/>
     </row>
     <row r="1278" ht="12.75" hidden="1">
       <c r="A1278" s="6" t="s">
         <v>1830</v>
       </c>
       <c r="B1278" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C1278" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D1278" s="1"/>
+        <v>1833</v>
+      </c>
+      <c r="D1278"/>
+      <c r="G1278"/>
     </row>
     <row r="1279" ht="12.75" hidden="1">
       <c r="A1279" s="6" t="s">
         <v>1830</v>
       </c>
       <c r="B1279" t="s">
-        <v>1832</v>
-      </c>
-      <c r="C1279" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D1279"/>
-      <c r="G1279"/>
+        <v>1834</v>
+      </c>
+      <c r="C1279"/>
+      <c r="D1279" s="1"/>
     </row>
     <row r="1280" ht="12.75" hidden="1">
       <c r="A1280" s="6" t="s">
         <v>1830</v>
       </c>
       <c r="B1280" t="s">
-        <v>1834</v>
-      </c>
-      <c r="C1280"/>
-      <c r="D1280" s="1"/>
+        <v>1835</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>432</v>
+      </c>
+      <c r="D1280"/>
+      <c r="G1280"/>
     </row>
     <row r="1281" ht="12.75" hidden="1">
-      <c r="A1281" s="6" t="s">
-        <v>1830</v>
+      <c r="A1281" s="7" t="s">
+        <v>1666</v>
       </c>
       <c r="B1281" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C1281" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1281"/>
-      <c r="G1281"/>
+        <v>1836</v>
+      </c>
+      <c r="C1281" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D1281" s="1"/>
     </row>
     <row r="1282" ht="12.75" hidden="1">
-      <c r="A1282" s="7" t="s">
-        <v>1666</v>
+      <c r="A1282" s="6" t="s">
+        <v>1837</v>
       </c>
       <c r="B1282" t="s">
-        <v>1836</v>
-      </c>
-      <c r="C1282" s="1" t="s">
-        <v>1668</v>
-      </c>
-      <c r="D1282" s="1"/>
+        <v>1838</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D1282"/>
+      <c r="G1282"/>
     </row>
     <row r="1283" ht="12.75" hidden="1">
       <c r="A1283" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="B1283" t="s">
-        <v>1838</v>
+      <c r="B1283" s="8" t="s">
+        <v>1840</v>
       </c>
       <c r="C1283" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D1283"/>
-      <c r="G1283"/>
+        <v>432</v>
+      </c>
+      <c r="D1283" s="1"/>
     </row>
     <row r="1284" ht="12.75" hidden="1">
       <c r="A1284" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1284" s="8" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C1284" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1284" s="1"/>
+        <v>1112</v>
+      </c>
+      <c r="D1284"/>
+      <c r="G1284"/>
     </row>
     <row r="1285" ht="12.75" hidden="1">
       <c r="A1285" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1285" s="8" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="C1285" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D1285"/>
-      <c r="G1285"/>
+        <v>497</v>
+      </c>
+      <c r="D1285" s="1"/>
     </row>
     <row r="1286" ht="12.75" hidden="1">
       <c r="A1286" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1286" s="8" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C1286" t="s">
-        <v>497</v>
-      </c>
-      <c r="D1286" s="1"/>
+        <v>1844</v>
+      </c>
+      <c r="D1286"/>
+      <c r="G1286"/>
     </row>
     <row r="1287" ht="12.75" hidden="1">
       <c r="A1287" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1287" s="8" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C1287" t="s">
-        <v>1844</v>
-      </c>
-      <c r="D1287"/>
-      <c r="G1287"/>
+        <v>1123</v>
+      </c>
+      <c r="D1287" s="1"/>
     </row>
     <row r="1288" ht="12.75" hidden="1">
       <c r="A1288" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1288" s="8" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="C1288" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D1288" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="D1288"/>
+      <c r="G1288"/>
     </row>
     <row r="1289" ht="12.75" hidden="1">
       <c r="A1289" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1289" s="8" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C1289" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1289"/>
-      <c r="G1289"/>
+        <v>1848</v>
+      </c>
+      <c r="D1289" s="1"/>
     </row>
     <row r="1290" ht="12.75" hidden="1">
       <c r="A1290" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1290" s="8" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C1290" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D1290" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="D1290"/>
+      <c r="G1290"/>
     </row>
     <row r="1291" ht="12.75" hidden="1">
       <c r="A1291" s="6" t="s">
         <v>1837</v>
       </c>
       <c r="B1291" s="8" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C1291" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D1291"/>
-      <c r="G1291"/>
+        <v>1852</v>
+      </c>
+      <c r="D1291" s="1"/>
     </row>
     <row r="1292" ht="12.75" hidden="1">
       <c r="A1292" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="B1292" s="8" t="s">
-        <v>1851</v>
-      </c>
-      <c r="C1292" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D1292" s="1"/>
+      <c r="B1292" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1292"/>
+      <c r="D1292"/>
+      <c r="G1292"/>
     </row>
     <row r="1293" ht="12.75" hidden="1">
       <c r="A1293" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="B1293" t="s">
-        <v>1853</v>
-      </c>
-      <c r="C1293"/>
-      <c r="D1293"/>
-      <c r="G1293"/>
+      <c r="B1293" s="8" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D1293" s="1"/>
     </row>
     <row r="1294" ht="12.75" hidden="1">
       <c r="A1294" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="B1294" s="8" t="s">
-        <v>1854</v>
+      <c r="B1294" t="s">
+        <v>1856</v>
       </c>
       <c r="C1294" t="s">
-        <v>1855</v>
-      </c>
-      <c r="D1294" s="1"/>
+        <v>423</v>
+      </c>
+      <c r="D1294"/>
+      <c r="G1294"/>
     </row>
     <row r="1295" ht="12.75" hidden="1">
-      <c r="A1295" s="6" t="s">
-        <v>1837</v>
+      <c r="A1295" s="11" t="s">
+        <v>1734</v>
       </c>
       <c r="B1295" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C1295" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1295"/>
-      <c r="G1295"/>
+        <v>1765</v>
+      </c>
+      <c r="D1295" s="1"/>
     </row>
     <row r="1296" ht="12.75" hidden="1">
-      <c r="A1296" s="14" t="s">
+      <c r="A1296" s="11" t="s">
         <v>1734</v>
       </c>
       <c r="B1296" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C1296" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D1296" s="1"/>
+        <v>1859</v>
+      </c>
+      <c r="D1296"/>
+      <c r="G1296"/>
     </row>
     <row r="1297" ht="12.75" hidden="1">
-      <c r="A1297" s="14" t="s">
+      <c r="A1297" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D1297" s="1"/>
+    </row>
+    <row r="1298" ht="12.75" hidden="1">
+      <c r="A1298" s="11" t="s">
         <v>1734</v>
       </c>
-      <c r="B1297" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C1297" t="s">
-        <v>1859</v>
-      </c>
-      <c r="D1297"/>
-      <c r="G1297"/>
-    </row>
-    <row r="1298" ht="12.75" hidden="1">
-      <c r="A1298" s="7" t="s">
-        <v>1342</v>
-      </c>
       <c r="B1298" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="C1298" t="s">
-        <v>1861</v>
-      </c>
-      <c r="D1298" s="1"/>
+        <v>1863</v>
+      </c>
+      <c r="D1298"/>
+      <c r="G1298"/>
     </row>
     <row r="1299" ht="12.75" hidden="1">
-      <c r="A1299" s="14" t="s">
-        <v>1734</v>
+      <c r="A1299" s="6" t="s">
+        <v>1864</v>
       </c>
       <c r="B1299" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="C1299" t="s">
-        <v>1863</v>
-      </c>
-      <c r="D1299"/>
-      <c r="G1299"/>
+        <v>1866</v>
+      </c>
+      <c r="D1299" s="8"/>
+      <c r="G1299" s="8"/>
     </row>
     <row r="1300" ht="12.75" hidden="1">
       <c r="A1300" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1300" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="C1300" t="s">
         <v>1866</v>
       </c>
-      <c r="D1300" s="8"/>
-      <c r="G1300" s="8"/>
+      <c r="D1300" s="1"/>
     </row>
     <row r="1301" ht="12.75" hidden="1">
       <c r="A1301" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1301" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C1301" t="s">
         <v>1866</v>
       </c>
-      <c r="D1301" s="1"/>
+      <c r="D1301"/>
+      <c r="G1301"/>
     </row>
     <row r="1302" ht="12.75" hidden="1">
       <c r="A1302" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1302" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="C1302" t="s">
         <v>1866</v>
       </c>
-      <c r="D1302"/>
-      <c r="G1302"/>
+      <c r="D1302" s="1"/>
     </row>
     <row r="1303" ht="12.75" hidden="1">
       <c r="A1303" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="B1303" t="s">
-        <v>1869</v>
+      <c r="B1303" s="1" t="s">
+        <v>1870</v>
       </c>
       <c r="C1303" t="s">
         <v>1866</v>
       </c>
-      <c r="D1303" s="1"/>
+      <c r="D1303"/>
+      <c r="G1303"/>
     </row>
     <row r="1304" ht="12.75" hidden="1">
       <c r="A1304" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="B1304" s="1" t="s">
-        <v>1870</v>
+      <c r="B1304" t="s">
+        <v>1871</v>
       </c>
       <c r="C1304" t="s">
         <v>1866</v>
       </c>
-      <c r="D1304"/>
-      <c r="G1304"/>
+      <c r="D1304" s="1"/>
     </row>
     <row r="1305" ht="12.75" hidden="1">
       <c r="A1305" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1305" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C1305" t="s">
         <v>1866</v>
       </c>
-      <c r="D1305" s="1"/>
+      <c r="D1305"/>
+      <c r="G1305"/>
     </row>
     <row r="1306" ht="12.75" hidden="1">
       <c r="A1306" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1306" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="C1306" t="s">
         <v>1866</v>
@@ -24097,113 +24155,110 @@
         <v>1864</v>
       </c>
       <c r="B1307" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C1307" t="s">
         <v>1866</v>
       </c>
-      <c r="D1307"/>
-      <c r="G1307"/>
+      <c r="D1307" s="1"/>
     </row>
     <row r="1308" ht="12.75" hidden="1">
       <c r="A1308" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1308" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="C1308" t="s">
         <v>1866</v>
       </c>
-      <c r="D1308" s="1"/>
+      <c r="D1308"/>
+      <c r="G1308"/>
     </row>
     <row r="1309" ht="12.75" hidden="1">
       <c r="A1309" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1309" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C1309" t="s">
         <v>1866</v>
       </c>
-      <c r="D1309"/>
-      <c r="G1309"/>
+      <c r="D1309" s="1"/>
     </row>
     <row r="1310" ht="12.75" hidden="1">
       <c r="A1310" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1310" t="s">
-        <v>1876</v>
-      </c>
-      <c r="C1310" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1310" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1310" s="1"/>
+      <c r="D1310"/>
+      <c r="G1310"/>
     </row>
     <row r="1311" ht="12.75" hidden="1">
       <c r="A1311" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1311" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="C1311" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1311"/>
-      <c r="G1311"/>
+      <c r="D1311" s="1"/>
     </row>
     <row r="1312" ht="12.75" hidden="1">
       <c r="A1312" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="B1312" t="s">
-        <v>1878</v>
+      <c r="B1312" s="8" t="s">
+        <v>1879</v>
       </c>
       <c r="C1312" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1312" s="1"/>
+      <c r="D1312"/>
+      <c r="G1312"/>
     </row>
     <row r="1313" ht="12.75" hidden="1">
       <c r="A1313" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1313" s="8" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="C1313" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1313"/>
-      <c r="G1313"/>
+      <c r="D1313" s="1"/>
     </row>
     <row r="1314" ht="12.75" hidden="1">
       <c r="A1314" s="6" t="s">
         <v>1864</v>
       </c>
       <c r="B1314" s="8" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="C1314" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1314" s="1"/>
+      <c r="D1314"/>
+      <c r="G1314"/>
     </row>
     <row r="1315" ht="12.75" hidden="1">
       <c r="A1315" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="B1315" s="8" t="s">
-        <v>1881</v>
-      </c>
+      <c r="B1315" s="8"/>
       <c r="C1315" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1315"/>
-      <c r="G1315"/>
+      <c r="D1315" s="1"/>
     </row>
     <row r="1316" ht="12.75" hidden="1">
       <c r="A1316" s="6" t="s">
@@ -24213,7 +24268,8 @@
       <c r="C1316" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1316" s="1"/>
+      <c r="D1316"/>
+      <c r="G1316"/>
     </row>
     <row r="1317" ht="12.75" hidden="1">
       <c r="A1317" s="6" t="s">
@@ -24223,113 +24279,115 @@
       <c r="C1317" s="9" t="s">
         <v>1866</v>
       </c>
-      <c r="D1317"/>
-      <c r="G1317"/>
+      <c r="D1317" s="1"/>
     </row>
     <row r="1318" ht="12.75" hidden="1">
       <c r="A1318" s="6" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B1318" s="8"/>
-      <c r="C1318" s="9" t="s">
-        <v>1866</v>
+        <v>1882</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>1226</v>
       </c>
       <c r="D1318" s="1"/>
+      <c r="G1318" s="1"/>
     </row>
     <row r="1319" ht="12.75" hidden="1">
       <c r="A1319" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1319" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C1319" t="s">
         <v>1226</v>
       </c>
-      <c r="D1319" s="1"/>
-      <c r="G1319" s="1"/>
+      <c r="D1319"/>
+      <c r="G1319"/>
     </row>
     <row r="1320" ht="12.75" hidden="1">
       <c r="A1320" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1320" t="s">
-        <v>1884</v>
-      </c>
-      <c r="C1320" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C1320" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1320"/>
-      <c r="G1320"/>
+      <c r="D1320" s="1"/>
     </row>
     <row r="1321" ht="12.75" hidden="1">
       <c r="A1321" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1321" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="C1321" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1321" s="1"/>
+      <c r="D1321"/>
+      <c r="G1321"/>
     </row>
     <row r="1322" ht="12.75" hidden="1">
       <c r="A1322" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1322" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="C1322" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1322"/>
-      <c r="G1322"/>
+      <c r="D1322" s="1"/>
     </row>
     <row r="1323" ht="12.75" hidden="1">
       <c r="A1323" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1323" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="C1323" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1323" s="1"/>
+      <c r="D1323"/>
+      <c r="G1323"/>
     </row>
     <row r="1324" ht="12.75" hidden="1">
       <c r="A1324" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1324" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="C1324" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1324"/>
-      <c r="G1324"/>
+      <c r="D1324" s="1"/>
     </row>
     <row r="1325" ht="12.75" hidden="1">
       <c r="A1325" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1325" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="C1325" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1325" s="1"/>
+      <c r="D1325"/>
+      <c r="G1325"/>
     </row>
     <row r="1326" ht="12.75" hidden="1">
       <c r="A1326" s="6" t="s">
         <v>1882</v>
       </c>
       <c r="B1326" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="C1326" s="9" t="s">
         <v>1226</v>
@@ -24342,48 +24400,48 @@
         <v>1882</v>
       </c>
       <c r="B1327" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C1327" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="D1327"/>
-      <c r="G1327"/>
+      <c r="D1327" s="1"/>
     </row>
     <row r="1328" ht="12.75" hidden="1">
       <c r="A1328" s="6" t="s">
-        <v>1882</v>
+        <v>1893</v>
       </c>
       <c r="B1328" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C1328" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1328" s="1"/>
+        <v>1894</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1328"/>
+      <c r="G1328"/>
     </row>
     <row r="1329" ht="12.75" hidden="1">
       <c r="A1329" s="6" t="s">
         <v>1893</v>
       </c>
       <c r="B1329" t="s">
-        <v>1894</v>
+        <v>1883</v>
       </c>
       <c r="C1329" t="s">
-        <v>1895</v>
-      </c>
-      <c r="D1329"/>
-      <c r="G1329"/>
+        <v>1226</v>
+      </c>
+      <c r="D1329" s="1"/>
+      <c r="G1329" s="1"/>
     </row>
     <row r="1330" ht="12.75" hidden="1">
       <c r="A1330" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1330" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C1330" t="s">
-        <v>1226</v>
+      <c r="B1330" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1330" s="8" t="s">
+        <v>1896</v>
       </c>
       <c r="D1330" s="1"/>
       <c r="G1330" s="1"/>
@@ -24392,50 +24450,49 @@
       <c r="A1331" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1331" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="C1331" s="8" t="s">
-        <v>1896</v>
-      </c>
-      <c r="D1331" s="1"/>
-      <c r="G1331" s="1"/>
+      <c r="B1331" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C1331" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D1331"/>
+      <c r="G1331"/>
     </row>
     <row r="1332" ht="12.75" hidden="1">
       <c r="A1332" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1332" t="s">
-        <v>1884</v>
+      <c r="B1332" s="8" t="s">
+        <v>1897</v>
       </c>
       <c r="C1332" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1332"/>
-      <c r="G1332"/>
+        <v>514</v>
+      </c>
+      <c r="D1332" s="8"/>
+      <c r="G1332" s="8"/>
     </row>
     <row r="1333" ht="12.75" hidden="1">
       <c r="A1333" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1333" s="8" t="s">
-        <v>1897</v>
+      <c r="B1333" t="s">
+        <v>1885</v>
       </c>
       <c r="C1333" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D1333" s="8"/>
-      <c r="G1333" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1333" s="1"/>
     </row>
     <row r="1334" ht="12.75" hidden="1">
       <c r="A1334" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1334" t="s">
-        <v>1885</v>
+      <c r="B1334" s="8" t="s">
+        <v>1898</v>
       </c>
       <c r="C1334" s="9" t="s">
-        <v>1226</v>
+        <v>1895</v>
       </c>
       <c r="D1334" s="1"/>
     </row>
@@ -24443,49 +24500,49 @@
       <c r="A1335" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1335" s="8" t="s">
-        <v>1898</v>
+      <c r="B1335" t="s">
+        <v>1886</v>
       </c>
       <c r="C1335" s="9" t="s">
-        <v>1895</v>
-      </c>
-      <c r="D1335" s="1"/>
+        <v>1226</v>
+      </c>
+      <c r="D1335"/>
+      <c r="G1335"/>
     </row>
     <row r="1336" ht="12.75" hidden="1">
       <c r="A1336" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1336" t="s">
-        <v>1886</v>
+      <c r="B1336" s="8" t="s">
+        <v>1899</v>
       </c>
       <c r="C1336" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1336"/>
-      <c r="G1336"/>
+        <v>1900</v>
+      </c>
+      <c r="D1336" s="8"/>
+      <c r="G1336" s="8"/>
     </row>
     <row r="1337" ht="12.75" hidden="1">
       <c r="A1337" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1337" s="8" t="s">
-        <v>1899</v>
+      <c r="B1337" t="s">
+        <v>1887</v>
       </c>
       <c r="C1337" s="9" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D1337" s="8"/>
-      <c r="G1337" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1337" s="1"/>
     </row>
     <row r="1338" ht="12.75" hidden="1">
       <c r="A1338" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1338" t="s">
-        <v>1887</v>
+      <c r="B1338" s="8" t="s">
+        <v>1901</v>
       </c>
       <c r="C1338" s="9" t="s">
-        <v>1226</v>
+        <v>1902</v>
       </c>
       <c r="D1338" s="1"/>
     </row>
@@ -24493,49 +24550,49 @@
       <c r="A1339" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1339" s="8" t="s">
-        <v>1901</v>
+      <c r="B1339" t="s">
+        <v>1888</v>
       </c>
       <c r="C1339" s="9" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D1339" s="1"/>
+        <v>1226</v>
+      </c>
+      <c r="D1339"/>
+      <c r="G1339"/>
     </row>
     <row r="1340" ht="12.75" hidden="1">
       <c r="A1340" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1340" t="s">
-        <v>1888</v>
+      <c r="B1340" s="8" t="s">
+        <v>1903</v>
       </c>
       <c r="C1340" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1340"/>
-      <c r="G1340"/>
+        <v>1904</v>
+      </c>
+      <c r="D1340" s="8"/>
+      <c r="G1340" s="8"/>
     </row>
     <row r="1341" ht="12.75" hidden="1">
       <c r="A1341" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1341" s="8" t="s">
-        <v>1903</v>
+      <c r="B1341" t="s">
+        <v>1889</v>
       </c>
       <c r="C1341" s="9" t="s">
-        <v>1904</v>
-      </c>
-      <c r="D1341" s="8"/>
-      <c r="G1341" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1341" s="1"/>
     </row>
     <row r="1342" ht="12.75" hidden="1">
       <c r="A1342" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1342" t="s">
-        <v>1889</v>
+      <c r="B1342" s="8" t="s">
+        <v>1141</v>
       </c>
       <c r="C1342" s="9" t="s">
-        <v>1226</v>
+        <v>1905</v>
       </c>
       <c r="D1342" s="1"/>
     </row>
@@ -24543,141 +24600,142 @@
       <c r="A1343" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1343" s="8" t="s">
-        <v>1141</v>
+      <c r="B1343" t="s">
+        <v>1890</v>
       </c>
       <c r="C1343" s="9" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D1343" s="1"/>
+        <v>1226</v>
+      </c>
+      <c r="D1343"/>
+      <c r="G1343"/>
     </row>
     <row r="1344" ht="12.75" hidden="1">
       <c r="A1344" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1344" t="s">
-        <v>1890</v>
+      <c r="B1344" s="8" t="s">
+        <v>1906</v>
       </c>
       <c r="C1344" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1344"/>
-      <c r="G1344"/>
+        <v>1905</v>
+      </c>
+      <c r="D1344" s="8"/>
+      <c r="G1344" s="8"/>
     </row>
     <row r="1345" ht="12.75" hidden="1">
       <c r="A1345" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1345" s="8" t="s">
-        <v>1906</v>
+      <c r="B1345" t="s">
+        <v>1891</v>
       </c>
       <c r="C1345" s="9" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D1345" s="8"/>
-      <c r="G1345" s="8"/>
+        <v>1226</v>
+      </c>
+      <c r="D1345" s="1"/>
     </row>
     <row r="1346" ht="12.75" hidden="1">
       <c r="A1346" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1346" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C1346" s="9" t="s">
-        <v>1226</v>
-      </c>
+      <c r="B1346"/>
+      <c r="C1346" s="9"/>
       <c r="D1346" s="1"/>
     </row>
     <row r="1347" ht="12.75" hidden="1">
       <c r="A1347" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B1347"/>
-      <c r="C1347" s="9"/>
-      <c r="D1347" s="1"/>
+      <c r="B1347" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C1347" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D1347"/>
+      <c r="G1347"/>
     </row>
     <row r="1348" ht="12.75" hidden="1">
-      <c r="A1348" s="6" t="s">
-        <v>1893</v>
+      <c r="A1348" s="7" t="s">
+        <v>1837</v>
       </c>
       <c r="B1348" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C1348" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D1348"/>
-      <c r="G1348"/>
+        <v>1907</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D1348" s="1"/>
     </row>
     <row r="1349" ht="12.75" hidden="1">
-      <c r="A1349" s="7" t="s">
-        <v>1837</v>
+      <c r="A1349" s="6" t="s">
+        <v>1908</v>
       </c>
       <c r="B1349" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1349" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D1349" s="1"/>
+        <v>1793</v>
+      </c>
+      <c r="D1349"/>
+      <c r="G1349"/>
     </row>
     <row r="1350" ht="12.75" hidden="1">
       <c r="A1350" s="6" t="s">
         <v>1908</v>
       </c>
-      <c r="B1350" t="s">
-        <v>1909</v>
+      <c r="B1350" s="8" t="s">
+        <v>1910</v>
       </c>
       <c r="C1350" t="s">
         <v>1793</v>
       </c>
-      <c r="D1350"/>
-      <c r="G1350"/>
+      <c r="D1350" s="1"/>
     </row>
     <row r="1351" ht="12.75" hidden="1">
       <c r="A1351" s="6" t="s">
         <v>1908</v>
       </c>
-      <c r="B1351" s="8" t="s">
-        <v>1910</v>
+      <c r="B1351" t="s">
+        <v>1911</v>
       </c>
       <c r="C1351" t="s">
         <v>1793</v>
       </c>
-      <c r="D1351" s="1"/>
+      <c r="D1351"/>
+      <c r="G1351"/>
     </row>
     <row r="1352" ht="12.75" hidden="1">
       <c r="A1352" s="6" t="s">
         <v>1908</v>
       </c>
       <c r="B1352" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C1352" t="s">
         <v>1793</v>
       </c>
-      <c r="D1352"/>
-      <c r="G1352"/>
+      <c r="D1352" s="1"/>
     </row>
     <row r="1353" ht="12.75" hidden="1">
       <c r="A1353" s="6" t="s">
         <v>1908</v>
       </c>
       <c r="B1353" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="C1353" t="s">
         <v>1793</v>
       </c>
-      <c r="D1353" s="1"/>
+      <c r="D1353"/>
+      <c r="G1353"/>
     </row>
     <row r="1354" ht="12.75" hidden="1">
       <c r="A1354" s="6" t="s">
         <v>1908</v>
       </c>
       <c r="B1354" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="C1354" t="s">
         <v>1793</v>
@@ -24686,464 +24744,464 @@
       <c r="G1354"/>
     </row>
     <row r="1355" ht="12.75" hidden="1">
-      <c r="A1355" s="6" t="s">
-        <v>1908</v>
-      </c>
-      <c r="B1355" t="s">
-        <v>1914</v>
-      </c>
-      <c r="C1355" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D1355"/>
-      <c r="G1355"/>
+      <c r="A1355" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1355" s="8" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C1355" s="8" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1355" s="1"/>
     </row>
     <row r="1356" ht="12.75" hidden="1">
-      <c r="A1356" s="14" t="s">
+      <c r="A1356" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1356" s="8" t="s">
-        <v>1915</v>
-      </c>
-      <c r="C1356" s="8" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D1356" s="1"/>
+        <v>1917</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D1356"/>
+      <c r="G1356"/>
     </row>
     <row r="1357" ht="12.75" hidden="1">
-      <c r="A1357" s="14" t="s">
+      <c r="A1357" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1357" s="8" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C1357" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D1357"/>
-      <c r="G1357"/>
+        <v>1754</v>
+      </c>
+      <c r="D1357" s="1"/>
     </row>
     <row r="1358" ht="12.75" hidden="1">
-      <c r="A1358" s="14" t="s">
+      <c r="A1358" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1358" s="8" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C1358" t="s">
-        <v>1754</v>
-      </c>
-      <c r="D1358" s="1"/>
+        <v>1921</v>
+      </c>
+      <c r="D1358"/>
+      <c r="G1358"/>
     </row>
     <row r="1359" ht="12.75" hidden="1">
-      <c r="A1359" s="14" t="s">
+      <c r="A1359" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1359" s="8" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="C1359" t="s">
         <v>1921</v>
       </c>
-      <c r="D1359"/>
-      <c r="G1359"/>
+      <c r="D1359" s="1"/>
     </row>
     <row r="1360" ht="12.75" hidden="1">
-      <c r="A1360" s="14" t="s">
+      <c r="A1360" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1360" s="8" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="C1360" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D1360" s="1"/>
+        <v>1924</v>
+      </c>
+      <c r="D1360"/>
+      <c r="G1360"/>
     </row>
     <row r="1361" ht="12.75" hidden="1">
-      <c r="A1361" s="14" t="s">
+      <c r="A1361" s="11" t="s">
         <v>1826</v>
       </c>
-      <c r="B1361" s="8" t="s">
-        <v>1923</v>
+      <c r="B1361" t="s">
+        <v>1925</v>
       </c>
       <c r="C1361" t="s">
-        <v>1924</v>
-      </c>
-      <c r="D1361"/>
-      <c r="G1361"/>
+        <v>1926</v>
+      </c>
+      <c r="D1361" s="1"/>
     </row>
     <row r="1362" ht="12.75" hidden="1">
-      <c r="A1362" s="14" t="s">
+      <c r="A1362" s="11" t="s">
         <v>1826</v>
       </c>
-      <c r="B1362" t="s">
-        <v>1925</v>
+      <c r="B1362" s="8" t="s">
+        <v>1927</v>
       </c>
       <c r="C1362" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D1362" s="1"/>
+        <v>1928</v>
+      </c>
+      <c r="D1362"/>
+      <c r="G1362"/>
     </row>
     <row r="1363" ht="12.75" hidden="1">
-      <c r="A1363" s="14" t="s">
+      <c r="A1363" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1363" s="8" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="C1363" t="s">
-        <v>1928</v>
-      </c>
-      <c r="D1363"/>
-      <c r="G1363"/>
+        <v>1930</v>
+      </c>
+      <c r="D1363" s="1"/>
     </row>
     <row r="1364" ht="12.75" hidden="1">
-      <c r="A1364" s="14" t="s">
+      <c r="A1364" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1364" s="8" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C1364" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D1364" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="D1364"/>
+      <c r="G1364"/>
     </row>
     <row r="1365" ht="12.75" hidden="1">
-      <c r="A1365" s="14" t="s">
+      <c r="A1365" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1365" s="8" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C1365" t="s">
-        <v>1932</v>
-      </c>
-      <c r="D1365"/>
-      <c r="G1365"/>
+        <v>1934</v>
+      </c>
+      <c r="D1365" s="1"/>
     </row>
     <row r="1366" ht="12.75" hidden="1">
-      <c r="A1366" s="14" t="s">
+      <c r="A1366" s="11" t="s">
         <v>1826</v>
       </c>
       <c r="B1366" s="8" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C1366" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1366" s="8" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D1366"/>
+      <c r="G1366"/>
+    </row>
+    <row r="1367" ht="12.75" hidden="1">
+      <c r="A1367" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1367" s="8" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C1367" s="8" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D1367" s="1"/>
+    </row>
+    <row r="1368" ht="12.75" hidden="1">
+      <c r="A1368" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1368" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1368" s="8" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D1368"/>
+      <c r="G1368"/>
+    </row>
+    <row r="1369" ht="12.75" hidden="1">
+      <c r="A1369" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1369" s="8" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C1369" s="8" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D1369" s="1"/>
+    </row>
+    <row r="1370" ht="12.75" hidden="1">
+      <c r="A1370" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1370" s="8" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C1370" s="8" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D1370"/>
+      <c r="G1370"/>
+    </row>
+    <row r="1371" ht="12.75" hidden="1">
+      <c r="A1371" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1371" s="8" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1371" s="8" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1371" s="1"/>
+    </row>
+    <row r="1372" ht="12.75" hidden="1">
+      <c r="A1372" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1372" s="8" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C1372" s="8" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D1372"/>
+      <c r="G1372"/>
+    </row>
+    <row r="1373" ht="12.75" hidden="1">
+      <c r="A1373" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1373" s="8" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C1373" s="8" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D1373" s="1"/>
+    </row>
+    <row r="1374" ht="12.75" hidden="1">
+      <c r="A1374" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1374" s="8" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D1374"/>
+      <c r="G1374"/>
+    </row>
+    <row r="1375" ht="12.75" hidden="1">
+      <c r="A1375" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1375" s="8" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C1375" s="8" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D1375" s="1"/>
+    </row>
+    <row r="1376" ht="12.75" hidden="1">
+      <c r="A1376" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1376" s="8" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D1376"/>
+      <c r="G1376"/>
+    </row>
+    <row r="1377" ht="12.75" hidden="1">
+      <c r="A1377" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1377" s="8" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C1377" s="8" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D1377" s="1"/>
+    </row>
+    <row r="1378" ht="12.75" hidden="1">
+      <c r="A1378" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1378" s="8" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D1378"/>
+      <c r="G1378"/>
+    </row>
+    <row r="1379" ht="12.75" hidden="1">
+      <c r="A1379" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1379" s="8" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1379" s="1"/>
+    </row>
+    <row r="1380" ht="12.75" hidden="1">
+      <c r="A1380" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1380" s="8" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D1380"/>
+      <c r="G1380"/>
+    </row>
+    <row r="1381" ht="12.75" hidden="1">
+      <c r="A1381" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1381" s="8" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D1381" s="1"/>
+    </row>
+    <row r="1382" ht="12.75" hidden="1">
+      <c r="A1382" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1382" s="8" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D1382"/>
+      <c r="G1382"/>
+    </row>
+    <row r="1383" ht="12.75" hidden="1">
+      <c r="A1383" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1383" s="8" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D1383" s="1"/>
+    </row>
+    <row r="1384" ht="12.75" hidden="1">
+      <c r="A1384" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1384" s="8" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1384"/>
+      <c r="G1384"/>
+    </row>
+    <row r="1385" ht="12.75" hidden="1">
+      <c r="A1385" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1385" s="8" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D1385" s="1"/>
+    </row>
+    <row r="1386" ht="12.75" hidden="1">
+      <c r="A1386" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1386" s="8" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D1386"/>
+      <c r="G1386"/>
+    </row>
+    <row r="1387" ht="12.75" hidden="1">
+      <c r="A1387" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1387" s="8" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D1387" s="1"/>
+    </row>
+    <row r="1388" ht="12.75" hidden="1">
+      <c r="A1388" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1388" s="8" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D1388"/>
+      <c r="G1388"/>
+    </row>
+    <row r="1389" ht="12.75" hidden="1">
+      <c r="A1389" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1389" s="8" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D1389" s="1"/>
+    </row>
+    <row r="1390" ht="12.75" hidden="1">
+      <c r="A1390" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1390" s="8" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C1390" s="8" t="s">
         <v>1934</v>
       </c>
-      <c r="D1366" s="1"/>
-    </row>
-    <row r="1367" ht="12.75" hidden="1">
-      <c r="A1367" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1367" s="8" t="s">
-        <v>1935</v>
-      </c>
-      <c r="C1367" s="8" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D1367"/>
-      <c r="G1367"/>
-    </row>
-    <row r="1368" ht="12.75" hidden="1">
-      <c r="A1368" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1368" s="8" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C1368" s="8" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D1368" s="1"/>
-    </row>
-    <row r="1369" ht="12.75" hidden="1">
-      <c r="A1369" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1369" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C1369" s="8" t="s">
-        <v>1939</v>
-      </c>
-      <c r="D1369"/>
-      <c r="G1369"/>
-    </row>
-    <row r="1370" ht="12.75" hidden="1">
-      <c r="A1370" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1370" s="8" t="s">
-        <v>1940</v>
-      </c>
-      <c r="C1370" s="8" t="s">
-        <v>1941</v>
-      </c>
-      <c r="D1370" s="1"/>
-    </row>
-    <row r="1371" ht="12.75" hidden="1">
-      <c r="A1371" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1371" s="8" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C1371" s="8" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D1371"/>
-      <c r="G1371"/>
-    </row>
-    <row r="1372" ht="12.75" hidden="1">
-      <c r="A1372" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1372" s="8" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C1372" s="8" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D1372" s="1"/>
-    </row>
-    <row r="1373" ht="12.75" hidden="1">
-      <c r="A1373" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1373" s="8" t="s">
-        <v>1946</v>
-      </c>
-      <c r="C1373" s="8" t="s">
-        <v>1947</v>
-      </c>
-      <c r="D1373"/>
-      <c r="G1373"/>
-    </row>
-    <row r="1374" ht="12.75" hidden="1">
-      <c r="A1374" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1374" s="8" t="s">
-        <v>1948</v>
-      </c>
-      <c r="C1374" s="8" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D1374" s="1"/>
-    </row>
-    <row r="1375" ht="12.75" hidden="1">
-      <c r="A1375" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1375" s="8" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C1375" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D1375"/>
-      <c r="G1375"/>
-    </row>
-    <row r="1376" ht="12.75" hidden="1">
-      <c r="A1376" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1376" s="8" t="s">
-        <v>1952</v>
-      </c>
-      <c r="C1376" s="8" t="s">
-        <v>1953</v>
-      </c>
-      <c r="D1376" s="1"/>
-    </row>
-    <row r="1377" ht="12.75" hidden="1">
-      <c r="A1377" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1377" s="8" t="s">
-        <v>1954</v>
-      </c>
-      <c r="C1377" t="s">
-        <v>1778</v>
-      </c>
-      <c r="D1377"/>
-      <c r="G1377"/>
-    </row>
-    <row r="1378" ht="12.75" hidden="1">
-      <c r="A1378" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1378" s="8" t="s">
-        <v>1955</v>
-      </c>
-      <c r="C1378" s="8" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D1378" s="1"/>
-    </row>
-    <row r="1379" ht="12.75" hidden="1">
-      <c r="A1379" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1379" s="8" t="s">
-        <v>1957</v>
-      </c>
-      <c r="C1379" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D1379"/>
-      <c r="G1379"/>
-    </row>
-    <row r="1380" ht="12.75" hidden="1">
-      <c r="A1380" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1380" s="8" t="s">
-        <v>1959</v>
-      </c>
-      <c r="C1380" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D1380" s="1"/>
-    </row>
-    <row r="1381" ht="12.75" hidden="1">
-      <c r="A1381" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1381" s="8" t="s">
-        <v>1960</v>
-      </c>
-      <c r="C1381" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D1381"/>
-      <c r="G1381"/>
-    </row>
-    <row r="1382" ht="12.75" hidden="1">
-      <c r="A1382" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1382" s="8" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C1382" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D1382" s="1"/>
-    </row>
-    <row r="1383" ht="12.75" hidden="1">
-      <c r="A1383" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1383" s="8" t="s">
-        <v>1963</v>
-      </c>
-      <c r="C1383" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D1383"/>
-      <c r="G1383"/>
-    </row>
-    <row r="1384" ht="12.75" hidden="1">
-      <c r="A1384" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1384" s="8" t="s">
-        <v>1964</v>
-      </c>
-      <c r="C1384" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D1384" s="1"/>
-    </row>
-    <row r="1385" ht="12.75" hidden="1">
-      <c r="A1385" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1385" s="8" t="s">
-        <v>1966</v>
-      </c>
-      <c r="C1385" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D1385"/>
-      <c r="G1385"/>
-    </row>
-    <row r="1386" ht="12.75" hidden="1">
-      <c r="A1386" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1386" s="8" t="s">
-        <v>1967</v>
-      </c>
-      <c r="C1386" t="s">
-        <v>1968</v>
-      </c>
-      <c r="D1386" s="1"/>
-    </row>
-    <row r="1387" ht="12.75" hidden="1">
-      <c r="A1387" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1387" s="8" t="s">
-        <v>1969</v>
-      </c>
-      <c r="C1387" t="s">
-        <v>1786</v>
-      </c>
-      <c r="D1387"/>
-      <c r="G1387"/>
-    </row>
-    <row r="1388" ht="12.75" hidden="1">
-      <c r="A1388" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1388" s="8" t="s">
-        <v>1970</v>
-      </c>
-      <c r="C1388" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D1388" s="1"/>
-    </row>
-    <row r="1389" ht="12.75" hidden="1">
-      <c r="A1389" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1389" s="8" t="s">
-        <v>1972</v>
-      </c>
-      <c r="C1389" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D1389"/>
-      <c r="G1389"/>
-    </row>
-    <row r="1390" ht="12.75" hidden="1">
-      <c r="A1390" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1390" s="8" t="s">
-        <v>1974</v>
-      </c>
-      <c r="C1390" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D1390" s="1"/>
+      <c r="D1390"/>
+      <c r="G1390"/>
     </row>
     <row r="1391" ht="12.75" hidden="1">
-      <c r="A1391" s="14" t="s">
-        <v>1826</v>
+      <c r="A1391" s="6" t="s">
+        <v>1976</v>
       </c>
       <c r="B1391" s="8" t="s">
-        <v>1975</v>
-      </c>
-      <c r="C1391" s="8" t="s">
-        <v>1934</v>
+        <v>1977</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>1978</v>
       </c>
       <c r="D1391"/>
       <c r="G1391"/>
@@ -25153,23 +25211,22 @@
         <v>1976</v>
       </c>
       <c r="B1392" s="8" t="s">
-        <v>1977</v>
+        <v>1438</v>
       </c>
       <c r="C1392" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D1392"/>
-      <c r="G1392"/>
+        <v>1439</v>
+      </c>
+      <c r="D1392" s="1"/>
     </row>
     <row r="1393" ht="12.75" hidden="1">
       <c r="A1393" s="6" t="s">
         <v>1976</v>
       </c>
       <c r="B1393" s="8" t="s">
-        <v>1438</v>
-      </c>
-      <c r="C1393" t="s">
-        <v>1439</v>
+        <v>1979</v>
+      </c>
+      <c r="C1393" s="8" t="s">
+        <v>1980</v>
       </c>
       <c r="D1393" s="1"/>
     </row>
@@ -25178,35 +25235,35 @@
         <v>1976</v>
       </c>
       <c r="B1394" s="8" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="C1394" s="8" t="s">
-        <v>1980</v>
-      </c>
-      <c r="D1394" s="1"/>
+        <v>1982</v>
+      </c>
+      <c r="D1394"/>
+      <c r="G1394"/>
     </row>
     <row r="1395" ht="12.75" hidden="1">
       <c r="A1395" s="6" t="s">
         <v>1976</v>
       </c>
       <c r="B1395" s="8" t="s">
-        <v>1981</v>
-      </c>
-      <c r="C1395" s="8" t="s">
-        <v>1982</v>
-      </c>
-      <c r="D1395"/>
-      <c r="G1395"/>
+        <v>1440</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D1395" s="1"/>
     </row>
     <row r="1396" ht="12.75" hidden="1">
       <c r="A1396" s="6" t="s">
         <v>1976</v>
       </c>
       <c r="B1396" s="8" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C1396" t="s">
-        <v>1983</v>
+        <v>1984</v>
+      </c>
+      <c r="C1396" s="8" t="s">
+        <v>1980</v>
       </c>
       <c r="D1396" s="1"/>
     </row>
@@ -25215,69 +25272,70 @@
         <v>1976</v>
       </c>
       <c r="B1397" s="8" t="s">
-        <v>1984</v>
-      </c>
-      <c r="C1397" s="8" t="s">
-        <v>1980</v>
-      </c>
-      <c r="D1397" s="1"/>
+        <v>1985</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D1397"/>
+      <c r="G1397"/>
     </row>
     <row r="1398" ht="12.75" hidden="1">
       <c r="A1398" s="6" t="s">
         <v>1976</v>
       </c>
       <c r="B1398" s="8" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="C1398" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D1398"/>
-      <c r="G1398"/>
+        <v>1988</v>
+      </c>
+      <c r="D1398" s="1"/>
     </row>
     <row r="1399" ht="12.75" hidden="1">
       <c r="A1399" s="6" t="s">
         <v>1976</v>
       </c>
       <c r="B1399" s="8" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C1399" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D1399" s="1"/>
+        <v>1989</v>
+      </c>
+      <c r="C1399" s="8" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D1399"/>
+      <c r="G1399"/>
     </row>
     <row r="1400" ht="12.75" hidden="1">
       <c r="A1400" s="6" t="s">
-        <v>1976</v>
-      </c>
-      <c r="B1400" s="8" t="s">
-        <v>1989</v>
-      </c>
-      <c r="C1400" s="8" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D1400"/>
-      <c r="G1400"/>
+        <v>1908</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1400" s="1"/>
     </row>
     <row r="1401" ht="12.75" hidden="1">
       <c r="A1401" s="6" t="s">
         <v>1908</v>
       </c>
       <c r="B1401" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C1401" t="s">
         <v>1793</v>
       </c>
-      <c r="D1401" s="1"/>
+      <c r="D1401"/>
+      <c r="G1401"/>
     </row>
     <row r="1402" ht="12.75" hidden="1">
       <c r="A1402" s="6" t="s">
         <v>1908</v>
       </c>
       <c r="B1402" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="C1402" t="s">
         <v>1793</v>
@@ -25290,700 +25348,699 @@
         <v>1908</v>
       </c>
       <c r="B1403" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C1403" t="s">
         <v>1793</v>
       </c>
-      <c r="D1403"/>
-      <c r="G1403"/>
+      <c r="D1403" s="1"/>
     </row>
     <row r="1404" ht="12.75" hidden="1">
       <c r="A1404" s="6" t="s">
         <v>1908</v>
       </c>
       <c r="B1404" t="s">
-        <v>1994</v>
-      </c>
-      <c r="C1404" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C1404" s="9" t="s">
         <v>1793</v>
       </c>
-      <c r="D1404" s="1"/>
+      <c r="D1404"/>
+      <c r="G1404"/>
     </row>
     <row r="1405" ht="12.75" hidden="1">
-      <c r="A1405" s="6" t="s">
-        <v>1908</v>
-      </c>
-      <c r="B1405" t="s">
-        <v>1995</v>
+      <c r="A1405" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1405" s="9" t="s">
+        <v>1821</v>
       </c>
       <c r="C1405" s="9" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D1405"/>
-      <c r="G1405"/>
+        <v>423</v>
+      </c>
+      <c r="D1405" s="1"/>
     </row>
     <row r="1406" ht="12.75" hidden="1">
       <c r="A1406" s="7" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B1406" s="9" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C1406" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="D1406" s="1"/>
+        <v>1420</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D1406"/>
+      <c r="G1406"/>
     </row>
     <row r="1407" ht="12.75" hidden="1">
       <c r="A1407" s="7" t="s">
         <v>1420</v>
       </c>
       <c r="B1407" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="C1407" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D1407"/>
-      <c r="G1407"/>
+        <v>1999</v>
+      </c>
+      <c r="D1407" s="1"/>
     </row>
     <row r="1408" ht="12.75" hidden="1">
-      <c r="A1408" s="7" t="s">
-        <v>1420</v>
+      <c r="A1408" s="6" t="s">
+        <v>2000</v>
       </c>
       <c r="B1408" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="C1408" t="s">
-        <v>1999</v>
-      </c>
-      <c r="D1408" s="1"/>
+        <v>2002</v>
+      </c>
+      <c r="D1408"/>
+      <c r="G1408"/>
     </row>
     <row r="1409" ht="12.75" hidden="1">
       <c r="A1409" s="6" t="s">
         <v>2000</v>
       </c>
       <c r="B1409" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C1409" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D1409"/>
-      <c r="G1409"/>
+        <v>2004</v>
+      </c>
+      <c r="D1409" s="1"/>
     </row>
     <row r="1410" ht="12.75" hidden="1">
       <c r="A1410" s="6" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="B1410" t="s">
-        <v>2003</v>
-      </c>
-      <c r="C1410" t="s">
-        <v>2004</v>
+        <v>2006</v>
+      </c>
+      <c r="C1410" s="8" t="s">
+        <v>2007</v>
       </c>
       <c r="D1410" s="1"/>
+      <c r="G1410" s="1"/>
     </row>
     <row r="1411" ht="12.75" hidden="1">
       <c r="A1411" s="6" t="s">
         <v>2005</v>
       </c>
       <c r="B1411" t="s">
-        <v>2006</v>
-      </c>
-      <c r="C1411" s="8" t="s">
-        <v>2007</v>
-      </c>
-      <c r="D1411" s="1"/>
-      <c r="G1411" s="1"/>
+        <v>2008</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D1411"/>
+      <c r="G1411"/>
     </row>
     <row r="1412" ht="12.75" hidden="1">
       <c r="A1412" s="6" t="s">
         <v>2005</v>
       </c>
       <c r="B1412" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="C1412" t="s">
-        <v>2009</v>
-      </c>
-      <c r="D1412"/>
-      <c r="G1412"/>
+        <v>2011</v>
+      </c>
+      <c r="D1412" s="1"/>
+      <c r="G1412" s="1"/>
     </row>
     <row r="1413" ht="12.75" hidden="1">
       <c r="A1413" s="6" t="s">
         <v>2005</v>
       </c>
       <c r="B1413" t="s">
-        <v>2010</v>
+        <v>1471</v>
       </c>
       <c r="C1413" t="s">
-        <v>2011</v>
-      </c>
-      <c r="D1413" s="1"/>
-      <c r="G1413" s="1"/>
+        <v>1472</v>
+      </c>
+      <c r="D1413"/>
+      <c r="G1413"/>
     </row>
     <row r="1414" ht="12.75" hidden="1">
-      <c r="A1414" s="6"/>
+      <c r="A1414" s="6" t="s">
+        <v>1976</v>
+      </c>
       <c r="B1414" t="s">
-        <v>1471</v>
-      </c>
-      <c r="C1414" t="s">
-        <v>1472</v>
-      </c>
-      <c r="D1414"/>
-      <c r="G1414"/>
+        <v>2012</v>
+      </c>
+      <c r="C1414" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D1414" s="1"/>
     </row>
     <row r="1415" ht="12.75" hidden="1">
       <c r="A1415" s="6" t="s">
         <v>1976</v>
       </c>
       <c r="B1415" t="s">
-        <v>2012</v>
-      </c>
-      <c r="C1415" s="9" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D1415" s="1"/>
+        <v>2013</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D1415"/>
+      <c r="G1415"/>
     </row>
     <row r="1416" ht="12.75" hidden="1">
-      <c r="A1416" s="6" t="s">
-        <v>1976</v>
+      <c r="A1416" s="7" t="s">
+        <v>749</v>
       </c>
       <c r="B1416" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C1416" t="s">
-        <v>1980</v>
-      </c>
-      <c r="D1416"/>
-      <c r="G1416"/>
+        <v>759</v>
+      </c>
+      <c r="D1416" s="1"/>
     </row>
     <row r="1417" ht="12.75" hidden="1">
       <c r="A1417" s="7" t="s">
-        <v>749</v>
+        <v>2015</v>
       </c>
       <c r="B1417" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C1417" t="s">
-        <v>759</v>
-      </c>
-      <c r="D1417" s="1"/>
+        <v>2017</v>
+      </c>
+      <c r="D1417"/>
+      <c r="G1417"/>
     </row>
     <row r="1418" ht="12.75" hidden="1">
       <c r="A1418" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1418" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C1418" t="s">
         <v>2017</v>
       </c>
-      <c r="D1418"/>
-      <c r="G1418"/>
+      <c r="D1418" s="1"/>
     </row>
     <row r="1419" ht="12.75" hidden="1">
       <c r="A1419" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1419" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C1419" t="s">
         <v>2017</v>
       </c>
-      <c r="D1419" s="1"/>
+      <c r="D1419"/>
+      <c r="G1419"/>
     </row>
     <row r="1420" ht="12.75" hidden="1">
       <c r="A1420" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1420" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C1420" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1420" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1420"/>
-      <c r="G1420"/>
+      <c r="D1420" s="1"/>
     </row>
     <row r="1421" ht="12.75" hidden="1">
       <c r="A1421" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1421" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1421" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1421" s="1"/>
+      <c r="D1421"/>
+      <c r="G1421"/>
     </row>
     <row r="1422" ht="12.75" hidden="1">
       <c r="A1422" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1422" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C1422" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1422"/>
-      <c r="G1422"/>
+      <c r="D1422" s="1"/>
     </row>
     <row r="1423" ht="12.75" hidden="1">
       <c r="A1423" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1423" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C1423" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1423" s="1"/>
+      <c r="D1423"/>
+      <c r="G1423"/>
     </row>
     <row r="1424" ht="12.75" hidden="1">
       <c r="A1424" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1424" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C1424" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1424"/>
-      <c r="G1424"/>
+      <c r="D1424" s="1"/>
     </row>
     <row r="1425" ht="12.75" hidden="1">
       <c r="A1425" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1425" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C1425" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1425" s="1"/>
+      <c r="D1425"/>
+      <c r="G1425"/>
     </row>
     <row r="1426" ht="12.75" hidden="1">
       <c r="A1426" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1426" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C1426" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1426"/>
-      <c r="G1426"/>
+      <c r="D1426" s="1"/>
     </row>
     <row r="1427" ht="12.75" hidden="1">
       <c r="A1427" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1427" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C1427" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1427" s="1"/>
+      <c r="D1427"/>
+      <c r="G1427"/>
     </row>
     <row r="1428" ht="12.75" hidden="1">
       <c r="A1428" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1428" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C1428" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1428"/>
-      <c r="G1428"/>
+      <c r="D1428" s="1"/>
     </row>
     <row r="1429" ht="12.75" hidden="1">
       <c r="A1429" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1429" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="C1429" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1429" s="1"/>
+      <c r="D1429"/>
+      <c r="G1429"/>
     </row>
     <row r="1430" ht="12.75" hidden="1">
       <c r="A1430" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1430" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="C1430" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1430"/>
-      <c r="G1430"/>
+      <c r="D1430" s="1"/>
     </row>
     <row r="1431" ht="12.75" hidden="1">
       <c r="A1431" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1431" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C1431" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1431" s="1"/>
+      <c r="D1431"/>
+      <c r="G1431"/>
     </row>
     <row r="1432" ht="12.75" hidden="1">
       <c r="A1432" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1432" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="C1432" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1432"/>
-      <c r="G1432"/>
+      <c r="D1432" s="1"/>
     </row>
     <row r="1433" ht="12.75" hidden="1">
       <c r="A1433" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1433" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C1433" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1433" s="1"/>
+      <c r="D1433"/>
+      <c r="G1433"/>
     </row>
     <row r="1434" ht="12.75" hidden="1">
       <c r="A1434" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1434" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="C1434" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1434"/>
-      <c r="G1434"/>
+      <c r="D1434" s="1"/>
     </row>
     <row r="1435" ht="12.75" hidden="1">
       <c r="A1435" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1435" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="C1435" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1435" s="1"/>
+      <c r="D1435"/>
+      <c r="G1435"/>
     </row>
     <row r="1436" ht="12.75" hidden="1">
       <c r="A1436" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1436" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="C1436" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1436"/>
-      <c r="G1436"/>
+      <c r="D1436" s="1"/>
     </row>
     <row r="1437" ht="12.75" hidden="1">
       <c r="A1437" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1437" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C1437" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1437" s="1"/>
+      <c r="D1437"/>
+      <c r="G1437"/>
     </row>
     <row r="1438" ht="12.75" hidden="1">
       <c r="A1438" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1438" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="C1438" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1438"/>
-      <c r="G1438"/>
+      <c r="D1438" s="1"/>
     </row>
     <row r="1439" ht="12.75" hidden="1">
       <c r="A1439" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1439" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="C1439" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1439" s="1"/>
+      <c r="D1439"/>
+      <c r="G1439"/>
     </row>
     <row r="1440" ht="12.75" hidden="1">
       <c r="A1440" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1440" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="C1440" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1440"/>
-      <c r="G1440"/>
+      <c r="D1440" s="1"/>
     </row>
     <row r="1441" ht="12.75" hidden="1">
       <c r="A1441" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1441" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="C1441" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1441" s="1"/>
+      <c r="D1441"/>
+      <c r="G1441"/>
     </row>
     <row r="1442" ht="12.75" hidden="1">
       <c r="A1442" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1442" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C1442" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1442"/>
-      <c r="G1442"/>
+      <c r="D1442" s="1"/>
     </row>
     <row r="1443" ht="12.75" hidden="1">
       <c r="A1443" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1443" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C1443" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1443" s="1"/>
+      <c r="D1443"/>
+      <c r="G1443"/>
     </row>
     <row r="1444" ht="12.75" hidden="1">
       <c r="A1444" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1444" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C1444" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1444"/>
-      <c r="G1444"/>
+      <c r="D1444" s="1"/>
     </row>
     <row r="1445" ht="12.75" hidden="1">
       <c r="A1445" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1445" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="C1445" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1445" s="1"/>
+      <c r="D1445"/>
+      <c r="G1445"/>
     </row>
     <row r="1446" ht="12.75" hidden="1">
       <c r="A1446" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1446" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="C1446" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1446"/>
-      <c r="G1446"/>
+      <c r="D1446" s="1"/>
     </row>
     <row r="1447" ht="12.75" hidden="1">
       <c r="A1447" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1447" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="C1447" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1447" s="1"/>
+      <c r="D1447"/>
+      <c r="G1447"/>
     </row>
     <row r="1448" ht="12.75" hidden="1">
       <c r="A1448" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1448" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C1448" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1448"/>
-      <c r="G1448"/>
+      <c r="D1448" s="1"/>
     </row>
     <row r="1449" ht="12.75" hidden="1">
       <c r="A1449" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1449" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="C1449" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1449" s="1"/>
+      <c r="D1449"/>
+      <c r="G1449"/>
     </row>
     <row r="1450" ht="12.75" hidden="1">
       <c r="A1450" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1450" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C1450" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1450"/>
-      <c r="G1450"/>
+      <c r="D1450" s="1"/>
     </row>
     <row r="1451" ht="12.75" hidden="1">
       <c r="A1451" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1451" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="C1451" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1451" s="1"/>
+      <c r="D1451"/>
+      <c r="G1451"/>
     </row>
     <row r="1452" ht="12.75" hidden="1">
       <c r="A1452" s="7" t="s">
         <v>2015</v>
       </c>
-      <c r="B1452" t="s">
-        <v>2051</v>
+      <c r="B1452" s="8" t="s">
+        <v>2052</v>
       </c>
       <c r="C1452" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1452"/>
-      <c r="G1452"/>
+      <c r="D1452" s="1"/>
     </row>
     <row r="1453" ht="12.75" hidden="1">
       <c r="A1453" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1453" s="8" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="C1453" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1453" s="1"/>
+      <c r="D1453"/>
+      <c r="G1453"/>
     </row>
     <row r="1454" ht="12.75" hidden="1">
       <c r="A1454" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1454" s="8" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="C1454" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1454"/>
-      <c r="G1454"/>
+      <c r="D1454" s="1"/>
     </row>
     <row r="1455" ht="12.75" hidden="1">
       <c r="A1455" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1455" s="8" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="C1455" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1455" s="1"/>
+      <c r="D1455"/>
+      <c r="G1455"/>
     </row>
     <row r="1456" ht="12.75" hidden="1">
       <c r="A1456" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1456" s="8" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="C1456" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1456"/>
-      <c r="G1456"/>
+      <c r="D1456" s="1"/>
     </row>
     <row r="1457" ht="12.75" hidden="1">
       <c r="A1457" s="7" t="s">
         <v>2015</v>
       </c>
       <c r="B1457" s="8" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="C1457" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1457" s="1"/>
+      <c r="D1457"/>
+      <c r="G1457"/>
     </row>
     <row r="1458" ht="12.75" hidden="1">
       <c r="A1458" s="7" t="s">
         <v>2015</v>
       </c>
-      <c r="B1458" s="8" t="s">
-        <v>2057</v>
-      </c>
+      <c r="B1458" s="8"/>
       <c r="C1458" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1458"/>
-      <c r="G1458"/>
+      <c r="D1458" s="1"/>
     </row>
     <row r="1459" ht="12.75" hidden="1">
       <c r="A1459" s="7" t="s">
@@ -25993,7 +26050,8 @@
       <c r="C1459" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1459" s="1"/>
+      <c r="D1459"/>
+      <c r="G1459"/>
     </row>
     <row r="1460" ht="12.75" hidden="1">
       <c r="A1460" s="7" t="s">
@@ -26003,8 +26061,7 @@
       <c r="C1460" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1460"/>
-      <c r="G1460"/>
+      <c r="D1460" s="1"/>
     </row>
     <row r="1461" ht="12.75" hidden="1">
       <c r="A1461" s="7" t="s">
@@ -26014,375 +26071,489 @@
       <c r="C1461" s="9" t="s">
         <v>2017</v>
       </c>
-      <c r="D1461" s="1"/>
+      <c r="D1461"/>
+      <c r="G1461"/>
     </row>
     <row r="1462" ht="12.75" hidden="1">
       <c r="A1462" s="7" t="s">
-        <v>2015</v>
-      </c>
-      <c r="B1462" s="8"/>
-      <c r="C1462" s="9" t="s">
-        <v>2017</v>
-      </c>
-      <c r="D1462"/>
-      <c r="G1462"/>
-    </row>
-    <row r="1463" ht="12.75">
+        <v>1593</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D1462" s="1"/>
+    </row>
+    <row r="1463" ht="12.75" hidden="1">
       <c r="A1463" s="7" t="s">
-        <v>1593</v>
+        <v>749</v>
       </c>
       <c r="B1463" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="C1463" t="s">
-        <v>1595</v>
-      </c>
-      <c r="D1463" s="1"/>
-    </row>
-    <row r="1464" ht="12.75">
-      <c r="A1464" s="6"/>
-      <c r="B1464"/>
-      <c r="C1464"/>
-      <c r="D1464"/>
-      <c r="G1464"/>
+        <v>2060</v>
+      </c>
+      <c r="D1463"/>
+      <c r="G1463"/>
+    </row>
+    <row r="1464" ht="12.75" hidden="1">
+      <c r="A1464" s="7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D1464" s="1"/>
     </row>
     <row r="1465" ht="12.75">
-      <c r="A1465" s="6"/>
-      <c r="B1465"/>
-      <c r="C1465"/>
-      <c r="D1465" s="1"/>
+      <c r="A1465" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1465"/>
+      <c r="G1465"/>
     </row>
     <row r="1466" ht="12.75">
-      <c r="A1466" s="6"/>
-      <c r="B1466"/>
-      <c r="C1466"/>
-      <c r="D1466"/>
-      <c r="G1466"/>
+      <c r="A1466" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1466" s="1"/>
     </row>
     <row r="1467" ht="12.75">
-      <c r="A1467" s="6"/>
-      <c r="B1467"/>
-      <c r="C1467"/>
-      <c r="D1467" s="1"/>
+      <c r="A1467" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1467"/>
+      <c r="G1467"/>
     </row>
     <row r="1468" ht="12.75">
-      <c r="A1468" s="6"/>
-      <c r="B1468"/>
-      <c r="C1468"/>
-      <c r="D1468"/>
-      <c r="G1468"/>
+      <c r="A1468" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1468" s="1"/>
     </row>
     <row r="1469" ht="12.75">
-      <c r="A1469" s="6"/>
-      <c r="B1469"/>
-      <c r="C1469"/>
-      <c r="D1469" s="1"/>
+      <c r="A1469" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1469"/>
+      <c r="G1469"/>
     </row>
     <row r="1470" ht="12.75">
-      <c r="A1470" s="6"/>
-      <c r="B1470"/>
-      <c r="C1470"/>
-      <c r="D1470"/>
-      <c r="G1470"/>
+      <c r="A1470" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1470" s="1"/>
     </row>
     <row r="1471" ht="12.75">
-      <c r="A1471" s="6"/>
-      <c r="B1471"/>
-      <c r="C1471"/>
-      <c r="D1471" s="1"/>
+      <c r="A1471" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1471"/>
+      <c r="G1471"/>
     </row>
     <row r="1472" ht="12.75">
-      <c r="A1472" s="6"/>
-      <c r="B1472"/>
-      <c r="C1472"/>
-      <c r="D1472"/>
-      <c r="G1472"/>
+      <c r="A1472" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1472" s="1"/>
     </row>
     <row r="1473" ht="12.75">
-      <c r="A1473" s="6"/>
-      <c r="B1473"/>
-      <c r="C1473"/>
-      <c r="D1473" s="1"/>
+      <c r="A1473" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1473"/>
+      <c r="G1473"/>
     </row>
     <row r="1474" ht="12.75">
-      <c r="A1474" s="6"/>
-      <c r="B1474"/>
-      <c r="C1474"/>
-      <c r="D1474"/>
-      <c r="G1474"/>
+      <c r="A1474" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1474" s="1"/>
     </row>
     <row r="1475" ht="12.75">
-      <c r="A1475" s="6"/>
-      <c r="B1475"/>
-      <c r="C1475"/>
-      <c r="D1475" s="1"/>
+      <c r="A1475" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C1475" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1475"/>
+      <c r="G1475"/>
     </row>
     <row r="1476" ht="12.75">
-      <c r="A1476" s="6"/>
-      <c r="B1476"/>
-      <c r="C1476"/>
-      <c r="D1476"/>
-      <c r="G1476"/>
+      <c r="A1476" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1476" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1476" s="1"/>
     </row>
     <row r="1477" ht="12.75">
-      <c r="A1477" s="6"/>
-      <c r="B1477"/>
-      <c r="C1477"/>
-      <c r="D1477" s="1"/>
+      <c r="A1477" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1477" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1477"/>
+      <c r="G1477"/>
     </row>
     <row r="1478" ht="12.75">
-      <c r="A1478" s="6"/>
-      <c r="B1478"/>
-      <c r="C1478"/>
-      <c r="D1478"/>
-      <c r="G1478"/>
+      <c r="A1478" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1478" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1478" s="1"/>
     </row>
     <row r="1479" ht="12.75">
-      <c r="A1479" s="6"/>
-      <c r="B1479"/>
-      <c r="C1479"/>
-      <c r="D1479" s="1"/>
+      <c r="A1479" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C1479" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1479"/>
+      <c r="G1479"/>
     </row>
     <row r="1480" ht="12.75">
-      <c r="A1480" s="6"/>
-      <c r="B1480"/>
-      <c r="C1480"/>
-      <c r="D1480"/>
-      <c r="G1480"/>
+      <c r="A1480" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C1480" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1480" s="1"/>
     </row>
     <row r="1481" ht="12.75">
-      <c r="A1481" s="6"/>
-      <c r="B1481"/>
-      <c r="C1481"/>
-      <c r="D1481" s="1"/>
+      <c r="A1481" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C1481" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1481"/>
+      <c r="G1481"/>
     </row>
     <row r="1482" ht="12.75">
-      <c r="A1482" s="6"/>
-      <c r="B1482"/>
-      <c r="C1482"/>
-      <c r="D1482"/>
-      <c r="G1482"/>
+      <c r="A1482" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C1482" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1482" s="1"/>
     </row>
     <row r="1483" ht="12.75">
       <c r="A1483" s="6"/>
       <c r="B1483"/>
       <c r="C1483"/>
-      <c r="D1483" s="1"/>
+      <c r="D1483"/>
+      <c r="G1483"/>
     </row>
     <row r="1484" ht="12.75">
       <c r="A1484" s="6"/>
       <c r="B1484"/>
       <c r="C1484"/>
-      <c r="D1484"/>
-      <c r="G1484"/>
+      <c r="D1484" s="1"/>
     </row>
     <row r="1485" ht="12.75">
       <c r="A1485" s="6"/>
       <c r="B1485"/>
       <c r="C1485"/>
-      <c r="D1485" s="1"/>
+      <c r="D1485"/>
+      <c r="G1485"/>
     </row>
     <row r="1486" ht="12.75">
       <c r="A1486" s="6"/>
       <c r="B1486"/>
       <c r="C1486"/>
-      <c r="D1486"/>
-      <c r="G1486"/>
+      <c r="D1486" s="1"/>
     </row>
     <row r="1487" ht="12.75">
       <c r="A1487" s="6"/>
       <c r="B1487"/>
       <c r="C1487"/>
-      <c r="D1487" s="1"/>
+      <c r="D1487"/>
+      <c r="G1487"/>
     </row>
     <row r="1488" ht="12.75">
       <c r="A1488" s="6"/>
       <c r="B1488"/>
       <c r="C1488"/>
-      <c r="D1488"/>
-      <c r="G1488"/>
+      <c r="D1488" s="1"/>
     </row>
     <row r="1489" ht="12.75">
       <c r="A1489" s="6"/>
       <c r="B1489"/>
       <c r="C1489"/>
-      <c r="D1489" s="1"/>
+      <c r="D1489"/>
+      <c r="G1489"/>
     </row>
     <row r="1490" ht="12.75">
       <c r="A1490" s="6"/>
       <c r="B1490"/>
       <c r="C1490"/>
-      <c r="D1490"/>
-      <c r="G1490"/>
+      <c r="D1490" s="1"/>
     </row>
     <row r="1491" ht="12.75">
       <c r="A1491" s="6"/>
       <c r="B1491"/>
       <c r="C1491"/>
-      <c r="D1491" s="1"/>
+      <c r="D1491"/>
+      <c r="G1491"/>
     </row>
     <row r="1492" ht="12.75">
       <c r="A1492" s="6"/>
       <c r="B1492"/>
       <c r="C1492"/>
-      <c r="D1492"/>
-      <c r="G1492"/>
+      <c r="D1492" s="1"/>
     </row>
     <row r="1493" ht="12.75">
       <c r="A1493" s="6"/>
       <c r="B1493"/>
       <c r="C1493"/>
-      <c r="D1493" s="1"/>
+      <c r="D1493"/>
+      <c r="G1493"/>
     </row>
     <row r="1494" ht="12.75">
       <c r="A1494" s="6"/>
       <c r="B1494"/>
       <c r="C1494"/>
-      <c r="D1494"/>
-      <c r="G1494"/>
+      <c r="D1494" s="1"/>
     </row>
     <row r="1495" ht="12.75">
       <c r="A1495" s="6"/>
       <c r="B1495"/>
       <c r="C1495"/>
-      <c r="D1495" s="1"/>
+      <c r="D1495"/>
+      <c r="G1495"/>
     </row>
     <row r="1496" ht="12.75">
       <c r="A1496" s="6"/>
       <c r="B1496"/>
       <c r="C1496"/>
-      <c r="D1496"/>
-      <c r="G1496"/>
+      <c r="D1496" s="1"/>
     </row>
     <row r="1497" ht="12.75">
       <c r="A1497" s="6"/>
       <c r="B1497"/>
       <c r="C1497"/>
-      <c r="D1497" s="1"/>
+      <c r="D1497"/>
+      <c r="G1497"/>
     </row>
     <row r="1498" ht="12.75">
       <c r="A1498" s="6"/>
       <c r="B1498"/>
       <c r="C1498"/>
-      <c r="D1498"/>
-      <c r="G1498"/>
+      <c r="D1498" s="1"/>
     </row>
     <row r="1499" ht="12.75">
       <c r="A1499" s="6"/>
       <c r="B1499"/>
       <c r="C1499"/>
-      <c r="D1499" s="1"/>
+      <c r="D1499"/>
+      <c r="G1499"/>
     </row>
     <row r="1500" ht="12.75">
       <c r="A1500" s="6"/>
       <c r="B1500"/>
       <c r="C1500"/>
-      <c r="D1500"/>
-      <c r="G1500"/>
+      <c r="D1500" s="1"/>
     </row>
     <row r="1501" ht="12.75">
       <c r="A1501" s="6"/>
       <c r="B1501"/>
       <c r="C1501"/>
-      <c r="D1501" s="1"/>
+      <c r="D1501"/>
+      <c r="G1501"/>
     </row>
     <row r="1502" ht="12.75">
       <c r="A1502" s="6"/>
       <c r="B1502"/>
       <c r="C1502"/>
-      <c r="D1502"/>
-      <c r="G1502"/>
+      <c r="D1502" s="1"/>
     </row>
     <row r="1503" ht="12.75">
       <c r="A1503" s="6"/>
       <c r="B1503"/>
       <c r="C1503"/>
-      <c r="D1503" s="1"/>
+      <c r="D1503"/>
+      <c r="G1503"/>
     </row>
     <row r="1504" ht="12.75">
       <c r="A1504" s="6"/>
       <c r="B1504"/>
       <c r="C1504"/>
-      <c r="D1504"/>
-      <c r="G1504"/>
+      <c r="D1504" s="1"/>
     </row>
     <row r="1505" ht="12.75">
       <c r="A1505" s="6"/>
       <c r="B1505"/>
       <c r="C1505"/>
-      <c r="D1505" s="1"/>
+      <c r="D1505"/>
+      <c r="G1505"/>
     </row>
     <row r="1506" ht="12.75">
       <c r="A1506" s="6"/>
       <c r="B1506"/>
       <c r="C1506"/>
-      <c r="D1506"/>
-      <c r="G1506"/>
+      <c r="D1506" s="1"/>
     </row>
     <row r="1507" ht="12.75">
       <c r="A1507" s="6"/>
       <c r="B1507"/>
       <c r="C1507"/>
-      <c r="D1507" s="1"/>
+      <c r="D1507"/>
+      <c r="G1507"/>
     </row>
     <row r="1508" ht="12.75">
       <c r="A1508" s="6"/>
       <c r="B1508"/>
       <c r="C1508"/>
-      <c r="D1508"/>
-      <c r="G1508"/>
+      <c r="D1508" s="1"/>
     </row>
     <row r="1509" ht="12.75">
       <c r="A1509" s="6"/>
       <c r="B1509"/>
       <c r="C1509"/>
-      <c r="D1509" s="1"/>
+      <c r="D1509"/>
+      <c r="G1509"/>
     </row>
     <row r="1510" ht="12.75">
       <c r="A1510" s="6"/>
       <c r="B1510"/>
       <c r="C1510"/>
-      <c r="D1510"/>
-      <c r="G1510"/>
+      <c r="D1510" s="1"/>
     </row>
     <row r="1511" ht="12.75">
       <c r="A1511" s="6"/>
       <c r="B1511"/>
       <c r="C1511"/>
-      <c r="D1511" s="1"/>
+      <c r="D1511"/>
+      <c r="G1511"/>
     </row>
     <row r="1512" ht="12.75">
       <c r="A1512" s="6"/>
       <c r="B1512"/>
       <c r="C1512"/>
-      <c r="D1512"/>
-      <c r="G1512"/>
+      <c r="D1512" s="1"/>
     </row>
     <row r="1513" ht="12.75">
       <c r="A1513" s="6"/>
       <c r="B1513"/>
       <c r="C1513"/>
-      <c r="D1513" s="1"/>
+      <c r="D1513"/>
+      <c r="G1513"/>
     </row>
     <row r="1514" ht="12.75">
       <c r="A1514" s="6"/>
       <c r="B1514"/>
       <c r="C1514"/>
-      <c r="D1514"/>
-      <c r="G1514"/>
+      <c r="D1514" s="1"/>
     </row>
     <row r="1515" ht="12.75">
       <c r="A1515" s="6"/>
       <c r="B1515"/>
       <c r="C1515"/>
-      <c r="D1515" s="1"/>
+      <c r="D1515"/>
+      <c r="G1515"/>
     </row>
     <row r="1516" ht="12.75">
       <c r="A1516" s="6"/>
-      <c r="B1516"/>
-      <c r="C1516"/>
-      <c r="D1516"/>
-      <c r="G1516"/>
+      <c r="D1516" s="1"/>
     </row>
     <row r="1517" ht="12.75">
       <c r="A1517" s="6"/>
@@ -26474,7 +26645,6 @@
     </row>
     <row r="1539" ht="12.75">
       <c r="A1539" s="6"/>
-      <c r="D1539" s="1"/>
     </row>
     <row r="1540" ht="12.75">
       <c r="A1540" s="6"/>
@@ -26485,78 +26655,79 @@
     <row r="1542" ht="12.75">
       <c r="A1542" s="6"/>
     </row>
-    <row r="1543" ht="12.75">
-      <c r="A1543" s="6"/>
+    <row r="1813" ht="12.75">
+      <c r="A1813" s="6"/>
+      <c r="B1813"/>
+      <c r="C1813"/>
+      <c r="D1813" s="1"/>
     </row>
     <row r="1814" ht="12.75">
       <c r="A1814" s="6"/>
       <c r="B1814"/>
       <c r="C1814"/>
-      <c r="D1814" s="1"/>
+      <c r="D1814"/>
+      <c r="G1814"/>
     </row>
     <row r="1815" ht="12.75">
       <c r="A1815" s="6"/>
       <c r="B1815"/>
       <c r="C1815"/>
-      <c r="D1815"/>
-      <c r="G1815"/>
+      <c r="D1815" s="1"/>
     </row>
     <row r="1816" ht="12.75">
       <c r="A1816" s="6"/>
       <c r="B1816"/>
       <c r="C1816"/>
-      <c r="D1816" s="1"/>
+      <c r="D1816"/>
+      <c r="G1816"/>
     </row>
     <row r="1817" ht="12.75">
       <c r="A1817" s="6"/>
       <c r="B1817"/>
       <c r="C1817"/>
-      <c r="D1817"/>
-      <c r="G1817"/>
+      <c r="D1817" s="1"/>
     </row>
     <row r="1818" ht="12.75">
       <c r="A1818" s="6"/>
       <c r="B1818"/>
       <c r="C1818"/>
-      <c r="D1818" s="1"/>
+      <c r="D1818"/>
+      <c r="G1818"/>
     </row>
     <row r="1819" ht="12.75">
       <c r="A1819" s="6"/>
       <c r="B1819"/>
       <c r="C1819"/>
-      <c r="D1819"/>
-      <c r="G1819"/>
+      <c r="D1819" s="1"/>
     </row>
     <row r="1820" ht="12.75">
       <c r="A1820" s="6"/>
       <c r="B1820"/>
       <c r="C1820"/>
-      <c r="D1820" s="1"/>
+      <c r="D1820"/>
+      <c r="G1820"/>
     </row>
     <row r="1821" ht="12.75">
       <c r="A1821" s="6"/>
       <c r="B1821"/>
       <c r="C1821"/>
-      <c r="D1821"/>
-      <c r="G1821"/>
+      <c r="D1821" s="1"/>
     </row>
     <row r="1822" ht="12.75">
       <c r="A1822" s="6"/>
       <c r="B1822"/>
       <c r="C1822"/>
-      <c r="D1822" s="1"/>
-    </row>
-    <row r="1823" ht="12.75">
-      <c r="A1823" s="6"/>
-      <c r="B1823"/>
-      <c r="C1823"/>
-      <c r="D1823"/>
-      <c r="G1823"/>
+      <c r="D1822"/>
+      <c r="G1822"/>
+    </row>
+    <row r="1836" ht="12.75">
+      <c r="D1836" s="1"/>
     </row>
     <row r="1837" ht="12.75">
       <c r="D1837" s="1"/>
     </row>
     <row r="1838" ht="12.75">
+      <c r="A1838" s="6"/>
       <c r="D1838" s="1"/>
     </row>
     <row r="1839" ht="12.75">
@@ -26577,24 +26748,23 @@
     </row>
     <row r="1843" ht="12.75">
       <c r="A1843" s="6"/>
+      <c r="B1843"/>
+      <c r="C1843"/>
       <c r="D1843" s="1"/>
     </row>
     <row r="1844" ht="12.75">
       <c r="A1844" s="6"/>
       <c r="B1844"/>
       <c r="C1844"/>
-      <c r="D1844" s="1"/>
+      <c r="D1844"/>
+      <c r="G1844"/>
     </row>
     <row r="1845" ht="12.75">
       <c r="A1845" s="6"/>
-      <c r="B1845"/>
-      <c r="C1845"/>
-      <c r="D1845"/>
-      <c r="G1845"/>
+      <c r="D1845" s="1"/>
     </row>
     <row r="1846" ht="12.75">
       <c r="A1846" s="6"/>
-      <c r="D1846" s="1"/>
     </row>
     <row r="1847" ht="12.75">
       <c r="A1847" s="6"/>
@@ -26640,12 +26810,12 @@
     </row>
     <row r="1861" ht="12.75">
       <c r="A1861" s="6"/>
+      <c r="B1861"/>
+      <c r="C1861"/>
+      <c r="D1861" s="1"/>
     </row>
     <row r="1862" ht="12.75">
       <c r="A1862" s="6"/>
-      <c r="B1862"/>
-      <c r="C1862"/>
-      <c r="D1862" s="1"/>
     </row>
     <row r="1863" ht="12.75">
       <c r="A1863" s="6"/>
@@ -26655,45 +26825,45 @@
     </row>
     <row r="1865" ht="12.75">
       <c r="A1865" s="6"/>
+      <c r="B1865"/>
+      <c r="C1865"/>
+      <c r="D1865" s="1"/>
     </row>
     <row r="1866" ht="12.75">
       <c r="A1866" s="6"/>
       <c r="B1866"/>
       <c r="C1866"/>
-      <c r="D1866" s="1"/>
+      <c r="D1866"/>
+      <c r="G1866"/>
     </row>
     <row r="1867" ht="12.75">
       <c r="A1867" s="6"/>
       <c r="B1867"/>
       <c r="C1867"/>
-      <c r="D1867"/>
-      <c r="G1867"/>
+      <c r="D1867" s="1"/>
     </row>
     <row r="1868" ht="12.75">
       <c r="A1868" s="6"/>
       <c r="B1868"/>
       <c r="C1868"/>
-      <c r="D1868" s="1"/>
+      <c r="D1868"/>
+      <c r="G1868"/>
     </row>
     <row r="1869" ht="12.75">
       <c r="A1869" s="6"/>
       <c r="B1869"/>
       <c r="C1869"/>
-      <c r="D1869"/>
-      <c r="G1869"/>
+      <c r="D1869" s="1"/>
     </row>
     <row r="1870" ht="12.75">
       <c r="A1870" s="6"/>
       <c r="B1870"/>
       <c r="C1870"/>
-      <c r="D1870" s="1"/>
+      <c r="D1870"/>
+      <c r="G1870"/>
     </row>
     <row r="1871" ht="12.75">
       <c r="A1871" s="6"/>
-      <c r="B1871"/>
-      <c r="C1871"/>
-      <c r="D1871"/>
-      <c r="G1871"/>
     </row>
     <row r="1872" ht="12.75">
       <c r="A1872" s="6"/>
@@ -26712,142 +26882,142 @@
     </row>
     <row r="1877" ht="12.75">
       <c r="A1877" s="6"/>
+      <c r="B1877"/>
+      <c r="C1877"/>
+      <c r="D1877" s="1"/>
     </row>
     <row r="1878" ht="12.75">
       <c r="A1878" s="6"/>
       <c r="B1878"/>
       <c r="C1878"/>
-      <c r="D1878" s="1"/>
+      <c r="D1878"/>
+      <c r="G1878"/>
     </row>
     <row r="1879" ht="12.75">
       <c r="A1879" s="6"/>
       <c r="B1879"/>
       <c r="C1879"/>
-      <c r="D1879"/>
-      <c r="G1879"/>
+      <c r="D1879" s="1"/>
     </row>
     <row r="1880" ht="12.75">
       <c r="A1880" s="6"/>
       <c r="B1880"/>
       <c r="C1880"/>
-      <c r="D1880" s="1"/>
+      <c r="D1880"/>
+      <c r="G1880"/>
     </row>
     <row r="1881" ht="12.75">
       <c r="A1881" s="6"/>
       <c r="B1881"/>
       <c r="C1881"/>
-      <c r="D1881"/>
-      <c r="G1881"/>
+      <c r="D1881" s="1"/>
     </row>
     <row r="1882" ht="12.75">
       <c r="A1882" s="6"/>
       <c r="B1882"/>
       <c r="C1882"/>
-      <c r="D1882" s="1"/>
+      <c r="D1882"/>
+      <c r="G1882"/>
     </row>
     <row r="1883" ht="12.75">
       <c r="A1883" s="6"/>
       <c r="B1883"/>
       <c r="C1883"/>
-      <c r="D1883"/>
-      <c r="G1883"/>
+      <c r="D1883" s="1"/>
     </row>
     <row r="1884" ht="12.75">
       <c r="A1884" s="6"/>
       <c r="B1884"/>
       <c r="C1884"/>
-      <c r="D1884" s="1"/>
+      <c r="D1884"/>
+      <c r="G1884"/>
     </row>
     <row r="1885" ht="12.75">
       <c r="A1885" s="6"/>
       <c r="B1885"/>
       <c r="C1885"/>
-      <c r="D1885"/>
-      <c r="G1885"/>
+      <c r="D1885" s="1"/>
     </row>
     <row r="1886" ht="12.75">
       <c r="A1886" s="6"/>
       <c r="B1886"/>
       <c r="C1886"/>
-      <c r="D1886" s="1"/>
+      <c r="D1886"/>
+      <c r="G1886"/>
     </row>
     <row r="1887" ht="12.75">
       <c r="A1887" s="6"/>
       <c r="B1887"/>
       <c r="C1887"/>
-      <c r="D1887"/>
-      <c r="G1887"/>
+      <c r="D1887" s="1"/>
     </row>
     <row r="1888" ht="12.75">
       <c r="A1888" s="6"/>
       <c r="B1888"/>
       <c r="C1888"/>
-      <c r="D1888" s="1"/>
+      <c r="D1888"/>
+      <c r="G1888"/>
     </row>
     <row r="1889" ht="12.75">
       <c r="A1889" s="6"/>
       <c r="B1889"/>
       <c r="C1889"/>
-      <c r="D1889"/>
-      <c r="G1889"/>
+      <c r="D1889" s="1"/>
     </row>
     <row r="1890" ht="12.75">
       <c r="A1890" s="6"/>
       <c r="B1890"/>
       <c r="C1890"/>
-      <c r="D1890" s="1"/>
+      <c r="D1890"/>
+      <c r="G1890"/>
     </row>
     <row r="1891" ht="12.75">
       <c r="A1891" s="6"/>
       <c r="B1891"/>
       <c r="C1891"/>
-      <c r="D1891"/>
-      <c r="G1891"/>
+      <c r="D1891" s="1"/>
     </row>
     <row r="1892" ht="12.75">
       <c r="A1892" s="6"/>
       <c r="B1892"/>
       <c r="C1892"/>
-      <c r="D1892" s="1"/>
+      <c r="D1892"/>
+      <c r="G1892"/>
     </row>
     <row r="1893" ht="12.75">
       <c r="A1893" s="6"/>
       <c r="B1893"/>
       <c r="C1893"/>
-      <c r="D1893"/>
-      <c r="G1893"/>
+      <c r="D1893" s="1"/>
     </row>
     <row r="1894" ht="12.75">
       <c r="A1894" s="6"/>
       <c r="B1894"/>
       <c r="C1894"/>
-      <c r="D1894" s="1"/>
+      <c r="D1894"/>
+      <c r="G1894"/>
     </row>
     <row r="1895" ht="12.75">
       <c r="A1895" s="6"/>
       <c r="B1895"/>
       <c r="C1895"/>
-      <c r="D1895"/>
-      <c r="G1895"/>
+      <c r="D1895" s="1"/>
     </row>
     <row r="1896" ht="12.75">
       <c r="A1896" s="6"/>
       <c r="B1896"/>
       <c r="C1896"/>
-      <c r="D1896" s="1"/>
+      <c r="D1896"/>
+      <c r="G1896"/>
     </row>
     <row r="1897" ht="12.75">
       <c r="A1897" s="6"/>
       <c r="B1897"/>
       <c r="C1897"/>
-      <c r="D1897"/>
-      <c r="G1897"/>
-    </row>
-    <row r="1898" ht="12.75">
-      <c r="A1898" s="6"/>
-      <c r="B1898"/>
-      <c r="C1898"/>
-      <c r="D1898" s="1"/>
+      <c r="D1897" s="1"/>
+    </row>
+    <row r="1900" ht="12.75">
+      <c r="D1900" s="1"/>
     </row>
     <row r="1901" ht="12.75">
       <c r="D1901" s="1"/>
@@ -26909,8 +27079,8 @@
     <row r="1920" ht="12.75">
       <c r="D1920" s="1"/>
     </row>
-    <row r="1921" ht="12.75">
-      <c r="D1921" s="1"/>
+    <row r="1944" ht="12.75">
+      <c r="A1944" s="6"/>
     </row>
     <row r="1945" ht="12.75">
       <c r="A1945" s="6"/>
@@ -27035,67 +27205,67 @@
     <row r="1985" ht="12.75">
       <c r="A1985" s="6"/>
     </row>
-    <row r="1986" ht="12.75">
-      <c r="A1986" s="6"/>
+    <row r="2078" ht="12.75">
+      <c r="A2078" s="6"/>
+      <c r="B2078"/>
+      <c r="C2078"/>
+      <c r="D2078"/>
+      <c r="G2078"/>
     </row>
     <row r="2079" ht="12.75">
       <c r="A2079" s="6"/>
       <c r="B2079"/>
       <c r="C2079"/>
-      <c r="D2079"/>
-      <c r="G2079"/>
+      <c r="D2079" s="1"/>
     </row>
     <row r="2080" ht="12.75">
       <c r="A2080" s="6"/>
       <c r="B2080"/>
       <c r="C2080"/>
-      <c r="D2080" s="1"/>
+      <c r="D2080"/>
+      <c r="G2080"/>
     </row>
     <row r="2081" ht="12.75">
       <c r="A2081" s="6"/>
       <c r="B2081"/>
       <c r="C2081"/>
-      <c r="D2081"/>
-      <c r="G2081"/>
+      <c r="D2081" s="1"/>
     </row>
     <row r="2082" ht="12.75">
       <c r="A2082" s="6"/>
       <c r="B2082"/>
       <c r="C2082"/>
-      <c r="D2082" s="1"/>
+      <c r="D2082"/>
+      <c r="G2082"/>
     </row>
     <row r="2083" ht="12.75">
       <c r="A2083" s="6"/>
       <c r="B2083"/>
       <c r="C2083"/>
-      <c r="D2083"/>
-      <c r="G2083"/>
+      <c r="D2083" s="1"/>
     </row>
     <row r="2084" ht="12.75">
       <c r="A2084" s="6"/>
       <c r="B2084"/>
       <c r="C2084"/>
-      <c r="D2084" s="1"/>
+      <c r="D2084"/>
+      <c r="G2084"/>
     </row>
     <row r="2085" ht="12.75">
       <c r="A2085" s="6"/>
       <c r="B2085"/>
       <c r="C2085"/>
-      <c r="D2085"/>
-      <c r="G2085"/>
+      <c r="D2085" s="1"/>
     </row>
     <row r="2086" ht="12.75">
       <c r="A2086" s="6"/>
       <c r="B2086"/>
       <c r="C2086"/>
-      <c r="D2086" s="1"/>
-    </row>
-    <row r="2087" ht="12.75">
-      <c r="A2087" s="6"/>
-      <c r="B2087"/>
-      <c r="C2087"/>
-      <c r="D2087"/>
-      <c r="G2087"/>
+      <c r="D2086"/>
+      <c r="G2086"/>
+    </row>
+    <row r="2101" ht="12.75">
+      <c r="D2101" s="1"/>
     </row>
     <row r="2102" ht="12.75">
       <c r="D2102" s="1"/>
@@ -27119,11 +27289,11 @@
       <c r="D2108" s="1"/>
     </row>
     <row r="2109" ht="12.75">
+      <c r="A2109" s="6"/>
       <c r="D2109" s="1"/>
     </row>
     <row r="2110" ht="12.75">
       <c r="A2110" s="6"/>
-      <c r="D2110" s="1"/>
     </row>
     <row r="2111" ht="12.75">
       <c r="A2111" s="6"/>
@@ -27167,8 +27337,8 @@
     <row r="2124" ht="12.75">
       <c r="A2124" s="6"/>
     </row>
-    <row r="2125" ht="12.75">
-      <c r="A2125" s="6"/>
+    <row r="2395" ht="12.75">
+      <c r="A2395" s="6"/>
     </row>
     <row r="2396" ht="12.75">
       <c r="A2396" s="6"/>
@@ -27185,8 +27355,8 @@
     <row r="2400" ht="12.75">
       <c r="A2400" s="6"/>
     </row>
-    <row r="2401" ht="12.75">
-      <c r="A2401" s="6"/>
+    <row r="2453" ht="12.75">
+      <c r="A2453" s="6"/>
     </row>
     <row r="2454" ht="12.75">
       <c r="A2454" s="6"/>
@@ -27215,8 +27385,8 @@
     <row r="2462" ht="12.75">
       <c r="A2462" s="6"/>
     </row>
-    <row r="2463" ht="12.75">
-      <c r="A2463" s="6"/>
+    <row r="2590" ht="12.75">
+      <c r="A2590" s="6"/>
     </row>
     <row r="2591" ht="12.75">
       <c r="A2591" s="6"/>
@@ -27308,22 +27478,24 @@
     <row r="2620" ht="12.75">
       <c r="A2620" s="6"/>
     </row>
-    <row r="2621" ht="12.75">
-      <c r="A2621" s="6"/>
+    <row r="2622" ht="12.75">
+      <c r="A2622" s="6"/>
     </row>
     <row r="2623" ht="12.75">
       <c r="A2623" s="6"/>
+      <c r="B2623"/>
+      <c r="C2623"/>
     </row>
     <row r="2624" ht="12.75">
       <c r="A2624" s="6"/>
-      <c r="B2624"/>
-      <c r="C2624"/>
     </row>
     <row r="2625" ht="12.75">
       <c r="A2625" s="6"/>
     </row>
     <row r="2626" ht="12.75">
       <c r="A2626" s="6"/>
+      <c r="B2626"/>
+      <c r="C2626"/>
     </row>
     <row r="2627" ht="12.75">
       <c r="A2627" s="6"/>
@@ -27378,7 +27550,6 @@
     <row r="2637" ht="12.75">
       <c r="A2637" s="6"/>
       <c r="B2637"/>
-      <c r="C2637"/>
     </row>
     <row r="2638" ht="12.75">
       <c r="A2638" s="6"/>
@@ -27391,30 +27562,29 @@
     <row r="2640" ht="12.75">
       <c r="A2640" s="6"/>
       <c r="B2640"/>
+      <c r="C2640"/>
     </row>
     <row r="2641" ht="12.75">
-      <c r="A2641" s="6"/>
-      <c r="B2641"/>
-      <c r="C2641"/>
+      <c r="A2641" s="2"/>
+      <c r="C2641" s="14"/>
     </row>
     <row r="2642" ht="12.75">
-      <c r="A2642" s="2"/>
-      <c r="C2642" s="17"/>
+      <c r="A2642" s="6"/>
     </row>
     <row r="2643" ht="12.75">
-      <c r="A2643" s="6"/>
+      <c r="A2643" s="7"/>
     </row>
     <row r="2644" ht="12.75">
       <c r="A2644" s="7"/>
     </row>
-    <row r="2645" ht="12.75">
-      <c r="A2645" s="7"/>
+    <row r="2646" ht="12.75">
+      <c r="A2646" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1462">
+  <autoFilter ref="A1:C1476">
     <filterColumn colId="0">
       <filters>
-        <filter val="(This is ...) Zabadak"/>
+        <filter val="(This is ...) Vacations"/>
       </filters>
     </filterColumn>
   </autoFilter>
